--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="G2" t="n">
         <v>2.12</v>
@@ -866,13 +866,13 @@
         <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G6" t="n">
         <v>1.59</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I6" t="n">
         <v>6.4</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K6" t="n">
         <v>5.5</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="Q6" t="n">
         <v>1.45</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>2.58</v>
       </c>
       <c r="I13" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
         <v>3.2</v>
@@ -3681,7 +3681,7 @@
         <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q13" t="n">
         <v>2.1</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
         <v>1.97</v>
@@ -4225,7 +4225,7 @@
         <v>350</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC15" t="n">
         <v>15.5</v>
@@ -4237,7 +4237,7 @@
         <v>150</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG15" t="n">
         <v>12.5</v>
@@ -4249,7 +4249,7 @@
         <v>120</v>
       </c>
       <c r="AJ15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK15" t="n">
         <v>16.5</v>
@@ -4270,13 +4270,13 @@
         <v>20</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
         <v>9</v>
@@ -4285,10 +4285,10 @@
         <v>10</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AX15" t="n">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB15" t="n">
         <v>9.6</v>
@@ -4309,16 +4309,16 @@
         <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF15" t="n">
         <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>2.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
         <v>3.95</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
         <v>1.9</v>
@@ -4458,7 +4458,7 @@
         <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4467,16 +4467,16 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
         <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB16" t="n">
         <v>14</v>
@@ -4485,7 +4485,7 @@
         <v>9.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE16" t="n">
         <v>34</v>
@@ -4500,7 +4500,7 @@
         <v>19.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ16" t="n">
         <v>55</v>
@@ -4509,43 +4509,43 @@
         <v>38</v>
       </c>
       <c r="AL16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM16" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR16" t="n">
         <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV16" t="n">
         <v>9.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>21</v>
+        <v>4.3</v>
       </c>
       <c r="AX16" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AY16" t="n">
         <v>10</v>
@@ -4554,25 +4554,25 @@
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE16" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BF16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G17" t="n">
         <v>1.8</v>
@@ -4694,7 +4694,7 @@
         <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P17" t="n">
         <v>2.18</v>
@@ -4706,7 +4706,7 @@
         <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T17" t="n">
         <v>1.75</v>
@@ -4724,7 +4724,7 @@
         <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z17" t="n">
         <v>48</v>
@@ -4775,58 +4775,58 @@
         <v>75</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV17" t="n">
         <v>5</v>
       </c>
-      <c r="AS17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AW17" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AZ17" t="n">
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC17" t="n">
         <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
         <v>7.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH17" t="n">
         <v>3.9</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
         <v>3.25</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 00:16:48</t>
+          <t>2026-07-09 02:26:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>12.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>6.4</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K6" t="n">
         <v>5.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="n">
         <v>3.65</v>
@@ -3176,7 +3176,7 @@
         <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>1.59</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -3197,19 +3197,19 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
         <v>14.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
         <v>29</v>
       </c>
       <c r="AB11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC11" t="n">
         <v>9.6</v>
@@ -3236,7 +3236,7 @@
         <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL11" t="n">
         <v>46</v>
@@ -3260,7 +3260,7 @@
         <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT11" t="n">
         <v>14</v>
@@ -3275,7 +3275,7 @@
         <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AY11" t="n">
         <v>12.5</v>
@@ -3284,22 +3284,22 @@
         <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BD11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF11" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>21</v>
       </c>
       <c r="BG11" t="n">
         <v>10.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
         <v>1.58</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3959,58 +3959,58 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP14" t="n">
         <v>1.03</v>
@@ -4061,10 +4061,10 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.34</v>
       </c>
       <c r="G15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H15" t="n">
         <v>8.800000000000001</v>
@@ -4192,7 +4192,7 @@
         <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
         <v>6</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS15" t="n">
         <v>7</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>2.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
         <v>3.95</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q16" t="n">
         <v>1.9</v>
@@ -4455,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4467,16 +4467,16 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z16" t="n">
         <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB16" t="n">
         <v>14</v>
@@ -4485,7 +4485,7 @@
         <v>9.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
         <v>34</v>
@@ -4497,10 +4497,10 @@
         <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ16" t="n">
         <v>55</v>
@@ -4512,37 +4512,37 @@
         <v>50</v>
       </c>
       <c r="AM16" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR16" t="n">
         <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV16" t="n">
         <v>9.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="AX16" t="n">
         <v>15</v>
@@ -4554,25 +4554,25 @@
         <v>13</v>
       </c>
       <c r="BA16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC16" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF16" t="n">
         <v>21</v>
       </c>
       <c r="BG16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G17" t="n">
         <v>1.8</v>
@@ -4691,7 +4691,7 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.26</v>
@@ -4703,16 +4703,16 @@
         <v>1.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
         <v>2.92</v>
       </c>
       <c r="T17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V17" t="n">
         <v>1.22</v>
@@ -4721,10 +4721,10 @@
         <v>2.24</v>
       </c>
       <c r="X17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="n">
         <v>48</v>
@@ -4775,58 +4775,58 @@
         <v>75</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AR17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE17" t="n">
         <v>5.6</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>6</v>
       </c>
       <c r="BF17" t="n">
         <v>7.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH17" t="n">
         <v>3.9</v>
@@ -4835,7 +4835,7 @@
         <v>3.15</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK17" t="n">
         <v>6</v>
@@ -4844,7 +4844,7 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="BN17" t="n">
         <v>4.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="G20" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="I20" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>2.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H21" t="n">
         <v>3.9</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>
@@ -5940,19 +5940,19 @@
         <v>2.36</v>
       </c>
       <c r="G22" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H22" t="n">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 02:26:20</t>
+          <t>2026-07-09 04:36:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>1.93</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
         <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I6" t="n">
         <v>6.4</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J9" t="n">
         <v>4.1</v>
@@ -2668,7 +2668,7 @@
         <v>3.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H10" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I10" t="n">
         <v>3.25</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H11" t="n">
         <v>2.12</v>
@@ -3242,7 +3242,7 @@
         <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AN11" t="n">
         <v>32</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -3908,16 +3908,16 @@
         <v>2.12</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
         <v>4.4</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="U14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3962,55 +3962,55 @@
         <v>25</v>
       </c>
       <c r="Y14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z14" t="n">
         <v>27</v>
       </c>
       <c r="AA14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH14" t="n">
         <v>16</v>
       </c>
-      <c r="AC14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE14" t="n">
+      <c r="AI14" t="n">
         <v>38</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>42</v>
       </c>
       <c r="AJ14" t="n">
         <v>34</v>
       </c>
       <c r="AK14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM14" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN14" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP14" t="n">
         <v>1.03</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -4165,16 +4165,16 @@
         <v>1.4</v>
       </c>
       <c r="H15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>11</v>
       </c>
       <c r="J15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
         <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4201,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U15" t="n">
         <v>1.97</v>
@@ -4222,19 +4222,19 @@
         <v>110</v>
       </c>
       <c r="AA15" t="n">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="AB15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD15" t="n">
         <v>38</v>
       </c>
       <c r="AE15" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF15" t="n">
         <v>9.6</v>
@@ -4243,52 +4243,52 @@
         <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI15" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK15" t="n">
         <v>16.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM15" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN15" t="n">
         <v>5</v>
       </c>
       <c r="AO15" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP15" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AR15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS15" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7</v>
       </c>
       <c r="AT15" t="n">
         <v>9</v>
       </c>
       <c r="AU15" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX15" t="n">
         <v>8</v>
@@ -4297,28 +4297,28 @@
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>5.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB15" t="n">
         <v>9.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I16" t="n">
         <v>2.8</v>
@@ -4455,7 +4455,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
         <v>2.16</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.7</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H17" t="n">
         <v>4.9</v>
@@ -4712,19 +4712,19 @@
         <v>1.78</v>
       </c>
       <c r="U17" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V17" t="n">
         <v>1.22</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X17" t="n">
         <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z17" t="n">
         <v>48</v>
@@ -4742,7 +4742,7 @@
         <v>24</v>
       </c>
       <c r="AE17" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
         <v>13</v>
@@ -4763,7 +4763,7 @@
         <v>20</v>
       </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -4775,58 +4775,58 @@
         <v>75</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AS17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW17" t="n">
         <v>5.7</v>
       </c>
-      <c r="AT17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AX17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.95</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH17" t="n">
         <v>3.9</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -4930,10 +4930,10 @@
         <v>2.52</v>
       </c>
       <c r="I18" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
         <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -5686,13 +5686,13 @@
         <v>2.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H21" t="n">
         <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>3.25</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
         <v>1.47</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 04:36:03</t>
+          <t>2026-07-09 06:45:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>South Korean K2 League</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Daegu Fc</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.99</v>
+        <v>1.36</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>South Korean K2 League</t>
+          <t>South Korean K1 League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,246 +1102,246 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ansan Greeners FC</t>
+          <t>Gimcheon Sangmu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Bucheon FC 1995</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="X3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV3" t="n">
         <v>12.5</v>
       </c>
-      <c r="H3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="AW3" t="n">
         <v>4.7</v>
       </c>
-      <c r="K3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>South Korean K2 League</t>
+          <t>South Korean K1 League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,246 +1356,246 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Yongin FC</t>
+          <t>Ulsan Hyundai Horang-i</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju FC</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="H4" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N4" t="n">
         <v>3.7</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>South Korean K2 League</t>
+          <t>South Korean K1 League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hwaseong FC</t>
+          <t>Gwangju FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.93</v>
+        <v>6.8</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>7.6</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>1.64</v>
       </c>
       <c r="I5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>330</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>320</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX5" t="n">
         <v>5.3</v>
       </c>
-      <c r="J5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Zhejiang Greentown</t>
+          <t>Daegu Fc</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X6" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
         <v>6.4</v>
       </c>
-      <c r="J6" t="n">
+      <c r="AU6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU6" t="n">
         <v>4.9</v>
       </c>
-      <c r="K6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>0</v>
-      </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ansan Greeners FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Songshan Longmen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V7" t="n">
         <v>3.05</v>
       </c>
-      <c r="G7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,159 +2367,159 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>Yongin FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>Cheongju FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.07</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
         <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>1.03</v>
@@ -2528,7 +2528,7 @@
         <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD8" t="n">
         <v>1.03</v>
@@ -2537,81 +2537,81 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.64</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>2.92</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>3.05</v>
+        <v>1.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Shenzhen Peng City</t>
+          <t>Dalian Kun City FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.56</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Shaanxi Union FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>1.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T11" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chongqing Tonglianglong</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>1.39</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>1.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Zhejiang Greentown</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.88</v>
+        <v>1.53</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.58</v>
+        <v>5.8</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>1.78</v>
+        <v>2.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>2.36</v>
+        <v>3.35</v>
       </c>
       <c r="H14" t="n">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="I14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J14" t="n">
         <v>3.6</v>
       </c>
-      <c r="J14" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="U14" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AB14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC14" t="n">
         <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP14" t="n">
         <v>34</v>
       </c>
-      <c r="AF14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH14" t="n">
+      <c r="BQ14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>22</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
         <v>16</v>
       </c>
-      <c r="AI14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK14" t="n">
+      <c r="BZ14" t="n">
         <v>22</v>
       </c>
-      <c r="AL14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>0</v>
-      </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>5.6</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
         <v>1.03</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>370</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="H16" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P16" t="n">
-        <v>1.92</v>
+        <v>3.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW16" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB16" t="n">
         <v>27</v>
       </c>
-      <c r="AP16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC16" t="n">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.8</v>
+        <v>27</v>
       </c>
       <c r="BF16" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Shenzhen Peng City</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="G17" t="n">
-        <v>1.79</v>
+        <v>2.64</v>
       </c>
       <c r="H17" t="n">
-        <v>4.9</v>
+        <v>2.98</v>
       </c>
       <c r="I17" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>2.04</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="S17" t="n">
-        <v>2.92</v>
+        <v>1.82</v>
       </c>
       <c r="T17" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="W17" t="n">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,36 +4907,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Chongqing Tonglianglong</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>1.31</v>
       </c>
       <c r="G18" t="n">
-        <v>3.75</v>
+        <v>1.39</v>
       </c>
       <c r="H18" t="n">
-        <v>2.52</v>
+        <v>10.5</v>
       </c>
       <c r="I18" t="n">
-        <v>3.25</v>
+        <v>13</v>
       </c>
       <c r="J18" t="n">
-        <v>2.82</v>
+        <v>5.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.59</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.06</v>
+        <v>1.58</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,42 +5161,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="I19" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5217,10 +5217,10 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5229,112 +5229,112 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,54 +5415,54 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Torque</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="G20" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="H20" t="n">
-        <v>1.86</v>
+        <v>2.56</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,42 +5669,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="G21" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5725,10 +5725,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -5737,112 +5737,112 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH21" t="n">
         <v>0</v>
@@ -5906,261 +5906,2039 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 06:45:31</t>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IFK Mariehamn</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>11</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>370</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-07-09 08:56:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TPS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AC Oulu</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-07-09 08:56:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Galway Utd</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sligo Rovers</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X24" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-07-09 08:56:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-07-09 08:56:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-07-09 08:56:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-07-09 08:56:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Wanderers (Uru)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-07-09 08:56:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Guayaquil City</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Delfin</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F29" t="n">
         <v>2.36</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G29" t="n">
         <v>2.68</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H29" t="n">
         <v>3.4</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I29" t="n">
         <v>4.5</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J29" t="n">
         <v>2.82</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K29" t="n">
         <v>3.3</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q29" t="n">
         <v>2.72</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>2026-07-09 06:45:31</t>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-07-09 08:56:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.76</v>
       </c>
       <c r="G3" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="H3" t="n">
         <v>5.3</v>
@@ -1135,88 +1135,88 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.54</v>
+        <v>2.96</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
         <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB3" t="n">
         <v>8</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP3" t="n">
         <v>1.03</v>
@@ -1243,7 +1243,7 @@
         <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
         <v>1.03</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G4" t="n">
         <v>2.16</v>
@@ -1374,16 +1374,16 @@
         <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1410,7 +1410,7 @@
         <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V4" t="n">
         <v>1.29</v>
@@ -1500,7 +1500,7 @@
         <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
         <v>6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -1619,31 +1619,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G5" t="n">
         <v>2.84</v>
       </c>
       <c r="H5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I5" t="n">
         <v>2.92</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.34</v>
@@ -1658,7 +1658,7 @@
         <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T5" t="n">
         <v>1.78</v>
@@ -1727,7 +1727,7 @@
         <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>1.64</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
@@ -1900,7 +1900,7 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P6" t="n">
         <v>1.66</v>
@@ -1912,7 +1912,7 @@
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T6" t="n">
         <v>2.28</v>
@@ -1921,7 +1921,7 @@
         <v>1.7</v>
       </c>
       <c r="V6" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="W6" t="n">
         <v>1.15</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
         <v>29</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
         <v>48</v>
@@ -2232,7 +2232,7 @@
         <v>19.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="n">
         <v>9.800000000000001</v>
@@ -2250,7 +2250,7 @@
         <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
         <v>13</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
         <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -2495,7 +2495,7 @@
         <v>7.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AS8" t="n">
         <v>8.800000000000001</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2800,7 +2800,7 @@
         <v>3.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
         <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R10" t="n">
         <v>1.28</v>
@@ -2931,7 +2931,7 @@
         <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U10" t="n">
         <v>1.92</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -3182,13 +3182,13 @@
         <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V11" t="n">
         <v>1.71</v>
@@ -3221,7 +3221,7 @@
         <v>29</v>
       </c>
       <c r="AF11" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG11" t="n">
         <v>17</v>
@@ -3257,10 +3257,10 @@
         <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT11" t="n">
         <v>12.5</v>
@@ -3272,10 +3272,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
@@ -3284,19 +3284,19 @@
         <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC11" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC11" t="n">
-        <v>4</v>
-      </c>
       <c r="BD11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
         <v>4.8</v>
@@ -3415,7 +3415,7 @@
         <v>5.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
@@ -3427,37 +3427,37 @@
         <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q12" t="n">
         <v>1.46</v>
       </c>
       <c r="R12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S12" t="n">
         <v>2.14</v>
       </c>
       <c r="T12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="X12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Y12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA12" t="n">
         <v>150</v>
@@ -3469,52 +3469,52 @@
         <v>12.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AE12" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AF12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK12" t="n">
         <v>15</v>
       </c>
       <c r="AL12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AM12" t="n">
         <v>70</v>
       </c>
       <c r="AN12" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AT12" t="n">
         <v>12</v>
@@ -3523,10 +3523,10 @@
         <v>11</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -3538,25 +3538,25 @@
         <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC12" t="n">
         <v>12.5</v>
       </c>
       <c r="BD12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG12" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>10</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3577,16 +3577,16 @@
         <v>21</v>
       </c>
       <c r="BN12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO12" t="n">
         <v>3.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BR12" t="n">
         <v>26</v>
@@ -3598,7 +3598,7 @@
         <v>13.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3607,7 +3607,7 @@
         <v>21</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
         <v>21</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="H14" t="n">
-        <v>2.86</v>
+        <v>5.7</v>
       </c>
       <c r="I14" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,22 +3929,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3953,10 +3953,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W14" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -4195,10 +4195,10 @@
         <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>2.04</v>
+        <v>3.45</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -4416,19 +4416,19 @@
         <v>3.65</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H16" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="I16" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>3.2</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4440,34 +4440,34 @@
         <v>2.96</v>
       </c>
       <c r="O16" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P16" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R16" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="V16" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y16" t="n">
         <v>8.6</v>
@@ -4476,13 +4476,13 @@
         <v>15</v>
       </c>
       <c r="AA16" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AB16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
         <v>12.5</v>
@@ -4491,7 +4491,7 @@
         <v>28</v>
       </c>
       <c r="AF16" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG16" t="n">
         <v>18.5</v>
@@ -4503,7 +4503,7 @@
         <v>50</v>
       </c>
       <c r="AJ16" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK16" t="n">
         <v>60</v>
@@ -4518,7 +4518,7 @@
         <v>70</v>
       </c>
       <c r="AO16" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AP16" t="n">
         <v>1.03</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -4673,13 +4673,13 @@
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -5459,16 +5459,16 @@
         <v>1.02</v>
       </c>
       <c r="P20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.07</v>
       </c>
       <c r="S20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G25" t="n">
         <v>2.64</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G26" t="n">
         <v>3.25</v>
@@ -6986,7 +6986,7 @@
         <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R26" t="n">
         <v>1.41</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="H27" t="n">
-        <v>1.47</v>
+        <v>2.98</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="K27" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7234,31 +7234,31 @@
         <v>1.13</v>
       </c>
       <c r="O27" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="P27" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="R27" t="n">
         <v>1.07</v>
       </c>
       <c r="S27" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="U27" t="n">
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.73</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -7461,19 +7461,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="G28" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="H28" t="n">
         <v>10</v>
       </c>
       <c r="I28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J28" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K28" t="n">
         <v>6.2</v>
@@ -7485,58 +7485,58 @@
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
         <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q28" t="n">
         <v>1.65</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
         <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="V28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W28" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="X28" t="n">
         <v>23</v>
       </c>
       <c r="Y28" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Z28" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA28" t="n">
-        <v>510</v>
+        <v>440</v>
       </c>
       <c r="AB28" t="n">
         <v>9.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AE28" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AF28" t="n">
         <v>8.6</v>
@@ -7545,10 +7545,10 @@
         <v>12.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI28" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ28" t="n">
         <v>11.5</v>
@@ -7557,28 +7557,28 @@
         <v>17</v>
       </c>
       <c r="AL28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM28" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN28" t="n">
         <v>5.7</v>
       </c>
       <c r="AO28" t="n">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="AP28" t="n">
         <v>15</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>7.8</v>
@@ -7587,10 +7587,10 @@
         <v>11</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
@@ -7599,10 +7599,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB28" t="n">
         <v>9.4</v>
@@ -7611,16 +7611,16 @@
         <v>12.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7629,10 +7629,10 @@
         <v>1.01</v>
       </c>
       <c r="BJ28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BK28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7644,25 +7644,25 @@
         <v>5</v>
       </c>
       <c r="BO28" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BP28" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BT28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BU28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
         <v>4.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8005,7 @@
         <v>1.31</v>
       </c>
       <c r="R30" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S30" t="n">
         <v>1.31</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -8477,13 +8477,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G32" t="n">
         <v>2.04</v>
       </c>
       <c r="H32" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
         <v>4.1</v>
@@ -8492,7 +8492,7 @@
         <v>3.85</v>
       </c>
       <c r="K32" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -8510,16 +8510,16 @@
         <v>2.12</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
         <v>3.05</v>
       </c>
       <c r="T32" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U32" t="n">
         <v>2.2</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
         <v>11</v>
       </c>
       <c r="AP34" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ34" t="n">
         <v>13</v>
@@ -9102,10 +9102,10 @@
         <v>6.8</v>
       </c>
       <c r="AS34" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT34" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU34" t="n">
         <v>9</v>
@@ -9120,22 +9120,22 @@
         <v>7.8</v>
       </c>
       <c r="AY34" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ34" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA34" t="n">
         <v>7.8</v>
       </c>
       <c r="BB34" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC34" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BD34" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE34" t="n">
         <v>9.199999999999999</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         <v>2.1</v>
       </c>
       <c r="G36" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H36" t="n">
         <v>3.15</v>
@@ -9505,7 +9505,7 @@
         <v>3.55</v>
       </c>
       <c r="J36" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K36" t="n">
         <v>4.4</v>
@@ -9517,19 +9517,19 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>4.4</v>
+        <v>1.08</v>
       </c>
       <c r="O36" t="n">
         <v>1.19</v>
       </c>
       <c r="P36" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R36" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S36" t="n">
         <v>2.36</v>
@@ -9538,13 +9538,13 @@
         <v>1.56</v>
       </c>
       <c r="U36" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V36" t="n">
         <v>1.39</v>
       </c>
       <c r="W36" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X36" t="n">
         <v>24</v>
@@ -9583,7 +9583,7 @@
         <v>38</v>
       </c>
       <c r="AJ36" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK36" t="n">
         <v>22</v>
@@ -9592,67 +9592,67 @@
         <v>30</v>
       </c>
       <c r="AM36" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN36" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO36" t="n">
         <v>24</v>
       </c>
       <c r="AP36" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX36" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AY36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG36" t="n">
         <v>7</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>6.6</v>
       </c>
       <c r="BH36" t="n">
         <v>5.6</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9819,7 @@
         <v>16</v>
       </c>
       <c r="AD37" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE37" t="n">
         <v>160</v>
@@ -9843,28 +9843,28 @@
         <v>16.5</v>
       </c>
       <c r="AL37" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM37" t="n">
         <v>150</v>
       </c>
       <c r="AN37" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AO37" t="n">
         <v>180</v>
       </c>
       <c r="AP37" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="AQ37" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AR37" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AT37" t="n">
         <v>9</v>
@@ -9873,10 +9873,10 @@
         <v>11.5</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AX37" t="n">
         <v>8</v>
@@ -9885,10 +9885,10 @@
         <v>9</v>
       </c>
       <c r="AZ37" t="n">
-        <v>4.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB37" t="n">
         <v>9.6</v>
@@ -9897,16 +9897,16 @@
         <v>12</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF37" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BH37" t="n">
         <v>4.7</v>
@@ -9930,7 +9930,7 @@
         <v>4.2</v>
       </c>
       <c r="BO37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BP37" t="n">
         <v>8.199999999999999</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
         <v>2.78</v>
       </c>
       <c r="G38" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H38" t="n">
         <v>2.52</v>
@@ -10025,10 +10025,10 @@
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O38" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P38" t="n">
         <v>1.92</v>
@@ -10037,13 +10037,13 @@
         <v>1.9</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T38" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U38" t="n">
         <v>2.12</v>
@@ -10052,7 +10052,7 @@
         <v>1.57</v>
       </c>
       <c r="W38" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X38" t="n">
         <v>17.5</v>
@@ -10112,7 +10112,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR38" t="n">
         <v>13.5</v>
@@ -10133,7 +10133,7 @@
         <v>21</v>
       </c>
       <c r="AX38" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AY38" t="n">
         <v>10</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10303,10 +10303,10 @@
         <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -10512,10 +10512,10 @@
         <v>5.9</v>
       </c>
       <c r="G40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H40" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I40" t="n">
         <v>1.6</v>
@@ -10524,10 +10524,10 @@
         <v>4.8</v>
       </c>
       <c r="K40" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L40" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M40" t="n">
         <v>1.03</v>
@@ -10542,13 +10542,13 @@
         <v>2.74</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R40" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S40" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T40" t="n">
         <v>1.65</v>
@@ -10566,10 +10566,10 @@
         <v>36</v>
       </c>
       <c r="Y40" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA40" t="n">
         <v>19.5</v>
@@ -10578,7 +10578,7 @@
         <v>38</v>
       </c>
       <c r="AC40" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD40" t="n">
         <v>12.5</v>
@@ -10593,7 +10593,7 @@
         <v>24</v>
       </c>
       <c r="AH40" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI40" t="n">
         <v>32</v>
@@ -10617,7 +10617,7 @@
         <v>5.8</v>
       </c>
       <c r="AP40" t="n">
-        <v>4.8</v>
+        <v>21</v>
       </c>
       <c r="AQ40" t="n">
         <v>11</v>
@@ -10629,7 +10629,7 @@
         <v>14</v>
       </c>
       <c r="AT40" t="n">
-        <v>4.9</v>
+        <v>22</v>
       </c>
       <c r="AU40" t="n">
         <v>10.5</v>
@@ -10641,43 +10641,43 @@
         <v>13</v>
       </c>
       <c r="AX40" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AY40" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AZ40" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="BB40" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BC40" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BD40" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BF40" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG40" t="n">
         <v>5.3</v>
       </c>
       <c r="BH40" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI40" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ40" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK40" t="n">
         <v>5.8</v>
@@ -10689,50 +10689,50 @@
         <v>21</v>
       </c>
       <c r="BN40" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BO40" t="n">
         <v>5.9</v>
       </c>
       <c r="BP40" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ40" t="n">
         <v>21</v>
       </c>
       <c r="BR40" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS40" t="n">
         <v>21</v>
       </c>
       <c r="BT40" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BU40" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="BV40" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BW40" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BX40" t="n">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="BY40" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ40" t="n">
         <v>12</v>
       </c>
-      <c r="BZ40" t="n">
-        <v>17.5</v>
-      </c>
       <c r="CA40" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
         <v>4.4</v>
       </c>
       <c r="L41" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M41" t="n">
         <v>1.05</v>
@@ -10934,7 +10934,7 @@
         <v>9.6</v>
       </c>
       <c r="BK41" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
@@ -10946,13 +10946,13 @@
         <v>4.5</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP41" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ41" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR41" t="n">
         <v>1000</v>
@@ -10964,7 +10964,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU41" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
         <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K42" t="n">
         <v>1000</v>
@@ -11041,13 +11041,13 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="O42" t="n">
         <v>1.21</v>
       </c>
       <c r="P42" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Q42" t="n">
         <v>1.21</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G43" t="n">
         <v>1.86</v>
@@ -11289,7 +11289,7 @@
         <v>4.3</v>
       </c>
       <c r="L43" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M43" t="n">
         <v>1.05</v>
@@ -11301,22 +11301,22 @@
         <v>1.27</v>
       </c>
       <c r="P43" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R43" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S43" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T43" t="n">
         <v>1.75</v>
       </c>
       <c r="U43" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V43" t="n">
         <v>1.24</v>
@@ -11337,13 +11337,13 @@
         <v>130</v>
       </c>
       <c r="AB43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC43" t="n">
         <v>11</v>
       </c>
       <c r="AD43" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE43" t="n">
         <v>75</v>
@@ -11355,7 +11355,7 @@
         <v>12.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI43" t="n">
         <v>75</v>
@@ -11364,7 +11364,7 @@
         <v>24</v>
       </c>
       <c r="AK43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL43" t="n">
         <v>40</v>
@@ -11385,13 +11385,13 @@
         <v>16.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT43" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU43" t="n">
         <v>8.199999999999999</v>
@@ -11400,7 +11400,7 @@
         <v>14</v>
       </c>
       <c r="AW43" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AX43" t="n">
         <v>10.5</v>
@@ -11412,7 +11412,7 @@
         <v>16</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BB43" t="n">
         <v>17</v>
@@ -11421,16 +11421,16 @@
         <v>16</v>
       </c>
       <c r="BD43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE43" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>4.3</v>
       </c>
       <c r="BF43" t="n">
         <v>7.6</v>
       </c>
       <c r="BG43" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -11525,13 +11525,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="G44" t="n">
         <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
@@ -11552,10 +11552,10 @@
         <v>1.07</v>
       </c>
       <c r="O44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P44" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q44" t="n">
         <v>1.4</v>
@@ -11564,7 +11564,7 @@
         <v>1.05</v>
       </c>
       <c r="S44" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="G45" t="n">
         <v>3.75</v>
@@ -11788,221 +11788,221 @@
         <v>2.52</v>
       </c>
       <c r="I45" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="J45" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="K45" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P45" t="n">
         <v>1.64</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BG45" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BH45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK45" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BL45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN45" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BO45" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BP45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BR45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT45" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU45" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BV45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BX45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA45" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
         <v>4.1</v>
       </c>
       <c r="G46" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="H46" t="n">
         <v>1.91</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="I48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q49" t="n">
         <v>2.2</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>
@@ -13079,10 +13079,10 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-09 13:41:30</t>
+          <t>2026-07-09 16:21:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
         <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
         <v>2.28</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -1380,10 +1380,10 @@
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>2.92</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
@@ -1664,7 +1664,7 @@
         <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
         <v>1.52</v>
@@ -1691,7 +1691,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>40</v>
@@ -1748,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1766,7 +1766,7 @@
         <v>5.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD5" t="n">
         <v>5.3</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
         <v>3.45</v>
@@ -2148,31 +2148,31 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
         <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
         <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
         <v>1.26</v>
@@ -2181,7 +2181,7 @@
         <v>1.9</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" t="n">
         <v>18</v>
@@ -2229,7 +2229,7 @@
         <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO7" t="n">
         <v>85</v>
@@ -2289,7 +2289,7 @@
         <v>48</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI7" t="n">
         <v>2.7</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -2387,10 +2387,10 @@
         <v>11</v>
       </c>
       <c r="H8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="J8" t="n">
         <v>4.8</v>
@@ -2405,7 +2405,7 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.25</v>
@@ -2420,16 +2420,16 @@
         <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
@@ -2444,10 +2444,10 @@
         <v>10.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AB8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AC8" t="n">
         <v>14</v>
@@ -2474,16 +2474,16 @@
         <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AL8" t="n">
         <v>160</v>
       </c>
       <c r="AM8" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AO8" t="n">
         <v>8</v>
@@ -2495,7 +2495,7 @@
         <v>7.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS8" t="n">
         <v>8.800000000000001</v>
@@ -2510,13 +2510,13 @@
         <v>7.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX8" t="n">
         <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
         <v>16.5</v>
@@ -2537,19 +2537,19 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH8" t="n">
         <v>3.95</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK8" t="n">
         <v>8.6</v>
@@ -2564,7 +2564,7 @@
         <v>13</v>
       </c>
       <c r="BO8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
@@ -2579,13 +2579,13 @@
         <v>21</v>
       </c>
       <c r="BT8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BU8" t="n">
         <v>3</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BW8" t="n">
         <v>6.2</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2800,7 +2800,7 @@
         <v>3.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H10" t="n">
         <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
@@ -2931,7 +2931,7 @@
         <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
         <v>1.92</v>
@@ -2940,7 +2940,7 @@
         <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X10" t="n">
         <v>13.5</v>
@@ -2970,7 +2970,7 @@
         <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
         <v>28</v>
@@ -2991,7 +2991,7 @@
         <v>160</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AO10" t="n">
         <v>100</v>
@@ -3057,7 +3057,7 @@
         <v>2.82</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK10" t="n">
         <v>8</v>
@@ -3087,7 +3087,7 @@
         <v>24</v>
       </c>
       <c r="BT10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU10" t="n">
         <v>6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>3.45</v>
       </c>
       <c r="H11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I11" t="n">
         <v>2.4</v>
@@ -3158,7 +3158,7 @@
         <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
         <v>1.34</v>
@@ -3182,7 +3182,7 @@
         <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T11" t="n">
         <v>1.64</v>
@@ -3200,7 +3200,7 @@
         <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
         <v>20</v>
@@ -3260,7 +3260,7 @@
         <v>3.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT11" t="n">
         <v>12.5</v>
@@ -3275,7 +3275,7 @@
         <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
@@ -3287,7 +3287,7 @@
         <v>4.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC11" t="n">
         <v>4.2</v>
@@ -3296,7 +3296,7 @@
         <v>4.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -3397,166 +3397,166 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="G12" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="H12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K12" t="n">
         <v>6</v>
       </c>
-      <c r="I12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.4</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P12" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="S12" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="T12" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W12" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="X12" t="n">
         <v>38</v>
       </c>
       <c r="Y12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AA12" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AB12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC12" t="n">
         <v>14</v>
       </c>
-      <c r="AC12" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AD12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AE12" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF12" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AL12" t="n">
         <v>30</v>
       </c>
       <c r="AM12" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AN12" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="AO12" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AT12" t="n">
         <v>12</v>
       </c>
       <c r="AU12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV12" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>8.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD12" t="n">
         <v>21</v>
       </c>
       <c r="BE12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3565,10 +3565,10 @@
         <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,25 +3580,25 @@
         <v>6</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP12" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3613,14 +3613,14 @@
         <v>21</v>
       </c>
       <c r="BZ12" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA12" t="n">
         <v>7.2</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -4195,10 +4195,10 @@
         <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="S15" t="n">
-        <v>3.45</v>
+        <v>2.04</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="H16" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J16" t="n">
         <v>3.2</v>
@@ -4437,13 +4437,13 @@
         <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
         <v>2.22</v>
@@ -4461,10 +4461,10 @@
         <v>1.94</v>
       </c>
       <c r="V16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W16" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="X16" t="n">
         <v>12.5</v>
@@ -4476,7 +4476,7 @@
         <v>15</v>
       </c>
       <c r="AA16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB16" t="n">
         <v>14</v>
@@ -4518,7 +4518,7 @@
         <v>70</v>
       </c>
       <c r="AO16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP16" t="n">
         <v>1.03</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -5432,19 +5432,19 @@
         <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
         <v>1.04</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
         <v>1.41</v>
       </c>
       <c r="U24" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V24" t="n">
         <v>1.52</v>
@@ -6598,10 +6598,10 @@
         <v>6.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG24" t="n">
         <v>9</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
         <v>3.85</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -6977,10 +6977,10 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P26" t="n">
         <v>2.04</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="G27" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H27" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7237,7 +7237,7 @@
         <v>1.41</v>
       </c>
       <c r="P27" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q27" t="n">
         <v>1.41</v>
@@ -7258,7 +7258,7 @@
         <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
         <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
         <v>1.82</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
         <v>3.6</v>
       </c>
       <c r="H29" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I29" t="n">
         <v>2.32</v>
@@ -7733,7 +7733,7 @@
         <v>4.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
@@ -7754,7 +7754,7 @@
         <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T29" t="n">
         <v>1.61</v>
@@ -7778,7 +7778,7 @@
         <v>17</v>
       </c>
       <c r="AA29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB29" t="n">
         <v>19</v>
@@ -7847,7 +7847,7 @@
         <v>18</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY29" t="n">
         <v>12</v>
@@ -7859,16 +7859,16 @@
         <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC29" t="n">
         <v>5.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF29" t="n">
         <v>20</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
         <v>2.02</v>
       </c>
       <c r="G32" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H32" t="n">
         <v>4</v>
@@ -8489,13 +8489,13 @@
         <v>4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K32" t="n">
         <v>3.95</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
@@ -8507,7 +8507,7 @@
         <v>1.28</v>
       </c>
       <c r="P32" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q32" t="n">
         <v>1.83</v>
@@ -8519,7 +8519,7 @@
         <v>3.05</v>
       </c>
       <c r="T32" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U32" t="n">
         <v>2.2</v>
@@ -8528,7 +8528,7 @@
         <v>1.32</v>
       </c>
       <c r="W32" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X32" t="n">
         <v>21</v>
@@ -8540,7 +8540,7 @@
         <v>38</v>
       </c>
       <c r="AA32" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB32" t="n">
         <v>12.5</v>
@@ -8561,7 +8561,7 @@
         <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI32" t="n">
         <v>65</v>
@@ -8585,19 +8585,19 @@
         <v>46</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ32" t="n">
         <v>14</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT32" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU32" t="n">
         <v>7.8</v>
@@ -8606,7 +8606,7 @@
         <v>12</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX32" t="n">
         <v>11</v>
@@ -8618,7 +8618,7 @@
         <v>14.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB32" t="n">
         <v>20</v>
@@ -8627,16 +8627,16 @@
         <v>17</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF32" t="n">
         <v>11</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
         <v>2.16</v>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J34" t="n">
         <v>4</v>
@@ -9033,7 +9033,7 @@
         <v>2.6</v>
       </c>
       <c r="V34" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W34" t="n">
         <v>1.41</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9505,7 @@
         <v>3.55</v>
       </c>
       <c r="J36" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K36" t="n">
         <v>4.4</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -9930,7 +9930,7 @@
         <v>4.2</v>
       </c>
       <c r="BO37" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BP37" t="n">
         <v>8.199999999999999</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G38" t="n">
         <v>3.05</v>
@@ -10019,7 +10019,7 @@
         <v>3.95</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
@@ -10040,19 +10040,19 @@
         <v>1.35</v>
       </c>
       <c r="S38" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T38" t="n">
         <v>1.72</v>
       </c>
       <c r="U38" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V38" t="n">
         <v>1.57</v>
       </c>
       <c r="W38" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
         <v>17.5</v>
@@ -10112,7 +10112,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR38" t="n">
         <v>13.5</v>
@@ -10127,13 +10127,13 @@
         <v>6.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW38" t="n">
         <v>21</v>
       </c>
       <c r="AX38" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AY38" t="n">
         <v>10</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -10518,13 +10518,13 @@
         <v>1.56</v>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="J40" t="n">
         <v>4.8</v>
       </c>
       <c r="K40" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L40" t="n">
         <v>1.27</v>
@@ -10557,7 +10557,7 @@
         <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="W40" t="n">
         <v>1.19</v>
@@ -10614,13 +10614,13 @@
         <v>65</v>
       </c>
       <c r="AO40" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AP40" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR40" t="n">
         <v>11</v>
@@ -10629,7 +10629,7 @@
         <v>14</v>
       </c>
       <c r="AT40" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AU40" t="n">
         <v>10.5</v>
@@ -10641,28 +10641,28 @@
         <v>13</v>
       </c>
       <c r="AX40" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY40" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AZ40" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA40" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="BB40" t="n">
         <v>6.4</v>
       </c>
       <c r="BC40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD40" t="n">
         <v>6.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF40" t="n">
         <v>6.2</v>
@@ -10716,7 +10716,7 @@
         <v>9.6</v>
       </c>
       <c r="BW40" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX40" t="n">
         <v>19.5</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
         <v>13.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH41" t="n">
         <v>22</v>
@@ -10871,28 +10871,28 @@
         <v>65</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR41" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS41" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AU41" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX41" t="n">
         <v>9</v>
@@ -10904,25 +10904,25 @@
         <v>14.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC41" t="n">
         <v>13.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF41" t="n">
         <v>7.2</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH41" t="n">
         <v>3.9</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
         <v>14.5</v>
       </c>
       <c r="AG43" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH43" t="n">
         <v>22</v>
@@ -11385,7 +11385,7 @@
         <v>16.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS43" t="n">
         <v>4.2</v>
@@ -11421,10 +11421,10 @@
         <v>16</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF43" t="n">
         <v>7.6</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -11525,19 +11525,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="G44" t="n">
         <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K44" t="n">
         <v>1000</v>
@@ -11561,10 +11561,10 @@
         <v>1.4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="S44" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
         <v>3.7</v>
       </c>
       <c r="T45" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U45" t="n">
         <v>1.01</v>
@@ -11845,7 +11845,7 @@
         <v>65</v>
       </c>
       <c r="AB45" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC45" t="n">
         <v>10.5</v>
@@ -11887,58 +11887,58 @@
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AQ45" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AS45" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AT45" t="n">
         <v>2.14</v>
       </c>
       <c r="AU45" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AV45" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AW45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BB45" t="n">
         <v>2.44</v>
       </c>
-      <c r="AX45" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB45" t="n">
+      <c r="BC45" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BE45" t="n">
         <v>2.5</v>
       </c>
-      <c r="BC45" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BD45" t="n">
+      <c r="BF45" t="n">
         <v>2.5</v>
       </c>
-      <c r="BE45" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BG45" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="BH45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -12305,212 +12305,212 @@
         <v>3.95</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P47" t="n">
         <v>1.85</v>
       </c>
       <c r="Q47" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V47" t="n">
         <v>2</v>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BG47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BH47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK47" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN47" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BO47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BP47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ47" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS47" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT47" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BU47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BV47" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BW47" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BX47" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BY47" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BZ47" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CA47" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="I48" t="n">
         <v>1000</v>
@@ -12565,13 +12565,13 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O48" t="n">
         <v>1.02</v>
       </c>
       <c r="P48" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Q48" t="n">
         <v>1.3</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
         <v>2.02</v>
       </c>
       <c r="G49" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H49" t="n">
         <v>3.9</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-09 16:21:50</t>
+          <t>2026-07-09 18:35:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -905,7 +905,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>1.76</v>
       </c>
       <c r="G3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I3" t="n">
         <v>7.4</v>
@@ -1126,7 +1126,7 @@
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1159,10 +1159,10 @@
         <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X3" t="n">
         <v>13.5</v>
@@ -1267,7 +1267,7 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G4" t="n">
         <v>2.16</v>
@@ -1383,7 +1383,7 @@
         <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1404,19 +1404,19 @@
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V4" t="n">
         <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
@@ -1431,7 +1431,7 @@
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
         <v>7.8</v>
@@ -1479,10 +1479,10 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
         <v>7.2</v>
@@ -1491,40 +1491,40 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4" t="n">
         <v>17</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="n">
         <v>3.15</v>
@@ -1545,7 +1545,7 @@
         <v>21</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO4" t="n">
         <v>3.6</v>
@@ -1566,29 +1566,29 @@
         <v>7.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BZ4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
         <v>23</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H5" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -1652,34 +1652,34 @@
         <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
         <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
         <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA5" t="n">
         <v>55</v>
@@ -1694,7 +1694,7 @@
         <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF5" t="n">
         <v>23</v>
@@ -1712,22 +1712,22 @@
         <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
         <v>34</v>
       </c>
       <c r="AO5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AP5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1748,31 +1748,31 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
         <v>19.5</v>
@@ -1787,7 +1787,7 @@
         <v>2.96</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK5" t="n">
         <v>7</v>
@@ -1835,14 +1835,14 @@
         <v>24</v>
       </c>
       <c r="BZ5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA5" t="n">
         <v>20</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>6.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H6" t="n">
         <v>1.64</v>
       </c>
       <c r="I6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
         <v>1.5</v>
@@ -1897,16 +1897,16 @@
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
@@ -1921,7 +1921,7 @@
         <v>1.7</v>
       </c>
       <c r="V6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="W6" t="n">
         <v>1.15</v>
@@ -1933,7 +1933,7 @@
         <v>6.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AA6" t="n">
         <v>20</v>
@@ -1978,13 +1978,13 @@
         <v>320</v>
       </c>
       <c r="AO6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR6" t="n">
         <v>7.6</v>
@@ -1996,49 +1996,49 @@
         <v>15</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW6" t="n">
         <v>19</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BG6" t="n">
         <v>12.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
@@ -2074,13 +2074,13 @@
         <v>3.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="BV6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>1.92</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -2160,7 +2160,7 @@
         <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
         <v>1.31</v>
@@ -2172,13 +2172,13 @@
         <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
         <v>1.26</v>
       </c>
       <c r="W7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X7" t="n">
         <v>16.5</v>
@@ -2250,7 +2250,7 @@
         <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
         <v>13</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="J8" t="n">
         <v>4.8</v>
@@ -2414,22 +2414,22 @@
         <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R8" t="n">
         <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
@@ -2549,7 +2549,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
         <v>8.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H9" t="n">
         <v>3.15</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J9" t="n">
         <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.37</v>
@@ -2665,10 +2665,10 @@
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
         <v>1.29</v>
@@ -2683,10 +2683,10 @@
         <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X9" t="n">
         <v>15</v>
@@ -2851,14 +2851,14 @@
         <v>29</v>
       </c>
       <c r="BZ9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
         <v>22</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         <v>1.39</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
         <v>2.14</v>
@@ -2934,7 +2934,7 @@
         <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V10" t="n">
         <v>1.25</v>
@@ -3051,13 +3051,13 @@
         <v>65</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK10" t="n">
         <v>8</v>
@@ -3087,7 +3087,7 @@
         <v>24</v>
       </c>
       <c r="BT10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU10" t="n">
         <v>6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I11" t="n">
         <v>2.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.34</v>
@@ -3170,40 +3170,40 @@
         <v>4.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U11" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V11" t="n">
         <v>1.71</v>
       </c>
       <c r="W11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y11" t="n">
         <v>14.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AA11" t="n">
         <v>38</v>
@@ -3212,10 +3212,10 @@
         <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AE11" t="n">
         <v>29</v>
@@ -3224,10 +3224,10 @@
         <v>26</v>
       </c>
       <c r="AG11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AI11" t="n">
         <v>40</v>
@@ -3248,61 +3248,61 @@
         <v>34</v>
       </c>
       <c r="AO11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AP11" t="n">
-        <v>15</v>
+        <v>5.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.8</v>
+        <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU11" t="n">
         <v>7.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BH11" t="n">
         <v>3.95</v>
@@ -3326,7 +3326,7 @@
         <v>6.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
@@ -3350,7 +3350,7 @@
         <v>17</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -3397,97 +3397,97 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="G12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="H12" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="R12" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="S12" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="T12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="X12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Y12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z12" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA12" t="n">
         <v>200</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF12" t="n">
         <v>14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
         <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK12" t="n">
         <v>13.5</v>
@@ -3496,67 +3496,67 @@
         <v>30</v>
       </c>
       <c r="AM12" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AP12" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="AS12" t="n">
-        <v>13.5</v>
+        <v>46</v>
       </c>
       <c r="AT12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU12" t="n">
         <v>12</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AW12" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="BA12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC12" t="n">
         <v>12</v>
       </c>
-      <c r="BB12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BD12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE12" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3565,10 +3565,10 @@
         <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3583,22 +3583,22 @@
         <v>3.45</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BU12" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3616,11 +3616,11 @@
         <v>13.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -3678,19 +3678,19 @@
         <v>1.09</v>
       </c>
       <c r="O13" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
         <v>1.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="R13" t="n">
         <v>1.07</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>5.7</v>
       </c>
       <c r="I14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -3929,7 +3929,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
@@ -3953,7 +3953,7 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W14" t="n">
         <v>2.48</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
         <v>1.35</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="H16" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="I16" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
         <v>3.5</v>
@@ -4461,10 +4461,10 @@
         <v>1.94</v>
       </c>
       <c r="V16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W16" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="X16" t="n">
         <v>12.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -4670,10 +4670,10 @@
         <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>1.44</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
@@ -4691,7 +4691,7 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
         <v>1.23</v>
@@ -4703,10 +4703,10 @@
         <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8</v>
+        <v>2.68</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -4718,7 +4718,7 @@
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5199,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O19" t="n">
         <v>1.02</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
         <v>1.08</v>
       </c>
       <c r="O20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="P20" t="n">
         <v>1.08</v>
@@ -5480,7 +5480,7 @@
         <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
         <v>1.09</v>
       </c>
       <c r="O21" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="P21" t="n">
         <v>1.09</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
         <v>1.07</v>
       </c>
       <c r="S22" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>2.34</v>
       </c>
       <c r="G24" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H24" t="n">
         <v>2.62</v>
@@ -6460,7 +6460,7 @@
         <v>4.1</v>
       </c>
       <c r="K24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L24" t="n">
         <v>1.2</v>
@@ -6475,7 +6475,7 @@
         <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q24" t="n">
         <v>1.4</v>
@@ -6484,7 +6484,7 @@
         <v>1.82</v>
       </c>
       <c r="S24" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="T24" t="n">
         <v>1.41</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -6729,10 +6729,10 @@
         <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R25" t="n">
         <v>1.39</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
         <v>2.28</v>
       </c>
       <c r="V26" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W26" t="n">
         <v>1.45</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.1</v>
+        <v>2.06</v>
       </c>
       <c r="G27" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H27" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J27" t="n">
-        <v>1.84</v>
+        <v>2.58</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7249,16 +7249,16 @@
         <v>1.41</v>
       </c>
       <c r="T27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="U27" t="n">
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="W27" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="G28" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H28" t="n">
         <v>10</v>
       </c>
       <c r="I28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K28" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -7512,7 +7512,7 @@
         <v>1.09</v>
       </c>
       <c r="W28" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="X28" t="n">
         <v>23</v>
@@ -7521,10 +7521,10 @@
         <v>38</v>
       </c>
       <c r="Z28" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA28" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AB28" t="n">
         <v>9.4</v>
@@ -7548,7 +7548,7 @@
         <v>34</v>
       </c>
       <c r="AI28" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ28" t="n">
         <v>11.5</v>
@@ -7566,7 +7566,7 @@
         <v>5.7</v>
       </c>
       <c r="AO28" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP28" t="n">
         <v>15</v>
@@ -7587,7 +7587,7 @@
         <v>11</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW28" t="n">
         <v>7.8</v>
@@ -7599,10 +7599,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB28" t="n">
         <v>9.4</v>
@@ -7620,7 +7620,7 @@
         <v>4.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
         <v>4.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8005,7 @@
         <v>1.31</v>
       </c>
       <c r="R30" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="S30" t="n">
         <v>1.31</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
         <v>1.09</v>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -8483,16 +8483,16 @@
         <v>2.06</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I32" t="n">
         <v>4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K32" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L32" t="n">
         <v>1.12</v>
@@ -8507,7 +8507,7 @@
         <v>1.28</v>
       </c>
       <c r="P32" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
         <v>1.83</v>
@@ -8519,10 +8519,10 @@
         <v>3.05</v>
       </c>
       <c r="T32" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U32" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V32" t="n">
         <v>1.32</v>
@@ -8534,10 +8534,10 @@
         <v>21</v>
       </c>
       <c r="Y32" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA32" t="n">
         <v>95</v>
@@ -8585,16 +8585,16 @@
         <v>46</v>
       </c>
       <c r="AP32" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AQ32" t="n">
         <v>14</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS32" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT32" t="n">
         <v>9.199999999999999</v>
@@ -8606,7 +8606,7 @@
         <v>12</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX32" t="n">
         <v>11</v>
@@ -8618,7 +8618,7 @@
         <v>14.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB32" t="n">
         <v>20</v>
@@ -8627,16 +8627,16 @@
         <v>17</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF32" t="n">
         <v>11</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
         <v>3.2</v>
       </c>
       <c r="K33" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
         <v>1.64</v>
       </c>
       <c r="S34" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T34" t="n">
         <v>1.54</v>
@@ -9042,10 +9042,10 @@
         <v>26</v>
       </c>
       <c r="Y34" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z34" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA34" t="n">
         <v>28</v>
@@ -9090,22 +9090,22 @@
         <v>24</v>
       </c>
       <c r="AO34" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="AP34" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ34" t="n">
         <v>13</v>
       </c>
       <c r="AR34" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS34" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT34" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AU34" t="n">
         <v>9</v>
@@ -9114,31 +9114,31 @@
         <v>10</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX34" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA34" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB34" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BC34" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD34" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE34" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF34" t="n">
         <v>14.5</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -9239,22 +9239,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="G35" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="H35" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J35" t="n">
         <v>3.2</v>
       </c>
       <c r="K35" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L35" t="n">
         <v>1.47</v>
@@ -9263,7 +9263,7 @@
         <v>1.11</v>
       </c>
       <c r="N35" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O35" t="n">
         <v>1.5</v>
@@ -9272,7 +9272,7 @@
         <v>1.57</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R35" t="n">
         <v>1.21</v>
@@ -9281,16 +9281,16 @@
         <v>5.5</v>
       </c>
       <c r="T35" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U35" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V35" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W35" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X35" t="n">
         <v>10</v>
@@ -9299,31 +9299,31 @@
         <v>17.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA35" t="n">
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC35" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AG35" t="n">
         <v>11.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI35" t="n">
         <v>1000</v>
@@ -9410,7 +9410,7 @@
         <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
@@ -9422,13 +9422,13 @@
         <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP35" t="n">
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
@@ -9440,7 +9440,7 @@
         <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
@@ -9458,11 +9458,11 @@
         <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G37" t="n">
         <v>1.39</v>
@@ -9816,7 +9816,7 @@
         <v>12.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD37" t="n">
         <v>38</v>
@@ -9846,7 +9846,7 @@
         <v>34</v>
       </c>
       <c r="AM37" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN37" t="n">
         <v>5</v>
@@ -9858,13 +9858,13 @@
         <v>20</v>
       </c>
       <c r="AQ37" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR37" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT37" t="n">
         <v>9</v>
@@ -9873,7 +9873,7 @@
         <v>11.5</v>
       </c>
       <c r="AV37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW37" t="n">
         <v>6</v>
@@ -9897,7 +9897,7 @@
         <v>12</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE37" t="n">
         <v>6</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -10001,13 +10001,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="G38" t="n">
         <v>3.05</v>
       </c>
       <c r="H38" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I38" t="n">
         <v>2.76</v>
@@ -10016,7 +10016,7 @@
         <v>3.45</v>
       </c>
       <c r="K38" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L38" t="n">
         <v>1.14</v>
@@ -10025,10 +10025,10 @@
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O38" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P38" t="n">
         <v>1.92</v>
@@ -10049,16 +10049,16 @@
         <v>2.14</v>
       </c>
       <c r="V38" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W38" t="n">
         <v>1.5</v>
       </c>
       <c r="X38" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y38" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z38" t="n">
         <v>21</v>
@@ -10070,7 +10070,7 @@
         <v>14</v>
       </c>
       <c r="AC38" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD38" t="n">
         <v>14</v>
@@ -10112,13 +10112,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR38" t="n">
         <v>13.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT38" t="n">
         <v>9.4</v>
@@ -10127,13 +10127,13 @@
         <v>6.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AW38" t="n">
         <v>21</v>
       </c>
       <c r="AX38" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AY38" t="n">
         <v>10</v>
@@ -10142,19 +10142,19 @@
         <v>13</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF38" t="n">
         <v>21</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -10255,19 +10255,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G39" t="n">
         <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I39" t="n">
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -10509,22 +10509,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
         <v>6.4</v>
       </c>
       <c r="H40" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I40" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J40" t="n">
         <v>4.8</v>
       </c>
       <c r="K40" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L40" t="n">
         <v>1.27</v>
@@ -10557,10 +10557,10 @@
         <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="W40" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
         <v>36</v>
@@ -10614,7 +10614,7 @@
         <v>65</v>
       </c>
       <c r="AO40" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AP40" t="n">
         <v>6.2</v>
@@ -10623,7 +10623,7 @@
         <v>11.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS40" t="n">
         <v>14</v>
@@ -10644,31 +10644,31 @@
         <v>6.2</v>
       </c>
       <c r="AY40" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AZ40" t="n">
         <v>16</v>
       </c>
       <c r="BA40" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="BB40" t="n">
         <v>6.4</v>
       </c>
       <c r="BC40" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD40" t="n">
         <v>6.2</v>
       </c>
       <c r="BE40" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF40" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF40" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG40" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH40" t="n">
         <v>4.7</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G41" t="n">
         <v>1.8</v>
@@ -10778,10 +10778,10 @@
         <v>4.1</v>
       </c>
       <c r="K41" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L41" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="M41" t="n">
         <v>1.05</v>
@@ -10796,7 +10796,7 @@
         <v>2.18</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R41" t="n">
         <v>1.46</v>
@@ -10871,58 +10871,58 @@
         <v>65</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AQ41" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AR41" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="AU41" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV41" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AW41" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX41" t="n">
         <v>9</v>
       </c>
       <c r="AY41" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ41" t="n">
         <v>14.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BC41" t="n">
         <v>13.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF41" t="n">
         <v>7.2</v>
       </c>
       <c r="BG41" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BH41" t="n">
         <v>3.9</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -11017,13 +11017,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="G42" t="n">
         <v>1000</v>
       </c>
       <c r="H42" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="I42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G43" t="n">
         <v>1.86</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -11525,13 +11525,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="G44" t="n">
         <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
         <v>2.9</v>
       </c>
       <c r="G45" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H45" t="n">
         <v>2.52</v>
@@ -11803,7 +11803,7 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.65</v>
+        <v>2.54</v>
       </c>
       <c r="O45" t="n">
         <v>1.43</v>
@@ -11821,10 +11821,10 @@
         <v>3.7</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="V45" t="n">
         <v>1.53</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -12048,7 +12048,7 @@
         <v>3.4</v>
       </c>
       <c r="K46" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12311,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.86</v>
+        <v>3.25</v>
       </c>
       <c r="O47" t="n">
         <v>1.3</v>
@@ -12320,13 +12320,13 @@
         <v>1.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R47" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="S47" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12410,7 +12410,7 @@
         <v>1.36</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.28</v>
+        <v>7</v>
       </c>
       <c r="AV47" t="n">
         <v>1.46</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>
@@ -13061,22 +13061,22 @@
         <v>4.5</v>
       </c>
       <c r="J50" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K50" t="n">
         <v>3.3</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P50" t="n">
         <v>1.46</v>
@@ -13085,194 +13085,194 @@
         <v>2.72</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BH50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI50" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-09 18:35:38</t>
+          <t>2026-07-09 20:49:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -905,7 +905,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
         <v>65</v>
@@ -1458,7 +1458,7 @@
         <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
         <v>48</v>
@@ -1479,7 +1479,7 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
         <v>9</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         <v>1.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -1709,7 +1709,7 @@
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK5" t="n">
         <v>34</v>
@@ -1736,7 +1736,7 @@
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1760,19 +1760,19 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC5" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
         <v>19.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>6.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="n">
         <v>1.64</v>
@@ -1897,13 +1897,13 @@
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O6" t="n">
         <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q6" t="n">
         <v>2.36</v>
@@ -1969,7 +1969,7 @@
         <v>180</v>
       </c>
       <c r="AL6" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AM6" t="n">
         <v>280</v>
@@ -2008,28 +2008,28 @@
         <v>6.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA6" t="n">
         <v>6.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG6" t="n">
         <v>12.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -2184,40 +2184,40 @@
         <v>16.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
         <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
         <v>22</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
@@ -2229,7 +2229,7 @@
         <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AO7" t="n">
         <v>85</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
         <v>5.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -3179,16 +3179,16 @@
         <v>1.78</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V11" t="n">
         <v>1.71</v>
@@ -3197,13 +3197,13 @@
         <v>1.42</v>
       </c>
       <c r="X11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y11" t="n">
         <v>14.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA11" t="n">
         <v>38</v>
@@ -3215,7 +3215,7 @@
         <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>29</v>
@@ -3227,7 +3227,7 @@
         <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>40</v>
@@ -3248,19 +3248,19 @@
         <v>34</v>
       </c>
       <c r="AO11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="AQ11" t="n">
         <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT11" t="n">
         <v>13</v>
@@ -3272,43 +3272,43 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ11" t="n">
         <v>9.4</v>
@@ -3347,7 +3347,7 @@
         <v>4.1</v>
       </c>
       <c r="BV11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW11" t="n">
         <v>12</v>
@@ -3356,17 +3356,17 @@
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>22</v>
       </c>
       <c r="CA11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>1.48</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="H12" t="n">
         <v>6.8</v>
       </c>
       <c r="I12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.22</v>
@@ -3427,31 +3427,31 @@
         <v>1.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R12" t="n">
         <v>1.8</v>
       </c>
       <c r="S12" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="T12" t="n">
         <v>1.69</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="X12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y12" t="n">
         <v>36</v>
@@ -3508,7 +3508,7 @@
         <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR12" t="n">
         <v>32</v>
@@ -3529,7 +3529,7 @@
         <v>34</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY12" t="n">
         <v>10</v>
@@ -3547,7 +3547,7 @@
         <v>12</v>
       </c>
       <c r="BD12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BE12" t="n">
         <v>34</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -3678,19 +3678,19 @@
         <v>1.09</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P13" t="n">
         <v>1.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="R13" t="n">
         <v>1.07</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5480,7 @@
         <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="G24" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H24" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I24" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="J24" t="n">
         <v>4.1</v>
       </c>
       <c r="K24" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
         <v>1.2</v>
@@ -6469,115 +6469,115 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R24" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="T24" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="U24" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="V24" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W24" t="n">
         <v>1.65</v>
       </c>
       <c r="X24" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="Y24" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB24" t="n">
         <v>23</v>
       </c>
-      <c r="Z24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>22</v>
-      </c>
       <c r="AC24" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF24" t="n">
         <v>25</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AK24" t="n">
         <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AN24" t="n">
         <v>10.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP24" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
       </c>
       <c r="AV24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="AX24" t="n">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="AY24" t="n">
         <v>11</v>
@@ -6586,25 +6586,25 @@
         <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BC24" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="BE24" t="n">
         <v>34</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BG24" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="H25" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
         <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L25" t="n">
         <v>1.13</v>
@@ -6729,28 +6729,28 @@
         <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U25" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V25" t="n">
         <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X25" t="n">
         <v>19</v>
@@ -6759,7 +6759,7 @@
         <v>14.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA25" t="n">
         <v>55</v>
@@ -6768,7 +6768,7 @@
         <v>12.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
         <v>14.5</v>
@@ -6780,7 +6780,7 @@
         <v>18</v>
       </c>
       <c r="AG25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
         <v>17</v>
@@ -6807,10 +6807,10 @@
         <v>29</v>
       </c>
       <c r="AP25" t="n">
-        <v>5.7</v>
+        <v>14</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
         <v>18.5</v>
@@ -6825,37 +6825,37 @@
         <v>7.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX25" t="n">
         <v>14</v>
       </c>
       <c r="AY25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC25" t="n">
         <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF25" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG25" t="n">
         <v>21</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H26" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I26" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J26" t="n">
         <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.32</v>
@@ -6983,28 +6983,28 @@
         <v>1.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U26" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V26" t="n">
         <v>1.63</v>
       </c>
       <c r="W26" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X26" t="n">
         <v>19</v>
@@ -7070,7 +7070,7 @@
         <v>15</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT26" t="n">
         <v>12</v>
@@ -7082,7 +7082,7 @@
         <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX26" t="n">
         <v>19</v>
@@ -7094,25 +7094,25 @@
         <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF26" t="n">
         <v>20</v>
       </c>
       <c r="BG26" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G27" t="n">
         <v>2.44</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I27" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>2.58</v>
+        <v>1.74</v>
       </c>
       <c r="K27" t="n">
         <v>5.1</v>
@@ -7255,7 +7255,7 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W27" t="n">
         <v>1.69</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G28" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="H28" t="n">
         <v>10</v>
@@ -7473,10 +7473,10 @@
         <v>11.5</v>
       </c>
       <c r="J28" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K28" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -7494,25 +7494,25 @@
         <v>2.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U28" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="V28" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="X28" t="n">
         <v>23</v>
@@ -7530,7 +7530,7 @@
         <v>9.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD28" t="n">
         <v>40</v>
@@ -7542,7 +7542,7 @@
         <v>8.6</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
         <v>34</v>
@@ -7554,7 +7554,7 @@
         <v>11.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AL28" t="n">
         <v>44</v>
@@ -7569,58 +7569,58 @@
         <v>250</v>
       </c>
       <c r="AP28" t="n">
-        <v>15</v>
+        <v>7.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU28" t="n">
         <v>11</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BG28" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G29" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H29" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I29" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J29" t="n">
         <v>3.85</v>
@@ -7742,40 +7742,40 @@
         <v>4.6</v>
       </c>
       <c r="O29" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P29" t="n">
         <v>2.26</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S29" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T29" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U29" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V29" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W29" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X29" t="n">
         <v>24</v>
       </c>
       <c r="Y29" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA29" t="n">
         <v>32</v>
@@ -7787,7 +7787,7 @@
         <v>9.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE29" t="n">
         <v>25</v>
@@ -7808,7 +7808,7 @@
         <v>65</v>
       </c>
       <c r="AK29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL29" t="n">
         <v>46</v>
@@ -7820,61 +7820,61 @@
         <v>32</v>
       </c>
       <c r="AO29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP29" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR29" t="n">
         <v>13.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AT29" t="n">
         <v>14</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW29" t="n">
         <v>18</v>
       </c>
       <c r="AX29" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF29" t="n">
         <v>20</v>
       </c>
       <c r="BG29" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH29" t="n">
         <v>4.2</v>
@@ -7919,7 +7919,7 @@
         <v>4.2</v>
       </c>
       <c r="BV29" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BW29" t="n">
         <v>11.5</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -7969,13 +7969,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G30" t="n">
         <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -8223,13 +8223,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G31" t="n">
         <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -8501,13 +8501,13 @@
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
         <v>1.28</v>
       </c>
       <c r="P32" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q32" t="n">
         <v>1.83</v>
@@ -8516,13 +8516,13 @@
         <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T32" t="n">
         <v>1.73</v>
       </c>
       <c r="U32" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V32" t="n">
         <v>1.32</v>
@@ -8534,10 +8534,10 @@
         <v>21</v>
       </c>
       <c r="Y32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA32" t="n">
         <v>95</v>
@@ -8561,7 +8561,7 @@
         <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI32" t="n">
         <v>65</v>
@@ -8570,7 +8570,7 @@
         <v>25</v>
       </c>
       <c r="AK32" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL32" t="n">
         <v>40</v>
@@ -8585,16 +8585,16 @@
         <v>46</v>
       </c>
       <c r="AP32" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AQ32" t="n">
         <v>14</v>
       </c>
       <c r="AR32" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS32" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT32" t="n">
         <v>9.199999999999999</v>
@@ -8603,40 +8603,40 @@
         <v>7.8</v>
       </c>
       <c r="AV32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX32" t="n">
         <v>12</v>
       </c>
-      <c r="AW32" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>11</v>
-      </c>
       <c r="AY32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB32" t="n">
         <v>20</v>
       </c>
       <c r="BC32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD32" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BF32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -8737,10 +8737,10 @@
         <v>3.2</v>
       </c>
       <c r="H33" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I33" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>3.2</v>
@@ -8755,16 +8755,16 @@
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O33" t="n">
         <v>1.38</v>
       </c>
       <c r="P33" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G34" t="n">
         <v>3.4</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
         <v>1.98</v>
       </c>
       <c r="H35" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I35" t="n">
         <v>6.8</v>
@@ -9254,7 +9254,7 @@
         <v>3.2</v>
       </c>
       <c r="K35" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L35" t="n">
         <v>1.47</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
         <v>1.57</v>
       </c>
       <c r="S36" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T36" t="n">
         <v>1.56</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
         <v>370</v>
       </c>
       <c r="AB37" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC37" t="n">
         <v>15.5</v>
@@ -9837,7 +9837,7 @@
         <v>130</v>
       </c>
       <c r="AJ37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK37" t="n">
         <v>16.5</v>
@@ -9858,13 +9858,13 @@
         <v>20</v>
       </c>
       <c r="AQ37" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT37" t="n">
         <v>9</v>
@@ -9873,10 +9873,10 @@
         <v>11.5</v>
       </c>
       <c r="AV37" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AW37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX37" t="n">
         <v>8</v>
@@ -9888,7 +9888,7 @@
         <v>19.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB37" t="n">
         <v>9.6</v>
@@ -9897,16 +9897,16 @@
         <v>12</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF37" t="n">
         <v>4.2</v>
       </c>
       <c r="BG37" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH37" t="n">
         <v>4.7</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -10255,13 +10255,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
       <c r="G39" t="n">
         <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
       <c r="I39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -10515,10 +10515,10 @@
         <v>6.4</v>
       </c>
       <c r="H40" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I40" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="J40" t="n">
         <v>4.8</v>
@@ -10557,10 +10557,10 @@
         <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X40" t="n">
         <v>36</v>
@@ -10617,7 +10617,7 @@
         <v>5.8</v>
       </c>
       <c r="AP40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ40" t="n">
         <v>11.5</v>
@@ -10629,7 +10629,7 @@
         <v>14</v>
       </c>
       <c r="AT40" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU40" t="n">
         <v>10.5</v>
@@ -10644,7 +10644,7 @@
         <v>6.2</v>
       </c>
       <c r="AY40" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AZ40" t="n">
         <v>16</v>
@@ -10653,19 +10653,19 @@
         <v>18.5</v>
       </c>
       <c r="BB40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD40" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC40" t="n">
+      <c r="BE40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF40" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>6.4</v>
       </c>
       <c r="BG40" t="n">
         <v>5.2</v>
@@ -10716,7 +10716,7 @@
         <v>9.6</v>
       </c>
       <c r="BW40" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX40" t="n">
         <v>19.5</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -10763,22 +10763,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G41" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="H41" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I41" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L41" t="n">
         <v>1.29</v>
@@ -10811,22 +10811,22 @@
         <v>2.18</v>
       </c>
       <c r="V41" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W41" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X41" t="n">
         <v>22</v>
       </c>
       <c r="Y41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z41" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA41" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB41" t="n">
         <v>12</v>
@@ -10835,7 +10835,7 @@
         <v>11</v>
       </c>
       <c r="AD41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE41" t="n">
         <v>65</v>
@@ -10850,7 +10850,7 @@
         <v>22</v>
       </c>
       <c r="AI41" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ41" t="n">
         <v>22</v>
@@ -10859,7 +10859,7 @@
         <v>21</v>
       </c>
       <c r="AL41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM41" t="n">
         <v>100</v>
@@ -10871,16 +10871,16 @@
         <v>65</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ41" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AR41" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT41" t="n">
         <v>9</v>
@@ -10889,40 +10889,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV41" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AW41" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AX41" t="n">
         <v>9</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="AZ41" t="n">
         <v>14.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC41" t="n">
         <v>13.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF41" t="n">
         <v>7.2</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH41" t="n">
         <v>3.9</v>
@@ -10940,10 +10940,10 @@
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN41" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO41" t="n">
         <v>4</v>
@@ -10958,10 +10958,10 @@
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT41" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU41" t="n">
         <v>6.8</v>
@@ -10970,7 +10970,7 @@
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -11525,13 +11525,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="G44" t="n">
         <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
@@ -11552,7 +11552,7 @@
         <v>1.07</v>
       </c>
       <c r="O44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P44" t="n">
         <v>1.07</v>
@@ -11561,10 +11561,10 @@
         <v>1.4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="S44" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -11779,16 +11779,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G45" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H45" t="n">
         <v>2.52</v>
       </c>
       <c r="I45" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J45" t="n">
         <v>2.72</v>
@@ -11800,7 +11800,7 @@
         <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N45" t="n">
         <v>2.54</v>
@@ -11815,16 +11815,16 @@
         <v>2.22</v>
       </c>
       <c r="R45" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S45" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="T45" t="n">
         <v>1.58</v>
       </c>
       <c r="U45" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="V45" t="n">
         <v>1.53</v>
@@ -11833,7 +11833,7 @@
         <v>1.4</v>
       </c>
       <c r="X45" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y45" t="n">
         <v>13</v>
@@ -11845,7 +11845,7 @@
         <v>65</v>
       </c>
       <c r="AB45" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC45" t="n">
         <v>10.5</v>
@@ -11863,7 +11863,7 @@
         <v>20</v>
       </c>
       <c r="AH45" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI45" t="n">
         <v>75</v>
@@ -11887,58 +11887,58 @@
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS45" t="n">
         <v>2.16</v>
       </c>
-      <c r="AQ45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>2.42</v>
-      </c>
       <c r="AT45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW45" t="n">
         <v>2.14</v>
       </c>
-      <c r="AU45" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AX45" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AY45" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AZ45" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="BA45" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="BB45" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="BD45" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="BE45" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="BF45" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="BG45" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="BH45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12311,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="O47" t="n">
         <v>1.3</v>
@@ -12320,7 +12320,7 @@
         <v>1.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="R47" t="n">
         <v>1.28</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12553,7 @@
         <v>1000</v>
       </c>
       <c r="J48" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="K48" t="n">
         <v>1000</v>
@@ -12565,13 +12565,13 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="O48" t="n">
         <v>1.02</v>
       </c>
       <c r="P48" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Q48" t="n">
         <v>1.3</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>
@@ -13076,7 +13076,7 @@
         <v>1.46</v>
       </c>
       <c r="O50" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="P50" t="n">
         <v>1.46</v>
@@ -13094,7 +13094,7 @@
         <v>1.01</v>
       </c>
       <c r="U50" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V50" t="n">
         <v>1.33</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-09 20:49:26</t>
+          <t>2026-07-09 23:03:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB50"/>
+  <dimension ref="A1:CB52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>1.76</v>
       </c>
       <c r="G3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I3" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,130 +1135,130 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
         <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AJ3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK3" t="n">
         <v>26</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV3" t="n">
         <v>17</v>
       </c>
-      <c r="AO3" t="n">
-        <v>230</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AW3" t="n">
         <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
         <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
         <v>1.03</v>
@@ -1267,10 +1267,10 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="n">
         <v>27</v>
@@ -1470,7 +1470,7 @@
         <v>21</v>
       </c>
       <c r="AO4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
@@ -1482,7 +1482,7 @@
         <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT4" t="n">
         <v>7.2</v>
@@ -1491,10 +1491,10 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX4" t="n">
         <v>10.5</v>
@@ -1503,28 +1503,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF4" t="n">
         <v>17</v>
       </c>
       <c r="BG4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="n">
         <v>3.15</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
@@ -1667,13 +1667,13 @@
         <v>2.16</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W5" t="n">
         <v>1.54</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Y5" t="n">
         <v>12</v>
@@ -1682,13 +1682,13 @@
         <v>19.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB5" t="n">
         <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
         <v>13</v>
@@ -1697,10 +1697,10 @@
         <v>34</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
         <v>18</v>
@@ -1736,7 +1736,7 @@
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1760,19 +1760,19 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BF5" t="n">
         <v>19.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -1897,25 +1897,25 @@
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
         <v>4.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U6" t="n">
         <v>1.7</v>
@@ -1927,64 +1927,64 @@
         <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
         <v>6.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AC6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH6" t="n">
         <v>34</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>36</v>
       </c>
       <c r="AI6" t="n">
         <v>70</v>
       </c>
       <c r="AJ6" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR6" t="n">
         <v>7.6</v>
@@ -1999,43 +1999,43 @@
         <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
         <v>19</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.8</v>
+        <v>19</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.8</v>
+        <v>48</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.8</v>
+        <v>42</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>44</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>50</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.8</v>
+        <v>48</v>
       </c>
       <c r="BG6" t="n">
         <v>12.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI6" t="n">
         <v>2.76</v>
@@ -2077,10 +2077,10 @@
         <v>3.55</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
@@ -2092,11 +2092,11 @@
         <v>29</v>
       </c>
       <c r="CA6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -2133,16 +2133,16 @@
         <v>2.08</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J7" t="n">
         <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2175,16 +2175,16 @@
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W7" t="n">
         <v>1.92</v>
       </c>
       <c r="X7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z7" t="n">
         <v>34</v>
@@ -2193,7 +2193,7 @@
         <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8.6</v>
@@ -2202,19 +2202,19 @@
         <v>22</v>
       </c>
       <c r="AE7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
         <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
         <v>25</v>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
         <v>140</v>
@@ -2232,7 +2232,7 @@
         <v>16.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP7" t="n">
         <v>9.800000000000001</v>
@@ -2319,7 +2319,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BR7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS7" t="n">
         <v>17.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
         <v>5.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2414,10 +2414,10 @@
         <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
         <v>2.88</v>
@@ -2564,7 +2564,7 @@
         <v>13</v>
       </c>
       <c r="BO8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
@@ -2600,11 +2600,11 @@
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G9" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
         <v>3.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
         <v>1.37</v>
@@ -2659,7 +2659,7 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
         <v>1.37</v>
@@ -2668,7 +2668,7 @@
         <v>1.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
         <v>1.29</v>
@@ -2686,10 +2686,10 @@
         <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y9" t="n">
         <v>14.5</v>
@@ -2701,10 +2701,10 @@
         <v>80</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
         <v>17.5</v>
@@ -2713,7 +2713,7 @@
         <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
         <v>14</v>
@@ -2722,7 +2722,7 @@
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ9" t="n">
         <v>42</v>
@@ -2746,7 +2746,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR9" t="n">
         <v>17</v>
@@ -2755,7 +2755,7 @@
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
         <v>5.8</v>
@@ -2797,10 +2797,10 @@
         <v>32</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2821,10 +2821,10 @@
         <v>4</v>
       </c>
       <c r="BP9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2839,7 +2839,7 @@
         <v>4.9</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW9" t="n">
         <v>20</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -2889,31 +2889,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G10" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H10" t="n">
         <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.39</v>
@@ -2934,13 +2934,13 @@
         <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
         <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X10" t="n">
         <v>13.5</v>
@@ -2958,7 +2958,7 @@
         <v>8</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
         <v>21</v>
@@ -2985,7 +2985,7 @@
         <v>30</v>
       </c>
       <c r="AL10" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AM10" t="n">
         <v>160</v>
@@ -3039,7 +3039,7 @@
         <v>17.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BE10" t="n">
         <v>1.03</v>
@@ -3051,7 +3051,7 @@
         <v>65</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI10" t="n">
         <v>2.84</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I11" t="n">
         <v>2.4</v>
@@ -3176,7 +3176,7 @@
         <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R11" t="n">
         <v>1.46</v>
@@ -3185,19 +3185,19 @@
         <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V11" t="n">
         <v>1.71</v>
       </c>
       <c r="W11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="n">
         <v>14.5</v>
@@ -3224,7 +3224,7 @@
         <v>26</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
@@ -3248,7 +3248,7 @@
         <v>34</v>
       </c>
       <c r="AO11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP11" t="n">
         <v>15</v>
@@ -3260,7 +3260,7 @@
         <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT11" t="n">
         <v>13</v>
@@ -3281,22 +3281,22 @@
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD11" t="n">
         <v>6.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
@@ -3308,7 +3308,7 @@
         <v>3.9</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
         <v>9.4</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="BN11" t="n">
         <v>6.8</v>
@@ -3347,26 +3347,26 @@
         <v>4.1</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BZ11" t="n">
         <v>22</v>
       </c>
       <c r="CA11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H12" t="n">
         <v>6.8</v>
@@ -3421,25 +3421,25 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R12" t="n">
         <v>1.8</v>
       </c>
       <c r="S12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U12" t="n">
         <v>2.32</v>
@@ -3448,7 +3448,7 @@
         <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X12" t="n">
         <v>30</v>
@@ -3466,7 +3466,7 @@
         <v>15</v>
       </c>
       <c r="AC12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD12" t="n">
         <v>28</v>
@@ -3490,7 +3490,7 @@
         <v>16.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL12" t="n">
         <v>30</v>
@@ -3520,7 +3520,7 @@
         <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV12" t="n">
         <v>20</v>
@@ -3553,10 +3553,10 @@
         <v>34</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="R13" t="n">
         <v>1.07</v>
       </c>
       <c r="S13" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G15" t="n">
         <v>2.46</v>
@@ -4168,25 +4168,25 @@
         <v>3.3</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
         <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
         <v>1.35</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
         <v>1.73</v>
@@ -4195,16 +4195,16 @@
         <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>2.04</v>
+        <v>3.85</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V15" t="n">
         <v>1.31</v>
@@ -4213,58 +4213,58 @@
         <v>1.68</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP15" t="n">
         <v>1.03</v>
@@ -4315,7 +4315,7 @@
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -4413,112 +4413,112 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="G16" t="n">
         <v>3.65</v>
       </c>
       <c r="H16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I16" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="O16" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="W16" t="n">
         <v>1.37</v>
       </c>
       <c r="X16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
         <v>1.03</v>
@@ -4572,7 +4572,7 @@
         <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -4667,46 +4667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4</v>
+        <v>9.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5</v>
+        <v>1.09</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
         <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
         <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -4715,7 +4715,7 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
         <v>3.3</v>
@@ -4832,7 +4832,7 @@
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="O18" t="n">
         <v>1.02</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>2.44</v>
       </c>
       <c r="G24" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H24" t="n">
         <v>2.64</v>
@@ -6475,16 +6475,16 @@
         <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
         <v>1.41</v>
       </c>
       <c r="R24" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="S24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T24" t="n">
         <v>1.43</v>
@@ -6499,19 +6499,19 @@
         <v>1.65</v>
       </c>
       <c r="X24" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Y24" t="n">
         <v>24</v>
       </c>
       <c r="Z24" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA24" t="n">
         <v>120</v>
       </c>
       <c r="AB24" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AC24" t="n">
         <v>11.5</v>
@@ -6532,7 +6532,7 @@
         <v>14.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AJ24" t="n">
         <v>85</v>
@@ -6565,7 +6565,7 @@
         <v>25</v>
       </c>
       <c r="AT24" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -6589,7 +6589,7 @@
         <v>17.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BC24" t="n">
         <v>15.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -6732,16 +6732,16 @@
         <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R25" t="n">
         <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U25" t="n">
         <v>2.28</v>
@@ -6771,7 +6771,7 @@
         <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE25" t="n">
         <v>36</v>
@@ -6828,31 +6828,31 @@
         <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY25" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BA25" t="n">
         <v>7.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC25" t="n">
         <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25" t="n">
         <v>15.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G26" t="n">
         <v>3.15</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G27" t="n">
         <v>2.44</v>
       </c>
       <c r="H27" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.74</v>
+        <v>2.58</v>
       </c>
       <c r="K27" t="n">
-        <v>5.1</v>
+        <v>15</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7255,118 +7255,118 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
         <v>1.69</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>720</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>780</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>590</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="AS27" t="n">
         <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7452,34 +7452,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chongqing Tonglianglong</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.36</v>
+        <v>3.25</v>
       </c>
       <c r="G28" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>2.16</v>
       </c>
       <c r="I28" t="n">
-        <v>11.5</v>
+        <v>2.28</v>
       </c>
       <c r="J28" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="K28" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
@@ -7488,151 +7488,151 @@
         <v>4.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S28" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T28" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="U28" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="V28" t="n">
-        <v>1.1</v>
+        <v>1.78</v>
       </c>
       <c r="W28" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="X28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK28" t="n">
         <v>38</v>
       </c>
-      <c r="Z28" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>430</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC28" t="n">
+      <c r="AL28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY28" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ28" t="n">
+      <c r="AZ28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG28" t="n">
         <v>11.5</v>
       </c>
-      <c r="AK28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH28" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ28" t="n">
-        <v>16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK28" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7641,57 +7641,57 @@
         <v>21</v>
       </c>
       <c r="BN28" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BO28" t="n">
-        <v>2.84</v>
+        <v>5.4</v>
       </c>
       <c r="BP28" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="BQ28" t="n">
-        <v>5.3</v>
+        <v>18.5</v>
       </c>
       <c r="BR28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS28" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BT28" t="n">
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="BV28" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW28" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BX28" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY28" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BZ28" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CA28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7706,187 +7706,187 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Chongqing Tonglianglong</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.25</v>
+        <v>1.36</v>
       </c>
       <c r="G29" t="n">
-        <v>3.5</v>
+        <v>1.41</v>
       </c>
       <c r="H29" t="n">
-        <v>2.16</v>
+        <v>9.6</v>
       </c>
       <c r="I29" t="n">
-        <v>2.28</v>
+        <v>11.5</v>
       </c>
       <c r="J29" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="K29" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O29" t="n">
         <v>1.24</v>
       </c>
       <c r="P29" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R29" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T29" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="U29" t="n">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="V29" t="n">
-        <v>1.78</v>
+        <v>1.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="X29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y29" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>420</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC29" t="n">
         <v>13</v>
       </c>
-      <c r="Z29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AD29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>11.5</v>
       </c>
-      <c r="AE29" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>65</v>
-      </c>
       <c r="AK29" t="n">
-        <v>38</v>
+        <v>15.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM29" t="n">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="AN29" t="n">
-        <v>32</v>
+        <v>5.7</v>
       </c>
       <c r="AO29" t="n">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="AP29" t="n">
-        <v>17.5</v>
+        <v>8</v>
       </c>
       <c r="AQ29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU29" t="n">
         <v>11</v>
       </c>
-      <c r="AR29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>8</v>
-      </c>
       <c r="AV29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW29" t="n">
         <v>10</v>
       </c>
-      <c r="AW29" t="n">
-        <v>18</v>
-      </c>
       <c r="AX29" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="BB29" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC29" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BD29" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BF29" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BG29" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH29" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BK29" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
@@ -7895,50 +7895,50 @@
         <v>21</v>
       </c>
       <c r="BN29" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BO29" t="n">
-        <v>5.4</v>
+        <v>2.84</v>
       </c>
       <c r="BP29" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="BQ29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BT29" t="n">
         <v>18</v>
       </c>
-      <c r="BR29" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS29" t="n">
-        <v>23</v>
-      </c>
-      <c r="BT29" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BU29" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BV29" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BX29" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="CA29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -8513,7 +8513,7 @@
         <v>1.83</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
         <v>3.1</v>
@@ -8522,7 +8522,7 @@
         <v>1.73</v>
       </c>
       <c r="U32" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V32" t="n">
         <v>1.32</v>
@@ -8531,7 +8531,7 @@
         <v>1.94</v>
       </c>
       <c r="X32" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Y32" t="n">
         <v>16.5</v>
@@ -8543,7 +8543,7 @@
         <v>95</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC32" t="n">
         <v>9.199999999999999</v>
@@ -8555,7 +8555,7 @@
         <v>48</v>
       </c>
       <c r="AF32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG32" t="n">
         <v>10.5</v>
@@ -8573,7 +8573,7 @@
         <v>22</v>
       </c>
       <c r="AL32" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -8591,10 +8591,10 @@
         <v>14</v>
       </c>
       <c r="AR32" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT32" t="n">
         <v>9.199999999999999</v>
@@ -8606,7 +8606,7 @@
         <v>13.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX32" t="n">
         <v>12</v>
@@ -8618,7 +8618,7 @@
         <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB32" t="n">
         <v>20</v>
@@ -8627,16 +8627,16 @@
         <v>18</v>
       </c>
       <c r="BD32" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF32" t="n">
         <v>11.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8648,7 +8648,7 @@
         <v>13.5</v>
       </c>
       <c r="BK32" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
@@ -8657,10 +8657,10 @@
         <v>21</v>
       </c>
       <c r="BN32" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BP32" t="n">
         <v>20</v>
@@ -8672,19 +8672,19 @@
         <v>38</v>
       </c>
       <c r="BS32" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BT32" t="n">
         <v>10.5</v>
       </c>
       <c r="BU32" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BV32" t="n">
         <v>46</v>
       </c>
       <c r="BW32" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8976,218 +8976,218 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t>SER Caxias do Sul</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.15</v>
+        <v>1.71</v>
       </c>
       <c r="G34" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="H34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W34" t="n">
         <v>2.16</v>
       </c>
-      <c r="I34" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J34" t="n">
-        <v>4</v>
-      </c>
-      <c r="K34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X34" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Y34" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="n">
-        <v>17.5</v>
+        <v>55</v>
       </c>
       <c r="AA34" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>19</v>
+        <v>8.4</v>
       </c>
       <c r="AC34" t="n">
         <v>10.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AK34" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF34" t="n">
         <v>13</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>26</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU34" t="n">
         <v>7.2</v>
       </c>
-      <c r="AS34" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU34" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV34" t="n">
         <v>1000</v>
       </c>
@@ -9204,18 +9204,18 @@
         <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9230,217 +9230,217 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="G35" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="H35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
         <v>4.8</v>
       </c>
-      <c r="I35" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K35" t="n">
+      <c r="O35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X35" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO35" t="n">
         <v>3.85</v>
       </c>
-      <c r="L35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK35" t="n">
-        <v>9</v>
-      </c>
-      <c r="BL35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO35" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BP35" t="n">
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BT35" t="n">
         <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
@@ -9458,18 +9458,18 @@
         <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9484,187 +9484,187 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="G36" t="n">
-        <v>2.28</v>
+        <v>1.39</v>
       </c>
       <c r="H36" t="n">
-        <v>3.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="J36" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="K36" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N36" t="n">
-        <v>1.08</v>
+        <v>5.5</v>
       </c>
       <c r="O36" t="n">
         <v>1.19</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R36" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="S36" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="T36" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="U36" t="n">
-        <v>2.54</v>
+        <v>1.97</v>
       </c>
       <c r="V36" t="n">
-        <v>1.39</v>
+        <v>1.1</v>
       </c>
       <c r="W36" t="n">
-        <v>1.78</v>
+        <v>3.55</v>
       </c>
       <c r="X36" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y36" t="n">
-        <v>18.5</v>
+        <v>40</v>
       </c>
       <c r="Z36" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="AA36" t="n">
-        <v>55</v>
+        <v>370</v>
       </c>
       <c r="AB36" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AC36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB36" t="n">
         <v>10</v>
       </c>
-      <c r="AD36" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG36" t="n">
+      <c r="BC36" t="n">
         <v>12</v>
       </c>
-      <c r="AH36" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ36" t="n">
+      <c r="BD36" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="BE36" t="n">
         <v>7.2</v>
       </c>
-      <c r="AS36" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD36" t="n">
+      <c r="BF36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG36" t="n">
         <v>7.4</v>
       </c>
-      <c r="BE36" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>7</v>
-      </c>
       <c r="BH36" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI36" t="n">
-        <v>2.98</v>
+        <v>3.65</v>
       </c>
       <c r="BJ36" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK36" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
@@ -9673,50 +9673,50 @@
         <v>21</v>
       </c>
       <c r="BN36" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BO36" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="BP36" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BQ36" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BR36" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BS36" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BT36" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BU36" t="n">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BV36" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="BW36" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BX36" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BY36" t="n">
-        <v>18.5</v>
+        <v>48</v>
       </c>
       <c r="BZ36" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CA36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -9738,187 +9738,187 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F37" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R37" t="n">
         <v>1.35</v>
       </c>
-      <c r="G37" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="H37" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I37" t="n">
+      <c r="S37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X37" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP37" t="n">
         <v>11.5</v>
       </c>
-      <c r="J37" t="n">
+      <c r="AQ37" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB37" t="n">
         <v>5.6</v>
       </c>
-      <c r="K37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N37" t="n">
+      <c r="BC37" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD37" t="n">
         <v>5.5</v>
       </c>
-      <c r="O37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W37" t="n">
+      <c r="BE37" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH37" t="n">
         <v>3.55</v>
       </c>
-      <c r="X37" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>370</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF37" t="n">
+      <c r="BI37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ37" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AG37" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH37" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI37" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BJ37" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BK37" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
@@ -9927,40 +9927,40 @@
         <v>21</v>
       </c>
       <c r="BN37" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO37" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="BP37" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BQ37" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BR37" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BS37" t="n">
+        <v>26</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW37" t="n">
         <v>16</v>
       </c>
-      <c r="BT37" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BU37" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BV37" t="n">
-        <v>80</v>
-      </c>
-      <c r="BW37" t="n">
-        <v>21</v>
-      </c>
       <c r="BX37" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="BY37" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="BZ37" t="n">
         <v>0</v>
@@ -9970,14 +9970,14 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9992,175 +9992,175 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="G38" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="H38" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="I38" t="n">
-        <v>2.76</v>
+        <v>2.26</v>
       </c>
       <c r="J38" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N38" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="O38" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="P38" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="R38" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="T38" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="U38" t="n">
-        <v>2.14</v>
+        <v>2.64</v>
       </c>
       <c r="V38" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="X38" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="Y38" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Z38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE38" t="n">
         <v>21</v>
       </c>
-      <c r="AA38" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>34</v>
-      </c>
       <c r="AF38" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AG38" t="n">
         <v>15</v>
       </c>
       <c r="AH38" t="n">
-        <v>19.5</v>
+        <v>550</v>
       </c>
       <c r="AI38" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AJ38" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM38" t="n">
         <v>55</v>
       </c>
-      <c r="AK38" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>100</v>
-      </c>
       <c r="AN38" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AO38" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="AP38" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AQ38" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AR38" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT38" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AV38" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW38" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="AX38" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY38" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AZ38" t="n">
         <v>13</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="BD38" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE38" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BF38" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="BG38" t="n">
-        <v>17</v>
+        <v>9.4</v>
       </c>
       <c r="BH38" t="n">
         <v>1000</v>
@@ -10169,62 +10169,62 @@
         <v>1.01</v>
       </c>
       <c r="BJ38" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN38" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP38" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BR38" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT38" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV38" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX38" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
         <v>1.59</v>
       </c>
       <c r="J40" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K40" t="n">
         <v>5</v>
@@ -10533,13 +10533,13 @@
         <v>1.03</v>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O40" t="n">
         <v>1.17</v>
       </c>
       <c r="P40" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q40" t="n">
         <v>1.52</v>
@@ -10560,7 +10560,7 @@
         <v>2.68</v>
       </c>
       <c r="W40" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
         <v>36</v>
@@ -10614,10 +10614,10 @@
         <v>65</v>
       </c>
       <c r="AO40" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AP40" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ40" t="n">
         <v>11.5</v>
@@ -10629,7 +10629,7 @@
         <v>14</v>
       </c>
       <c r="AT40" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU40" t="n">
         <v>10.5</v>
@@ -10641,7 +10641,7 @@
         <v>13</v>
       </c>
       <c r="AX40" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY40" t="n">
         <v>21</v>
@@ -10653,28 +10653,28 @@
         <v>18.5</v>
       </c>
       <c r="BB40" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BC40" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD40" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE40" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF40" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH40" t="n">
         <v>4.7</v>
       </c>
       <c r="BI40" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ40" t="n">
         <v>9.4</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G41" t="n">
         <v>1.83</v>
@@ -10790,7 +10790,7 @@
         <v>4.4</v>
       </c>
       <c r="O41" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P41" t="n">
         <v>2.18</v>
@@ -10823,7 +10823,7 @@
         <v>22</v>
       </c>
       <c r="Z41" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA41" t="n">
         <v>130</v>
@@ -10871,13 +10871,13 @@
         <v>65</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR41" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS41" t="n">
         <v>6</v>
@@ -10889,10 +10889,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV41" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW41" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX41" t="n">
         <v>9</v>
@@ -10904,25 +10904,25 @@
         <v>14.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC41" t="n">
         <v>13.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE41" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG41" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>5.8</v>
       </c>
       <c r="BH41" t="n">
         <v>3.9</v>
@@ -10946,7 +10946,7 @@
         <v>4.6</v>
       </c>
       <c r="BO41" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP41" t="n">
         <v>11.5</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
         <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11289,7 @@
         <v>4.3</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M43" t="n">
         <v>1.05</v>
@@ -11304,7 +11304,7 @@
         <v>2.12</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R43" t="n">
         <v>1.44</v>
@@ -11433,16 +11433,16 @@
         <v>4.1</v>
       </c>
       <c r="BH43" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI43" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ43" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK43" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
@@ -11451,50 +11451,50 @@
         <v>1.01</v>
       </c>
       <c r="BN43" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO43" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP43" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ43" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR43" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS43" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BT43" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU43" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BZ43" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA43" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -11525,13 +11525,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="G44" t="n">
         <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
@@ -11549,19 +11549,19 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="O44" t="n">
         <v>1.01</v>
       </c>
       <c r="P44" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Q44" t="n">
         <v>1.4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="S44" t="n">
         <v>1.4</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -11779,16 +11779,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="G45" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="H45" t="n">
         <v>2.52</v>
       </c>
       <c r="I45" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="J45" t="n">
         <v>2.72</v>
@@ -11803,7 +11803,7 @@
         <v>1.1</v>
       </c>
       <c r="N45" t="n">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="O45" t="n">
         <v>1.43</v>
@@ -11821,124 +11821,124 @@
         <v>4.3</v>
       </c>
       <c r="T45" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="U45" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="V45" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W45" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X45" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y45" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD45" t="n">
         <v>13</v>
       </c>
-      <c r="Z45" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AE45" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AF45" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AG45" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI45" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AJ45" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AK45" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AL45" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AM45" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN45" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO45" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.24</v>
+        <v>4.9</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.91</v>
+        <v>4.3</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.04</v>
+        <v>5.4</v>
       </c>
       <c r="AS45" t="n">
-        <v>2.16</v>
+        <v>6.6</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.91</v>
+        <v>8.6</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.84</v>
+        <v>6.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="AW45" t="n">
-        <v>2.14</v>
+        <v>6.4</v>
       </c>
       <c r="AX45" t="n">
-        <v>2.08</v>
+        <v>5.7</v>
       </c>
       <c r="AY45" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="AZ45" t="n">
-        <v>2.04</v>
+        <v>5.7</v>
       </c>
       <c r="BA45" t="n">
-        <v>2.16</v>
+        <v>6.8</v>
       </c>
       <c r="BB45" t="n">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.16</v>
+        <v>6.6</v>
       </c>
       <c r="BD45" t="n">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="BE45" t="n">
-        <v>2.24</v>
+        <v>4.9</v>
       </c>
       <c r="BF45" t="n">
-        <v>2.24</v>
+        <v>6.8</v>
       </c>
       <c r="BG45" t="n">
-        <v>2.24</v>
+        <v>6.6</v>
       </c>
       <c r="BH45" t="n">
         <v>1000</v>
@@ -11977,7 +11977,7 @@
         <v>21</v>
       </c>
       <c r="BT45" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU45" t="n">
         <v>3.6</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
@@ -12256,14 +12256,14 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12273,60 +12273,60 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Portuguesa SP</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Marcilio</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="G47" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="H47" t="n">
-        <v>1.86</v>
+        <v>1.02</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>3.5</v>
+        <v>1.02</v>
       </c>
       <c r="K47" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L47" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M47" t="n">
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="O47" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="P47" t="n">
-        <v>1.85</v>
+        <v>1.07</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.82</v>
+        <v>1.05</v>
       </c>
       <c r="R47" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="S47" t="n">
-        <v>3.4</v>
+        <v>1.05</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12335,16 +12335,16 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="X47" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y47" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z47" t="n">
         <v>1000</v>
@@ -12353,10 +12353,10 @@
         <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC47" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD47" t="n">
         <v>1000</v>
@@ -12380,10 +12380,10 @@
         <v>1000</v>
       </c>
       <c r="AK47" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL47" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM47" t="n">
         <v>1000</v>
@@ -12395,58 +12395,58 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AU47" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.43</v>
+        <v>1.03</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.43</v>
+        <v>1.03</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BH47" t="n">
         <v>1000</v>
@@ -12455,69 +12455,69 @@
         <v>1.01</v>
       </c>
       <c r="BJ47" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK47" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN47" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BO47" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BP47" t="n">
         <v>1000</v>
       </c>
       <c r="BQ47" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR47" t="n">
         <v>1000</v>
       </c>
       <c r="BS47" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT47" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU47" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BV47" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW47" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX47" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ47" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="CA47" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12527,180 +12527,180 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.09</v>
+        <v>4.4</v>
       </c>
       <c r="G48" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="H48" t="n">
-        <v>1.09</v>
+        <v>1.85</v>
       </c>
       <c r="I48" t="n">
-        <v>1000</v>
+        <v>1.99</v>
       </c>
       <c r="J48" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K48" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L48" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M48" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N48" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="O48" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="P48" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="R48" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="S48" t="n">
-        <v>1.3</v>
+        <v>3.55</v>
       </c>
       <c r="T48" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U48" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V48" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="W48" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="X48" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y48" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z48" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA48" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB48" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC48" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD48" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF48" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG48" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH48" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI48" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK48" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL48" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM48" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN48" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO48" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH48" t="n">
         <v>1000</v>
@@ -12709,69 +12709,69 @@
         <v>1.01</v>
       </c>
       <c r="BJ48" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK48" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN48" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO48" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BP48" t="n">
         <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT48" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU48" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV48" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BX48" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BZ48" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12786,229 +12786,229 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>XV De Piracicaba</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Cianorte PR</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.02</v>
+        <v>1.02</v>
       </c>
       <c r="G49" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H49" t="n">
-        <v>3.9</v>
+        <v>1.02</v>
       </c>
       <c r="I49" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J49" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K49" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P49" t="n">
-        <v>1.64</v>
+        <v>1.09</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ49" t="n">
         <v>0</v>
@@ -13018,261 +13018,769 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-09 23:03:04</t>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Wanderers (Uru)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB50" t="inlineStr">
+        <is>
+          <t>2026-07-10 01:20:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Huracan del Paso</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Colon FC</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB51" t="inlineStr">
+        <is>
+          <t>2026-07-10 01:20:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Guayaquil City</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Delfin</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F52" t="n">
         <v>2.36</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G52" t="n">
         <v>2.68</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H52" t="n">
         <v>3.4</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I52" t="n">
         <v>4.5</v>
       </c>
-      <c r="J50" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K50" t="n">
+      <c r="J52" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K52" t="n">
         <v>3.3</v>
       </c>
-      <c r="L50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N50" t="n">
+      <c r="L52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P52" t="n">
         <v>1.46</v>
       </c>
-      <c r="O50" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q50" t="n">
+      <c r="Q52" t="n">
         <v>2.72</v>
       </c>
-      <c r="R50" t="n">
+      <c r="R52" t="n">
         <v>1.13</v>
       </c>
-      <c r="S50" t="n">
+      <c r="S52" t="n">
         <v>2.72</v>
       </c>
-      <c r="T50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V50" t="n">
+      <c r="T52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V52" t="n">
         <v>1.33</v>
       </c>
-      <c r="W50" t="n">
+      <c r="W52" t="n">
         <v>1.59</v>
       </c>
-      <c r="X50" t="n">
+      <c r="X52" t="n">
         <v>9.6</v>
       </c>
-      <c r="Y50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ50" t="n">
+      <c r="Y52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ52" t="n">
         <v>1.11</v>
       </c>
-      <c r="AR50" t="n">
+      <c r="AR52" t="n">
         <v>1.11</v>
       </c>
-      <c r="AS50" t="n">
+      <c r="AS52" t="n">
         <v>1.11</v>
       </c>
-      <c r="AT50" t="n">
+      <c r="AT52" t="n">
         <v>1.11</v>
       </c>
-      <c r="AU50" t="n">
+      <c r="AU52" t="n">
         <v>1.11</v>
       </c>
-      <c r="AV50" t="n">
+      <c r="AV52" t="n">
         <v>1.11</v>
       </c>
-      <c r="AW50" t="n">
+      <c r="AW52" t="n">
         <v>1.11</v>
       </c>
-      <c r="AX50" t="n">
+      <c r="AX52" t="n">
         <v>1.11</v>
       </c>
-      <c r="AY50" t="n">
+      <c r="AY52" t="n">
         <v>1.11</v>
       </c>
-      <c r="AZ50" t="n">
+      <c r="AZ52" t="n">
         <v>1.11</v>
       </c>
-      <c r="BA50" t="n">
+      <c r="BA52" t="n">
         <v>1.11</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BB52" t="n">
         <v>1.11</v>
       </c>
-      <c r="BC50" t="n">
+      <c r="BC52" t="n">
         <v>1.11</v>
       </c>
-      <c r="BD50" t="n">
+      <c r="BD52" t="n">
         <v>1.11</v>
       </c>
-      <c r="BE50" t="n">
+      <c r="BE52" t="n">
         <v>1.11</v>
       </c>
-      <c r="BF50" t="n">
+      <c r="BF52" t="n">
         <v>1.11</v>
       </c>
-      <c r="BG50" t="n">
+      <c r="BG52" t="n">
         <v>1.11</v>
       </c>
-      <c r="BH50" t="n">
+      <c r="BH52" t="n">
         <v>3</v>
       </c>
-      <c r="BI50" t="n">
+      <c r="BI52" t="n">
         <v>2.12</v>
       </c>
-      <c r="BJ50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB50" t="inlineStr">
-        <is>
-          <t>2026-07-09 23:03:04</t>
+      <c r="BJ52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB52" t="inlineStr">
+        <is>
+          <t>2026-07-10 01:20:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -1114,73 +1114,73 @@
         <v>1.76</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
         <v>220</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>29</v>
@@ -1189,7 +1189,7 @@
         <v>130</v>
       </c>
       <c r="AF3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
         <v>12.5</v>
@@ -1201,7 +1201,7 @@
         <v>130</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
         <v>26</v>
@@ -1216,70 +1216,70 @@
         <v>17.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC3" t="n">
         <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>10.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
         <v>1.01</v>
@@ -1291,13 +1291,13 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ3" t="n">
         <v>1.01</v>
@@ -1309,7 +1309,7 @@
         <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H4" t="n">
         <v>4.1</v>
@@ -1419,10 +1419,10 @@
         <v>1.87</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
         <v>32</v>
@@ -1431,7 +1431,7 @@
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
         <v>7.8</v>
@@ -1443,7 +1443,7 @@
         <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
@@ -1482,7 +1482,7 @@
         <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AT4" t="n">
         <v>7.2</v>
@@ -1491,10 +1491,10 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
         <v>10.5</v>
@@ -1503,28 +1503,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF4" t="n">
         <v>17</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.15</v>
@@ -1536,13 +1536,13 @@
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
         <v>4.8</v>
@@ -1554,13 +1554,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
         <v>7.8</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         <v>1.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -1790,7 +1790,7 @@
         <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1808,13 +1808,13 @@
         <v>23</v>
       </c>
       <c r="BQ5" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>36</v>
       </c>
       <c r="BS5" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
         <v>6.2</v>
@@ -1826,23 +1826,23 @@
         <v>23</v>
       </c>
       <c r="BW5" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>36</v>
       </c>
       <c r="BY5" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>29</v>
       </c>
       <c r="CA5" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>6.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H6" t="n">
         <v>1.64</v>
@@ -1888,7 +1888,7 @@
         <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
         <v>1.5</v>
@@ -1909,7 +1909,7 @@
         <v>2.38</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
         <v>4.7</v>
@@ -1924,7 +1924,7 @@
         <v>2.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
         <v>11</v>
@@ -1945,7 +1945,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
         <v>25</v>
@@ -1978,7 +1978,7 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
         <v>9.6</v>
@@ -2044,31 +2044,31 @@
         <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BN6" t="n">
         <v>10.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BT6" t="n">
         <v>3.9</v>
@@ -2080,23 +2080,23 @@
         <v>12</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
         <v>29</v>
       </c>
       <c r="CA6" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -2184,7 +2184,7 @@
         <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z7" t="n">
         <v>34</v>
@@ -2193,7 +2193,7 @@
         <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7" t="n">
         <v>8.6</v>
@@ -2208,7 +2208,7 @@
         <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
@@ -2244,7 +2244,7 @@
         <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
@@ -2256,7 +2256,7 @@
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -2268,7 +2268,7 @@
         <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
         <v>17</v>
@@ -2277,80 +2277,80 @@
         <v>16</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO7" t="n">
         <v>4</v>
       </c>
-      <c r="BI7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BP7" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BQ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BR7" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>21</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="CA7" t="n">
-        <v>16.5</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -2438,13 +2438,13 @@
         <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AB8" t="n">
         <v>38</v>
@@ -2465,7 +2465,7 @@
         <v>44</v>
       </c>
       <c r="AH8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
         <v>48</v>
@@ -2486,7 +2486,7 @@
         <v>280</v>
       </c>
       <c r="AO8" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AP8" t="n">
         <v>13.5</v>
@@ -2504,7 +2504,7 @@
         <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AV8" t="n">
         <v>7.8</v>
@@ -2513,10 +2513,10 @@
         <v>11.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="AZ8" t="n">
         <v>16.5</v>
@@ -2525,19 +2525,19 @@
         <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>160</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
         <v>5.6</v>
@@ -2552,13 +2552,13 @@
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
         <v>13</v>
@@ -2570,13 +2570,13 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
         <v>3.9</v>
@@ -2588,23 +2588,23 @@
         <v>8.6</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="H9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
         <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2683,10 +2683,10 @@
         <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X9" t="n">
         <v>14.5</v>
@@ -2695,16 +2695,16 @@
         <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
         <v>17.5</v>
@@ -2725,7 +2725,7 @@
         <v>65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK9" t="n">
         <v>34</v>
@@ -2815,16 +2815,16 @@
         <v>21</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO9" t="n">
         <v>4</v>
       </c>
       <c r="BP9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2833,16 +2833,16 @@
         <v>24</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV9" t="n">
         <v>29</v>
       </c>
       <c r="BW9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -2913,28 +2913,28 @@
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V10" t="n">
         <v>1.25</v>
@@ -2988,10 +2988,10 @@
         <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN10" t="n">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="AO10" t="n">
         <v>100</v>
@@ -3027,7 +3027,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>1.03</v>
@@ -3054,7 +3054,7 @@
         <v>3.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3075,7 +3075,7 @@
         <v>3.65</v>
       </c>
       <c r="BP10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
         <v>11</v>
@@ -3084,7 +3084,7 @@
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BT10" t="n">
         <v>7.8</v>
@@ -3108,11 +3108,11 @@
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -3143,46 +3143,46 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
         <v>4.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P11" t="n">
         <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T11" t="n">
         <v>1.66</v>
@@ -3191,25 +3191,25 @@
         <v>2.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
         <v>38</v>
       </c>
       <c r="AB11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
         <v>9</v>
@@ -3233,7 +3233,7 @@
         <v>40</v>
       </c>
       <c r="AJ11" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK11" t="n">
         <v>42</v>
@@ -3245,13 +3245,13 @@
         <v>90</v>
       </c>
       <c r="AN11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO11" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>10.5</v>
@@ -3260,10 +3260,10 @@
         <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU11" t="n">
         <v>7.4</v>
@@ -3272,55 +3272,55 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ11" t="n">
         <v>9.4</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
         <v>6.8</v>
@@ -3329,44 +3329,44 @@
         <v>4.9</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ11" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
         <v>23</v>
       </c>
-      <c r="BT11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>22</v>
-      </c>
       <c r="CA11" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>5.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
@@ -3427,16 +3427,16 @@
         <v>1.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T12" t="n">
         <v>1.68</v>
@@ -3466,7 +3466,7 @@
         <v>15</v>
       </c>
       <c r="AC12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD12" t="n">
         <v>28</v>
@@ -3553,19 +3553,19 @@
         <v>34</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG12" t="n">
         <v>40</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ12" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="BK12" t="n">
         <v>6.2</v>
@@ -3574,53 +3574,53 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BS12" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BU12" t="n">
         <v>7</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY12" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BZ12" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="CA12" t="n">
         <v>6.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O13" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
         <v>1.07</v>
       </c>
       <c r="S13" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -3905,172 +3905,172 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G14" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="H14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K14" t="n">
         <v>5.7</v>
       </c>
-      <c r="I14" t="n">
-        <v>11</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6.2</v>
-      </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP14" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG14" t="n">
         <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4085,10 +4085,10 @@
         <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4162,10 +4162,10 @@
         <v>2.16</v>
       </c>
       <c r="G15" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
         <v>4.2</v>
@@ -4174,22 +4174,22 @@
         <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
         <v>2.04</v>
@@ -4201,7 +4201,7 @@
         <v>3.85</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U15" t="n">
         <v>2.02</v>
@@ -4210,16 +4210,16 @@
         <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
@@ -4231,7 +4231,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
         <v>55</v>
@@ -4267,55 +4267,55 @@
         <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
         <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
         <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
         <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
         <v>1.01</v>
@@ -4324,7 +4324,7 @@
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4342,7 +4342,7 @@
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4360,7 +4360,7 @@
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4413,46 +4413,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="G16" t="n">
         <v>3.65</v>
       </c>
       <c r="H16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I16" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P16" t="n">
         <v>1.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
         <v>1.9</v>
@@ -4461,112 +4461,112 @@
         <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W16" t="n">
         <v>1.37</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS16" t="n">
         <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -4575,13 +4575,13 @@
         <v>18</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK16" t="n">
         <v>1.01</v>
@@ -4593,13 +4593,13 @@
         <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ16" t="n">
         <v>1.01</v>
@@ -4611,32 +4611,32 @@
         <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW16" t="n">
         <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY16" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA16" t="n">
         <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4670,31 +4670,31 @@
         <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="J17" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="P17" t="n">
         <v>2.02</v>
@@ -4706,134 +4706,134 @@
         <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI17" t="n">
         <v>3.3</v>
       </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.96</v>
-      </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
@@ -4847,16 +4847,16 @@
         <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="G18" t="n">
         <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="G20" t="n">
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
@@ -5722,7 +5722,7 @@
         <v>1.07</v>
       </c>
       <c r="S21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G24" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H24" t="n">
         <v>2.64</v>
@@ -6511,7 +6511,7 @@
         <v>120</v>
       </c>
       <c r="AB24" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AC24" t="n">
         <v>11.5</v>
@@ -6556,7 +6556,7 @@
         <v>23</v>
       </c>
       <c r="AQ24" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR24" t="n">
         <v>17</v>
@@ -6592,7 +6592,7 @@
         <v>23</v>
       </c>
       <c r="BC24" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD24" t="n">
         <v>17</v>
@@ -6610,7 +6610,7 @@
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ24" t="n">
         <v>11</v>
@@ -6622,7 +6622,7 @@
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>21</v>
+        <v>2.16</v>
       </c>
       <c r="BN24" t="n">
         <v>8.6</v>
@@ -6634,13 +6634,13 @@
         <v>21</v>
       </c>
       <c r="BQ24" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BR24" t="n">
         <v>29</v>
       </c>
       <c r="BS24" t="n">
-        <v>13</v>
+        <v>2.06</v>
       </c>
       <c r="BT24" t="n">
         <v>9</v>
@@ -6652,23 +6652,23 @@
         <v>24</v>
       </c>
       <c r="BW24" t="n">
-        <v>11</v>
+        <v>2.04</v>
       </c>
       <c r="BX24" t="n">
         <v>30</v>
       </c>
       <c r="BY24" t="n">
-        <v>13.5</v>
+        <v>2.06</v>
       </c>
       <c r="BZ24" t="n">
         <v>16</v>
       </c>
       <c r="CA24" t="n">
-        <v>7.6</v>
+        <v>1.95</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6699,16 +6699,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>3.5</v>
@@ -6717,7 +6717,7 @@
         <v>3.75</v>
       </c>
       <c r="L25" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
@@ -6726,58 +6726,58 @@
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P25" t="n">
         <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R25" t="n">
         <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U25" t="n">
         <v>2.28</v>
       </c>
       <c r="V25" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W25" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="X25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA25" t="n">
         <v>55</v>
       </c>
       <c r="AB25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC25" t="n">
         <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE25" t="n">
         <v>36</v>
       </c>
       <c r="AF25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
         <v>12</v>
@@ -6789,25 +6789,25 @@
         <v>44</v>
       </c>
       <c r="AJ25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL25" t="n">
         <v>36</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>38</v>
       </c>
       <c r="AM25" t="n">
         <v>85</v>
       </c>
       <c r="AN25" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AP25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>12</v>
@@ -6828,34 +6828,34 @@
         <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC25" t="n">
         <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF25" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG25" t="n">
         <v>21</v>
@@ -6864,19 +6864,19 @@
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BJ25" t="n">
         <v>12.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.9</v>
+        <v>1.66</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>21</v>
+        <v>1.92</v>
       </c>
       <c r="BN25" t="n">
         <v>7.4</v>
@@ -6885,44 +6885,44 @@
         <v>3.8</v>
       </c>
       <c r="BP25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BQ25" t="n">
-        <v>11.5</v>
+        <v>1.77</v>
       </c>
       <c r="BR25" t="n">
         <v>40</v>
       </c>
       <c r="BS25" t="n">
-        <v>17.5</v>
+        <v>1.83</v>
       </c>
       <c r="BT25" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW25" t="n">
-        <v>14.5</v>
+        <v>1.82</v>
       </c>
       <c r="BX25" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY25" t="n">
-        <v>20</v>
+        <v>1.85</v>
       </c>
       <c r="BZ25" t="n">
         <v>32</v>
       </c>
       <c r="CA25" t="n">
-        <v>14.5</v>
+        <v>1.81</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G26" t="n">
         <v>3.15</v>
@@ -6971,7 +6971,7 @@
         <v>3.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
@@ -7115,68 +7115,68 @@
         <v>16.5</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BR26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX26" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -7213,16 +7213,16 @@
         <v>2.44</v>
       </c>
       <c r="H27" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>2.58</v>
+        <v>1.7</v>
       </c>
       <c r="K27" t="n">
-        <v>15</v>
+        <v>4.9</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7258,7 +7258,7 @@
         <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X27" t="n">
         <v>36</v>
@@ -7315,19 +7315,19 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR27" t="n">
         <v>23</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AU27" t="n">
         <v>7</v>
@@ -7363,7 +7363,7 @@
         <v>36</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG27" t="n">
         <v>10.5</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         <v>2.28</v>
       </c>
       <c r="J28" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K28" t="n">
         <v>4.2</v>
@@ -7632,13 +7632,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK28" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN28" t="n">
         <v>7.2</v>
@@ -7647,16 +7647,16 @@
         <v>5.4</v>
       </c>
       <c r="BP28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ28" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR28" t="n">
         <v>34</v>
       </c>
       <c r="BS28" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BT28" t="n">
         <v>5.5</v>
@@ -7665,16 +7665,16 @@
         <v>4.2</v>
       </c>
       <c r="BV28" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BW28" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BX28" t="n">
         <v>26</v>
       </c>
       <c r="BY28" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
         <v>5.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
@@ -7877,13 +7877,13 @@
         <v>10</v>
       </c>
       <c r="BH29" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ29" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BK29" t="n">
         <v>7.6</v>
@@ -7892,53 +7892,53 @@
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="BN29" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="BO29" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="BP29" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ29" t="n">
         <v>5.3</v>
       </c>
       <c r="BR29" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BS29" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="BT29" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BU29" t="n">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BZ29" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA29" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -7969,19 +7969,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
         <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
         <v>1000</v>
@@ -8235,7 +8235,7 @@
         <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K31" t="n">
         <v>950</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
         <v>3.95</v>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
         <v>3.85</v>
@@ -8495,7 +8495,7 @@
         <v>3.9</v>
       </c>
       <c r="L32" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
@@ -8525,7 +8525,7 @@
         <v>2.22</v>
       </c>
       <c r="V32" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W32" t="n">
         <v>1.94</v>
@@ -8639,13 +8639,13 @@
         <v>8</v>
       </c>
       <c r="BH32" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ32" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK32" t="n">
         <v>5.9</v>
@@ -8657,50 +8657,50 @@
         <v>21</v>
       </c>
       <c r="BN32" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP32" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BQ32" t="n">
         <v>8.4</v>
       </c>
       <c r="BR32" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BS32" t="n">
         <v>16</v>
       </c>
       <c r="BT32" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BU32" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV32" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BW32" t="n">
         <v>21</v>
       </c>
       <c r="BX32" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY32" t="n">
         <v>21</v>
       </c>
       <c r="BZ32" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="CA32" t="n">
         <v>13</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -8985,25 +8985,25 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G34" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H34" t="n">
         <v>5.1</v>
       </c>
       <c r="I34" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J34" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K34" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M34" t="n">
         <v>1.1</v>
@@ -9012,31 +9012,31 @@
         <v>2.84</v>
       </c>
       <c r="O34" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P34" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R34" t="n">
         <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T34" t="n">
         <v>2.18</v>
       </c>
       <c r="U34" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="V34" t="n">
         <v>1.17</v>
       </c>
       <c r="W34" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X34" t="n">
         <v>12</v>
@@ -9057,7 +9057,7 @@
         <v>10.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE34" t="n">
         <v>1000</v>
@@ -9069,7 +9069,7 @@
         <v>14.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI34" t="n">
         <v>1000</v>
@@ -9078,61 +9078,61 @@
         <v>25</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
         <v>1.03</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
         <v>1.03</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
         <v>1.03</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
         <v>1.03</v>
@@ -9141,7 +9141,7 @@
         <v>1.03</v>
       </c>
       <c r="BF34" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
         <v>1.01</v>
@@ -9150,13 +9150,13 @@
         <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ34" t="n">
         <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
@@ -9168,25 +9168,25 @@
         <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BT34" t="n">
         <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
@@ -9204,11 +9204,11 @@
         <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -9239,112 +9239,112 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="G35" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="H35" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="I35" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="J35" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M35" t="n">
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P35" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="Q35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T35" t="n">
         <v>1.56</v>
       </c>
-      <c r="R35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.53</v>
-      </c>
       <c r="U35" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V35" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W35" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="X35" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Y35" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="Z35" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AA35" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AB35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF35" t="n">
         <v>15</v>
       </c>
-      <c r="AC35" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF35" t="n">
+      <c r="AG35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK35" t="n">
         <v>18</v>
       </c>
-      <c r="AG35" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>22</v>
-      </c>
       <c r="AL35" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AM35" t="n">
         <v>70</v>
       </c>
       <c r="AN35" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO35" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AP35" t="n">
         <v>6.4</v>
@@ -9353,116 +9353,116 @@
         <v>6</v>
       </c>
       <c r="AR35" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW35" t="n">
         <v>7.6</v>
       </c>
-      <c r="AT35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE35" t="n">
+      <c r="BX35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY35" t="n">
         <v>7.8</v>
       </c>
-      <c r="BF35" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BJ35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO35" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY35" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BZ35" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G36" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H36" t="n">
         <v>9.199999999999999</v>
@@ -9517,7 +9517,7 @@
         <v>1.03</v>
       </c>
       <c r="N36" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O36" t="n">
         <v>1.19</v>
@@ -9532,7 +9532,7 @@
         <v>1.63</v>
       </c>
       <c r="S36" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T36" t="n">
         <v>1.92</v>
@@ -9604,7 +9604,7 @@
         <v>20</v>
       </c>
       <c r="AQ36" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR36" t="n">
         <v>7.4</v>
@@ -9619,7 +9619,7 @@
         <v>11.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW36" t="n">
         <v>7.4</v>
@@ -9643,7 +9643,7 @@
         <v>12</v>
       </c>
       <c r="BD36" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE36" t="n">
         <v>7.2</v>
@@ -9664,13 +9664,13 @@
         <v>11.5</v>
       </c>
       <c r="BK36" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN36" t="n">
         <v>4.2</v>
@@ -9688,25 +9688,25 @@
         <v>22</v>
       </c>
       <c r="BS36" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BT36" t="n">
         <v>13.5</v>
       </c>
       <c r="BU36" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BV36" t="n">
         <v>80</v>
       </c>
       <c r="BW36" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX36" t="n">
         <v>70</v>
       </c>
       <c r="BY36" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BZ36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -9750,22 +9750,22 @@
         <v>2.86</v>
       </c>
       <c r="G37" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I37" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J37" t="n">
         <v>3.45</v>
       </c>
       <c r="K37" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L37" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M37" t="n">
         <v>1.07</v>
@@ -9774,37 +9774,37 @@
         <v>3.7</v>
       </c>
       <c r="O37" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P37" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U37" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V37" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W37" t="n">
         <v>1.5</v>
       </c>
       <c r="X37" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z37" t="n">
         <v>18.5</v>
@@ -9813,13 +9813,13 @@
         <v>40</v>
       </c>
       <c r="AB37" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD37" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE37" t="n">
         <v>34</v>
@@ -9828,7 +9828,7 @@
         <v>21</v>
       </c>
       <c r="AG37" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH37" t="n">
         <v>18</v>
@@ -9855,25 +9855,25 @@
         <v>27</v>
       </c>
       <c r="AP37" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR37" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT37" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV37" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW37" t="n">
         <v>21</v>
@@ -9882,85 +9882,85 @@
         <v>16.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BC37" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BF37" t="n">
         <v>21</v>
       </c>
       <c r="BG37" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BH37" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI37" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BJ37" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK37" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN37" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO37" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP37" t="n">
         <v>24</v>
       </c>
       <c r="BQ37" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BR37" t="n">
         <v>36</v>
       </c>
       <c r="BS37" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BT37" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU37" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BV37" t="n">
         <v>21</v>
       </c>
       <c r="BW37" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BX37" t="n">
         <v>34</v>
       </c>
       <c r="BY37" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BZ37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10007,7 @@
         <v>3.4</v>
       </c>
       <c r="H38" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I38" t="n">
         <v>2.26</v>
@@ -10016,10 +10016,10 @@
         <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M38" t="n">
         <v>1.03</v>
@@ -10034,7 +10034,7 @@
         <v>2.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R38" t="n">
         <v>1.65</v>
@@ -10052,7 +10052,7 @@
         <v>1.79</v>
       </c>
       <c r="W38" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X38" t="n">
         <v>26</v>
@@ -10073,7 +10073,7 @@
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE38" t="n">
         <v>21</v>
@@ -10085,13 +10085,13 @@
         <v>15</v>
       </c>
       <c r="AH38" t="n">
-        <v>550</v>
+        <v>300</v>
       </c>
       <c r="AI38" t="n">
         <v>27</v>
       </c>
       <c r="AJ38" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK38" t="n">
         <v>32</v>
@@ -10103,22 +10103,22 @@
         <v>55</v>
       </c>
       <c r="AN38" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO38" t="n">
         <v>11</v>
       </c>
       <c r="AP38" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AQ38" t="n">
         <v>13</v>
       </c>
       <c r="AR38" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT38" t="n">
         <v>16.5</v>
@@ -10130,46 +10130,46 @@
         <v>10</v>
       </c>
       <c r="AW38" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY38" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AZ38" t="n">
         <v>13</v>
       </c>
       <c r="BA38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB38" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BD38" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG38" t="n">
         <v>9.4</v>
       </c>
       <c r="BH38" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ38" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK38" t="n">
         <v>1.01</v>
@@ -10181,10 +10181,10 @@
         <v>1.01</v>
       </c>
       <c r="BN38" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BP38" t="n">
         <v>1000</v>
@@ -10199,13 +10199,13 @@
         <v>1.01</v>
       </c>
       <c r="BT38" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV38" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -10515,10 +10515,10 @@
         <v>6.4</v>
       </c>
       <c r="H40" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I40" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>4.7</v>
@@ -10557,10 +10557,10 @@
         <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X40" t="n">
         <v>36</v>
@@ -10572,7 +10572,7 @@
         <v>13</v>
       </c>
       <c r="AA40" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AB40" t="n">
         <v>38</v>
@@ -10617,7 +10617,7 @@
         <v>5.7</v>
       </c>
       <c r="AP40" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ40" t="n">
         <v>11.5</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -10763,13 +10763,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="G41" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H41" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I41" t="n">
         <v>5.2</v>
@@ -10799,7 +10799,7 @@
         <v>1.76</v>
       </c>
       <c r="R41" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S41" t="n">
         <v>2.9</v>
@@ -10826,16 +10826,16 @@
         <v>38</v>
       </c>
       <c r="AA41" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB41" t="n">
         <v>12</v>
       </c>
       <c r="AC41" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE41" t="n">
         <v>65</v>
@@ -10859,28 +10859,28 @@
         <v>21</v>
       </c>
       <c r="AL41" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM41" t="n">
         <v>100</v>
       </c>
       <c r="AN41" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AO41" t="n">
         <v>65</v>
       </c>
       <c r="AP41" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ41" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AR41" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AS41" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT41" t="n">
         <v>9</v>
@@ -10889,40 +10889,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV41" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AW41" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX41" t="n">
         <v>9</v>
       </c>
       <c r="AY41" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ41" t="n">
         <v>14.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB41" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BC41" t="n">
         <v>13.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BE41" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF41" t="n">
         <v>8.4</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH41" t="n">
         <v>3.9</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
         <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -11271,25 +11271,25 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G43" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H43" t="n">
         <v>4.6</v>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J43" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K43" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M43" t="n">
         <v>1.05</v>
@@ -11304,19 +11304,19 @@
         <v>2.12</v>
       </c>
       <c r="Q43" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="n">
         <v>1.76</v>
       </c>
-      <c r="R43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.75</v>
-      </c>
       <c r="U43" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V43" t="n">
         <v>1.24</v>
@@ -11385,7 +11385,7 @@
         <v>16.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS43" t="n">
         <v>4.2</v>
@@ -11400,7 +11400,7 @@
         <v>14</v>
       </c>
       <c r="AW43" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AX43" t="n">
         <v>10.5</v>
@@ -11412,7 +11412,7 @@
         <v>16</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB43" t="n">
         <v>17</v>
@@ -11421,16 +11421,16 @@
         <v>16</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BE43" t="n">
         <v>4.2</v>
       </c>
       <c r="BF43" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG43" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH43" t="n">
         <v>3.75</v>
@@ -11442,59 +11442,59 @@
         <v>9.6</v>
       </c>
       <c r="BK43" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BN43" t="n">
         <v>4.6</v>
       </c>
       <c r="BO43" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP43" t="n">
         <v>12</v>
       </c>
       <c r="BQ43" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BR43" t="n">
         <v>25</v>
       </c>
       <c r="BS43" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="BT43" t="n">
         <v>8.4</v>
       </c>
       <c r="BU43" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>27</v>
+        <v>11.5</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="BZ43" t="n">
         <v>19.5</v>
       </c>
       <c r="CA43" t="n">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -11525,19 +11525,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="G44" t="n">
         <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G45" t="n">
         <v>3.35</v>
@@ -11788,22 +11788,22 @@
         <v>2.52</v>
       </c>
       <c r="I45" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J45" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
         <v>3.5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M45" t="n">
         <v>1.1</v>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O45" t="n">
         <v>1.43</v>
@@ -11812,7 +11812,7 @@
         <v>1.64</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R45" t="n">
         <v>1.23</v>
@@ -11821,13 +11821,13 @@
         <v>4.3</v>
       </c>
       <c r="T45" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U45" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V45" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W45" t="n">
         <v>1.42</v>
@@ -11836,7 +11836,7 @@
         <v>13</v>
       </c>
       <c r="Y45" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z45" t="n">
         <v>17.5</v>
@@ -11887,16 +11887,16 @@
         <v>42</v>
       </c>
       <c r="AP45" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ45" t="n">
         <v>4.3</v>
       </c>
       <c r="AR45" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT45" t="n">
         <v>8.6</v>
@@ -11905,104 +11905,104 @@
         <v>6.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW45" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN45" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX45" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG45" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ45" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK45" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM45" t="n">
-        <v>21</v>
-      </c>
-      <c r="BN45" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BO45" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="BP45" t="n">
         <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR45" t="n">
         <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT45" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW45" t="n">
         <v>7.6</v>
       </c>
-      <c r="BU45" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BV45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW45" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BX45" t="n">
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BZ45" t="n">
         <v>1000</v>
       </c>
       <c r="CA45" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G46" t="n">
         <v>5</v>
@@ -12063,10 +12063,10 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -12314,19 +12314,19 @@
         <v>1.08</v>
       </c>
       <c r="O47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P47" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q47" t="n">
         <v>1.05</v>
       </c>
       <c r="R47" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S47" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12571,7 @@
         <v>1.34</v>
       </c>
       <c r="P48" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q48" t="n">
         <v>1.95</v>
@@ -12580,7 +12580,7 @@
         <v>1.33</v>
       </c>
       <c r="S48" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T48" t="n">
         <v>1.84</v>
@@ -12706,40 +12706,40 @@
         <v>1000</v>
       </c>
       <c r="BI48" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BJ48" t="n">
         <v>15</v>
       </c>
       <c r="BK48" t="n">
-        <v>6.2</v>
+        <v>1.61</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="BN48" t="n">
         <v>11</v>
       </c>
       <c r="BO48" t="n">
-        <v>5.9</v>
+        <v>1.55</v>
       </c>
       <c r="BP48" t="n">
         <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>21</v>
+        <v>1.75</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>21</v>
+        <v>1.76</v>
       </c>
       <c r="BT48" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU48" t="n">
         <v>3.45</v>
@@ -12748,23 +12748,23 @@
         <v>20</v>
       </c>
       <c r="BW48" t="n">
-        <v>9.6</v>
+        <v>1.65</v>
       </c>
       <c r="BX48" t="n">
         <v>44</v>
       </c>
       <c r="BY48" t="n">
-        <v>17.5</v>
+        <v>1.73</v>
       </c>
       <c r="BZ48" t="n">
         <v>38</v>
       </c>
       <c r="CA48" t="n">
-        <v>15.5</v>
+        <v>1.72</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -12831,10 +12831,10 @@
         <v>1.32</v>
       </c>
       <c r="R49" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S49" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T49" t="n">
         <v>1.01</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -13079,10 +13079,10 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -13303,13 +13303,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G51" t="n">
         <v>1000</v>
       </c>
       <c r="H51" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="I51" t="n">
         <v>1000</v>
@@ -13327,7 +13327,7 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="O51" t="n">
         <v>1.02</v>
@@ -13339,7 +13339,7 @@
         <v>1.3</v>
       </c>
       <c r="R51" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="S51" t="n">
         <v>1.3</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -13566,7 +13566,7 @@
         <v>3.4</v>
       </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
         <v>2.82</v>
@@ -13575,13 +13575,13 @@
         <v>3.3</v>
       </c>
       <c r="L52" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M52" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N52" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="O52" t="n">
         <v>1.56</v>
@@ -13593,16 +13593,16 @@
         <v>2.72</v>
       </c>
       <c r="R52" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S52" t="n">
-        <v>2.72</v>
+        <v>5.7</v>
       </c>
       <c r="T52" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U52" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="V52" t="n">
         <v>1.33</v>
@@ -13611,176 +13611,176 @@
         <v>1.59</v>
       </c>
       <c r="X52" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA52" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB52" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC52" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD52" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE52" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF52" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG52" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI52" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK52" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL52" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM52" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN52" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO52" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.11</v>
+        <v>7</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.11</v>
+        <v>17.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.11</v>
+        <v>5.5</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.11</v>
+        <v>5.4</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.11</v>
+        <v>12</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.11</v>
+        <v>4.4</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.11</v>
+        <v>10.5</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.11</v>
+        <v>9.4</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.11</v>
+        <v>18</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.11</v>
+        <v>4.2</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.11</v>
+        <v>4.4</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.11</v>
+        <v>4.6</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="BH52" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="BJ52" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN52" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP52" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR52" t="n">
         <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT52" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV52" t="n">
         <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX52" t="n">
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ52" t="n">
         <v>1000</v>
       </c>
       <c r="CA52" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -857,46 +857,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.16</v>
+        <v>1.87</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.16</v>
+        <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.09</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.4</v>
+        <v>2.26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.73</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1180,7 +1180,7 @@
         <v>8</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>29</v>
@@ -1219,19 +1219,19 @@
         <v>200</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
@@ -1240,19 +1240,19 @@
         <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB3" t="n">
         <v>12.5</v>
@@ -1261,25 +1261,25 @@
         <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G4" t="n">
         <v>2.14</v>
@@ -1374,7 +1374,7 @@
         <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
@@ -1383,7 +1383,7 @@
         <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1413,7 +1413,7 @@
         <v>1.94</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
         <v>1.87</v>
@@ -1443,7 +1443,7 @@
         <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
@@ -1476,7 +1476,7 @@
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR4" t="n">
         <v>25</v>
@@ -1491,7 +1491,7 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW4" t="n">
         <v>11</v>
@@ -1569,7 +1569,7 @@
         <v>5.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -1661,13 +1661,13 @@
         <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U5" t="n">
         <v>2.16</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
         <v>1.54</v>
@@ -1721,10 +1721,10 @@
         <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP5" t="n">
         <v>12</v>
@@ -1736,7 +1736,7 @@
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1760,19 +1760,19 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC5" t="n">
         <v>8</v>
       </c>
-      <c r="BC5" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BD5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
         <v>19.5</v>
@@ -1784,7 +1784,7 @@
         <v>3.45</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="G6" t="n">
         <v>7.4</v>
@@ -1885,7 +1885,7 @@
         <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
@@ -1924,7 +1924,7 @@
         <v>2.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
         <v>11</v>
@@ -1948,10 +1948,10 @@
         <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF6" t="n">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="AG6" t="n">
         <v>32</v>
@@ -1993,7 +1993,7 @@
         <v>14.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU6" t="n">
         <v>8</v>
@@ -2002,7 +2002,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX6" t="n">
         <v>27</v>
@@ -2038,37 +2038,37 @@
         <v>2.98</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BN6" t="n">
         <v>10.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BT6" t="n">
         <v>3.9</v>
@@ -2077,26 +2077,26 @@
         <v>3.55</v>
       </c>
       <c r="BV6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
       </c>
       <c r="BY6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>28</v>
+      </c>
+      <c r="CA6" t="n">
         <v>11</v>
       </c>
-      <c r="BZ6" t="n">
-        <v>29</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>2.08</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>4.7</v>
@@ -2145,7 +2145,7 @@
         <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -2184,7 +2184,7 @@
         <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
         <v>34</v>
@@ -2193,7 +2193,7 @@
         <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
         <v>8.6</v>
@@ -2238,55 +2238,55 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU7" t="n">
         <v>7</v>
       </c>
       <c r="AV7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF7" t="n">
         <v>13</v>
       </c>
-      <c r="AW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH7" t="n">
         <v>3.4</v>
@@ -2316,7 +2316,7 @@
         <v>15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="BR7" t="n">
         <v>32</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G8" t="n">
         <v>11</v>
@@ -2426,7 +2426,7 @@
         <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V8" t="n">
         <v>3.2</v>
@@ -2444,7 +2444,7 @@
         <v>8.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AB8" t="n">
         <v>38</v>
@@ -2456,7 +2456,7 @@
         <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF8" t="n">
         <v>110</v>
@@ -2489,22 +2489,22 @@
         <v>6.6</v>
       </c>
       <c r="AP8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR8" t="n">
         <v>7.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
         <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AV8" t="n">
         <v>7.8</v>
@@ -2549,7 +2549,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
         <v>1.01</v>
@@ -2597,14 +2597,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA8" t="n">
         <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>3.15</v>
       </c>
       <c r="I9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J9" t="n">
         <v>3.35</v>
@@ -2653,7 +2653,7 @@
         <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2665,7 +2665,7 @@
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
         <v>2.1</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
         <v>17.5</v>
@@ -2743,31 +2743,31 @@
         <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
         <v>7.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AV9" t="n">
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY9" t="n">
         <v>8.6</v>
@@ -2776,7 +2776,7 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
         <v>1.03</v>
@@ -2785,34 +2785,34 @@
         <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>17</v>
       </c>
       <c r="BG9" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
         <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="BN9" t="n">
         <v>5.5</v>
@@ -2824,13 +2824,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="BT9" t="n">
         <v>6.6</v>
@@ -2842,23 +2842,23 @@
         <v>29</v>
       </c>
       <c r="BW9" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>29</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G10" t="n">
         <v>2.04</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
@@ -2910,7 +2910,7 @@
         <v>1.46</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
         <v>3.25</v>
@@ -2919,7 +2919,7 @@
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
         <v>2.12</v>
@@ -2928,7 +2928,7 @@
         <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T10" t="n">
         <v>1.92</v>
@@ -2955,16 +2955,16 @@
         <v>130</v>
       </c>
       <c r="AB10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC10" t="n">
         <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="n">
         <v>12</v>
@@ -2973,7 +2973,7 @@
         <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
         <v>90</v>
@@ -2982,31 +2982,31 @@
         <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AT10" t="n">
         <v>6.2</v>
@@ -3015,76 +3015,76 @@
         <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD10" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>65</v>
+        <v>8.4</v>
       </c>
       <c r="BH10" t="n">
         <v>3.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
         <v>4.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
         <v>7.8</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -3149,16 +3149,16 @@
         <v>3.35</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I11" t="n">
         <v>2.48</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.35</v>
@@ -3167,7 +3167,7 @@
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
         <v>1.27</v>
@@ -3176,16 +3176,16 @@
         <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R11" t="n">
         <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="T11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
         <v>2.32</v>
@@ -3194,7 +3194,7 @@
         <v>1.67</v>
       </c>
       <c r="W11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X11" t="n">
         <v>17.5</v>
@@ -3212,7 +3212,7 @@
         <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
         <v>12</v>
@@ -3260,7 +3260,7 @@
         <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT11" t="n">
         <v>12.5</v>
@@ -3272,43 +3272,43 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH11" t="n">
         <v>3.85</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="BJ11" t="n">
         <v>9.4</v>
@@ -3326,7 +3326,7 @@
         <v>6.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP11" t="n">
         <v>24</v>
@@ -3347,7 +3347,7 @@
         <v>4.7</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BW11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>5.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
@@ -3433,10 +3433,10 @@
         <v>1.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T12" t="n">
         <v>1.68</v>
@@ -3568,7 +3568,7 @@
         <v>9.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3616,11 +3616,11 @@
         <v>10</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
         <v>1.07</v>
       </c>
       <c r="S13" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>5.4</v>
       </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J14" t="n">
         <v>4.2</v>
@@ -3944,7 +3944,7 @@
         <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
         <v>1.79</v>
@@ -3992,22 +3992,22 @@
         <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ14" t="n">
         <v>18</v>
       </c>
       <c r="AK14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM14" t="n">
         <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO14" t="n">
         <v>120</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -4159,25 +4159,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I15" t="n">
         <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
@@ -4207,10 +4207,10 @@
         <v>2.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X15" t="n">
         <v>14</v>
@@ -4267,76 +4267,76 @@
         <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
         <v>7</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
@@ -4348,13 +4348,13 @@
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         <v>1.41</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
         <v>2.22</v>
@@ -4455,10 +4455,10 @@
         <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="V16" t="n">
         <v>1.74</v>
@@ -4515,7 +4515,7 @@
         <v>150</v>
       </c>
       <c r="AN16" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AO16" t="n">
         <v>28</v>
@@ -4524,13 +4524,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR16" t="n">
         <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT16" t="n">
         <v>9.199999999999999</v>
@@ -4539,7 +4539,7 @@
         <v>5.9</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW16" t="n">
         <v>20</v>
@@ -4554,22 +4554,22 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG16" t="n">
         <v>18</v>
@@ -4578,19 +4578,19 @@
         <v>3.05</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BN16" t="n">
         <v>6.8</v>
@@ -4602,13 +4602,13 @@
         <v>34</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BT16" t="n">
         <v>5</v>
@@ -4620,23 +4620,23 @@
         <v>18</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX16" t="n">
         <v>36</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ16" t="n">
         <v>36</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
         <v>6.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -4700,7 +4700,7 @@
         <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
         <v>1.39</v>
@@ -4802,7 +4802,7 @@
         <v>5.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ17" t="n">
         <v>1.03</v>
@@ -4832,7 +4832,7 @@
         <v>3.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -5456,13 +5456,13 @@
         <v>1.08</v>
       </c>
       <c r="O20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="P20" t="n">
         <v>1.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
         <v>1.07</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -5683,19 +5683,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5722,7 +5722,7 @@
         <v>1.07</v>
       </c>
       <c r="S21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G24" t="n">
         <v>2.56</v>
@@ -6463,7 +6463,7 @@
         <v>4.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
@@ -6481,13 +6481,13 @@
         <v>1.41</v>
       </c>
       <c r="R24" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S24" t="n">
         <v>2.06</v>
       </c>
       <c r="T24" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U24" t="n">
         <v>3.15</v>
@@ -6511,7 +6511,7 @@
         <v>120</v>
       </c>
       <c r="AB24" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AC24" t="n">
         <v>11.5</v>
@@ -6559,7 +6559,7 @@
         <v>18.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
         <v>25</v>
@@ -6571,10 +6571,10 @@
         <v>10</v>
       </c>
       <c r="AV24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AX24" t="n">
         <v>16.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
         <v>3.2</v>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J25" t="n">
         <v>3.5</v>
@@ -6717,7 +6717,7 @@
         <v>3.75</v>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
@@ -6729,25 +6729,25 @@
         <v>1.29</v>
       </c>
       <c r="P25" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
         <v>1.86</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
         <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U25" t="n">
         <v>2.28</v>
       </c>
       <c r="V25" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
         <v>1.69</v>
@@ -6756,7 +6756,7 @@
         <v>18.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z25" t="n">
         <v>25</v>
@@ -6765,7 +6765,7 @@
         <v>55</v>
       </c>
       <c r="AB25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC25" t="n">
         <v>8.4</v>
@@ -6816,19 +6816,19 @@
         <v>18.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="AT25" t="n">
         <v>10</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX25" t="n">
         <v>13.5</v>
@@ -6837,22 +6837,22 @@
         <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC25" t="n">
         <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF25" t="n">
         <v>14.5</v>
@@ -6882,7 +6882,7 @@
         <v>7.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP25" t="n">
         <v>23</v>
@@ -6903,10 +6903,10 @@
         <v>4.4</v>
       </c>
       <c r="BV25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="BX25" t="n">
         <v>48</v>
@@ -6915,14 +6915,14 @@
         <v>1.85</v>
       </c>
       <c r="BZ25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6953,19 +6953,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="H26" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="I26" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="J26" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
         <v>3.7</v>
@@ -6977,7 +6977,7 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.28</v>
@@ -6986,7 +6986,7 @@
         <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R26" t="n">
         <v>1.43</v>
@@ -6998,13 +6998,13 @@
         <v>1.68</v>
       </c>
       <c r="U26" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V26" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W26" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="X26" t="n">
         <v>19</v>
@@ -7016,7 +7016,7 @@
         <v>20</v>
       </c>
       <c r="AA26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB26" t="n">
         <v>16</v>
@@ -7025,10 +7025,10 @@
         <v>8.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF26" t="n">
         <v>26</v>
@@ -7055,10 +7055,10 @@
         <v>90</v>
       </c>
       <c r="AN26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
         <v>14.5</v>
@@ -7070,7 +7070,7 @@
         <v>15</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT26" t="n">
         <v>12</v>
@@ -7082,7 +7082,7 @@
         <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX26" t="n">
         <v>19</v>
@@ -7094,34 +7094,34 @@
         <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC26" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF26" t="n">
         <v>20</v>
       </c>
       <c r="BG26" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH26" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI26" t="n">
         <v>3.3</v>
       </c>
       <c r="BJ26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK26" t="n">
         <v>5.8</v>
@@ -7130,53 +7130,53 @@
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ26" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS26" t="n">
         <v>11</v>
       </c>
       <c r="BT26" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV26" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW26" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX26" t="n">
         <v>29</v>
       </c>
       <c r="BY26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ26" t="n">
         <v>23</v>
       </c>
       <c r="CA26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G27" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H27" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
-        <v>1.7</v>
+        <v>2.72</v>
       </c>
       <c r="K27" t="n">
         <v>4.9</v>
@@ -7255,10 +7255,10 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X27" t="n">
         <v>36</v>
@@ -7267,22 +7267,22 @@
         <v>34</v>
       </c>
       <c r="Z27" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA27" t="n">
-        <v>720</v>
+        <v>610</v>
       </c>
       <c r="AB27" t="n">
         <v>24</v>
       </c>
       <c r="AC27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD27" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AE27" t="n">
-        <v>780</v>
+        <v>670</v>
       </c>
       <c r="AF27" t="n">
         <v>25</v>
@@ -7291,7 +7291,7 @@
         <v>32</v>
       </c>
       <c r="AH27" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
@@ -7303,7 +7303,7 @@
         <v>170</v>
       </c>
       <c r="AL27" t="n">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
@@ -7315,19 +7315,19 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR27" t="n">
         <v>23</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AU27" t="n">
         <v>7</v>
@@ -7339,7 +7339,7 @@
         <v>21</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY27" t="n">
         <v>8.6</v>
@@ -7351,7 +7351,7 @@
         <v>22</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC27" t="n">
         <v>12.5</v>
@@ -7363,7 +7363,7 @@
         <v>36</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG27" t="n">
         <v>10.5</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -7461,43 +7461,43 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I28" t="n">
         <v>2.28</v>
       </c>
       <c r="J28" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
         <v>1.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S28" t="n">
         <v>2.74</v>
@@ -7506,25 +7506,25 @@
         <v>1.62</v>
       </c>
       <c r="U28" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="V28" t="n">
         <v>1.78</v>
       </c>
       <c r="W28" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X28" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="n">
         <v>13</v>
       </c>
       <c r="Z28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA28" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB28" t="n">
         <v>17</v>
@@ -7536,13 +7536,13 @@
         <v>11.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF28" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AG28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH28" t="n">
         <v>16.5</v>
@@ -7551,40 +7551,40 @@
         <v>32</v>
       </c>
       <c r="AJ28" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK28" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL28" t="n">
         <v>42</v>
       </c>
       <c r="AM28" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AO28" t="n">
         <v>13.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR28" t="n">
         <v>13.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="AT28" t="n">
         <v>14</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
         <v>10</v>
@@ -7593,31 +7593,31 @@
         <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="AY28" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BC28" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BE28" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="BF28" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BG28" t="n">
         <v>11.5</v>
@@ -7647,7 +7647,7 @@
         <v>5.4</v>
       </c>
       <c r="BP28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ28" t="n">
         <v>1.01</v>
@@ -7665,7 +7665,7 @@
         <v>4.2</v>
       </c>
       <c r="BV28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G29" t="n">
         <v>1.41</v>
@@ -7724,22 +7724,22 @@
         <v>9.6</v>
       </c>
       <c r="I29" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J29" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K29" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
         <v>1.24</v>
@@ -7748,19 +7748,19 @@
         <v>2.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S29" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="T29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U29" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V29" t="n">
         <v>1.1</v>
@@ -7769,31 +7769,31 @@
         <v>3.4</v>
       </c>
       <c r="X29" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y29" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z29" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD29" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AE29" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG29" t="n">
         <v>11</v>
@@ -7802,49 +7802,49 @@
         <v>30</v>
       </c>
       <c r="AI29" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
         <v>11.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL29" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM29" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AO29" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>19.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AS29" t="n">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="AT29" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AW29" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="AX29" t="n">
         <v>7.6</v>
@@ -7853,31 +7853,31 @@
         <v>9.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>8.6</v>
+        <v>19</v>
       </c>
       <c r="BA29" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB29" t="n">
         <v>10</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BC29" t="n">
         <v>13</v>
       </c>
       <c r="BD29" t="n">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BE29" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="BF29" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG29" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="BH29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI29" t="n">
         <v>3.3</v>
@@ -7886,13 +7886,13 @@
         <v>12.5</v>
       </c>
       <c r="BK29" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN29" t="n">
         <v>3.95</v>
@@ -7901,7 +7901,7 @@
         <v>3.35</v>
       </c>
       <c r="BP29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BQ29" t="n">
         <v>5.3</v>
@@ -7910,35 +7910,35 @@
         <v>25</v>
       </c>
       <c r="BS29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BU29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ29" t="n">
         <v>13.5</v>
       </c>
       <c r="CA29" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G32" t="n">
         <v>2.06</v>
       </c>
       <c r="H32" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I32" t="n">
         <v>4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K32" t="n">
         <v>3.9</v>
@@ -8501,28 +8501,28 @@
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O32" t="n">
         <v>1.28</v>
       </c>
       <c r="P32" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
         <v>3.1</v>
       </c>
       <c r="T32" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U32" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V32" t="n">
         <v>1.33</v>
@@ -8540,31 +8540,31 @@
         <v>32</v>
       </c>
       <c r="AA32" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
         <v>11</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AF32" t="n">
         <v>13.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH32" t="n">
         <v>18</v>
       </c>
       <c r="AI32" t="n">
-        <v>65</v>
+        <v>240</v>
       </c>
       <c r="AJ32" t="n">
         <v>25</v>
@@ -8576,49 +8576,49 @@
         <v>38</v>
       </c>
       <c r="AM32" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
         <v>13.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AP32" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ32" t="n">
         <v>14</v>
       </c>
       <c r="AR32" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="AT32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW32" t="n">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="AX32" t="n">
         <v>12</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ32" t="n">
         <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BB32" t="n">
         <v>20</v>
@@ -8627,16 +8627,16 @@
         <v>18</v>
       </c>
       <c r="BD32" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BE32" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="BF32" t="n">
         <v>11.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BH32" t="n">
         <v>3.8</v>
@@ -8654,7 +8654,7 @@
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="BN32" t="n">
         <v>5.1</v>
@@ -8672,10 +8672,10 @@
         <v>27</v>
       </c>
       <c r="BS32" t="n">
-        <v>16</v>
+        <v>7.6</v>
       </c>
       <c r="BT32" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU32" t="n">
         <v>4.8</v>
@@ -8684,23 +8684,23 @@
         <v>32</v>
       </c>
       <c r="BW32" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BX32" t="n">
         <v>42</v>
       </c>
       <c r="BY32" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BZ32" t="n">
         <v>23</v>
       </c>
       <c r="CA32" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
         <v>7.4</v>
       </c>
       <c r="J34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K34" t="n">
         <v>4</v>
@@ -9009,7 +9009,7 @@
         <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O34" t="n">
         <v>1.47</v>
@@ -9024,7 +9024,7 @@
         <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="T34" t="n">
         <v>2.18</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G35" t="n">
         <v>1.96</v>
@@ -9254,7 +9254,7 @@
         <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L35" t="n">
         <v>1.25</v>
@@ -9263,7 +9263,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O35" t="n">
         <v>1.18</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9505,7 @@
         <v>11</v>
       </c>
       <c r="J36" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K36" t="n">
         <v>6.2</v>
@@ -9517,124 +9517,124 @@
         <v>1.03</v>
       </c>
       <c r="N36" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O36" t="n">
         <v>1.19</v>
       </c>
       <c r="P36" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
         <v>1.56</v>
       </c>
       <c r="R36" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S36" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T36" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U36" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>1.1</v>
       </c>
       <c r="W36" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X36" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y36" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z36" t="n">
         <v>110</v>
       </c>
       <c r="AA36" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AB36" t="n">
         <v>11</v>
       </c>
       <c r="AC36" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD36" t="n">
         <v>38</v>
       </c>
       <c r="AE36" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH36" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>13</v>
-      </c>
       <c r="AK36" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL36" t="n">
         <v>34</v>
       </c>
       <c r="AM36" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO36" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ36" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AR36" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="AT36" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU36" t="n">
         <v>11.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AX36" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA36" t="n">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="BB36" t="n">
         <v>10</v>
@@ -9643,16 +9643,16 @@
         <v>12</v>
       </c>
       <c r="BD36" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BE36" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="BF36" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>7.4</v>
+        <v>44</v>
       </c>
       <c r="BH36" t="n">
         <v>4.7</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H37" t="n">
         <v>2.6</v>
@@ -9762,37 +9762,37 @@
         <v>3.45</v>
       </c>
       <c r="K37" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L37" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M37" t="n">
         <v>1.07</v>
       </c>
       <c r="N37" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O37" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P37" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S37" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T37" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U37" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V37" t="n">
         <v>1.58</v>
@@ -9801,10 +9801,10 @@
         <v>1.5</v>
       </c>
       <c r="X37" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y37" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z37" t="n">
         <v>18.5</v>
@@ -9831,7 +9831,7 @@
         <v>13.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI37" t="n">
         <v>46</v>
@@ -9843,19 +9843,19 @@
         <v>34</v>
       </c>
       <c r="AL37" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM37" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN37" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO37" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP37" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ37" t="n">
         <v>10</v>
@@ -9864,10 +9864,10 @@
         <v>15</v>
       </c>
       <c r="AS37" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT37" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU37" t="n">
         <v>7</v>
@@ -9885,55 +9885,55 @@
         <v>11</v>
       </c>
       <c r="AZ37" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BC37" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD37" t="n">
         <v>7.4</v>
       </c>
-      <c r="BD37" t="n">
-        <v>8</v>
-      </c>
       <c r="BE37" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF37" t="n">
         <v>21</v>
       </c>
       <c r="BG37" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BH37" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BJ37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK37" t="n">
         <v>1.01</v>
       </c>
       <c r="BL37" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM37" t="n">
         <v>1.01</v>
       </c>
       <c r="BN37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO37" t="n">
         <v>4.7</v>
       </c>
       <c r="BP37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ37" t="n">
         <v>1.01</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
         <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L38" t="n">
         <v>1.23</v>
@@ -10073,7 +10073,7 @@
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AE38" t="n">
         <v>21</v>
@@ -10085,7 +10085,7 @@
         <v>15</v>
       </c>
       <c r="AH38" t="n">
-        <v>300</v>
+        <v>830</v>
       </c>
       <c r="AI38" t="n">
         <v>27</v>
@@ -10157,7 +10157,7 @@
         <v>11.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BG38" t="n">
         <v>9.4</v>
@@ -10193,7 +10193,7 @@
         <v>1.01</v>
       </c>
       <c r="BR38" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -10261,13 +10261,13 @@
         <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="I39" t="n">
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10306,7 +10306,7 @@
         <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -10512,16 +10512,16 @@
         <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H40" t="n">
         <v>1.57</v>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="J40" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K40" t="n">
         <v>5</v>
@@ -10539,13 +10539,13 @@
         <v>1.17</v>
       </c>
       <c r="P40" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="Q40" t="n">
         <v>1.52</v>
       </c>
       <c r="R40" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S40" t="n">
         <v>2.28</v>
@@ -10554,70 +10554,70 @@
         <v>1.65</v>
       </c>
       <c r="U40" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V40" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="W40" t="n">
         <v>1.19</v>
       </c>
       <c r="X40" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y40" t="n">
         <v>13.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA40" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AB40" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AC40" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD40" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AF40" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG40" t="n">
         <v>24</v>
       </c>
       <c r="AH40" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI40" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ40" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AK40" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL40" t="n">
-        <v>70</v>
+        <v>350</v>
       </c>
       <c r="AM40" t="n">
         <v>85</v>
       </c>
       <c r="AN40" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO40" t="n">
         <v>5.7</v>
       </c>
       <c r="AP40" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="AQ40" t="n">
         <v>11.5</v>
@@ -10629,19 +10629,19 @@
         <v>14</v>
       </c>
       <c r="AT40" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="AU40" t="n">
         <v>10.5</v>
       </c>
       <c r="AV40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW40" t="n">
         <v>13</v>
       </c>
       <c r="AX40" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="AY40" t="n">
         <v>21</v>
@@ -10650,22 +10650,22 @@
         <v>16</v>
       </c>
       <c r="BA40" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BB40" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="BC40" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BD40" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BE40" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BF40" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BG40" t="n">
         <v>5.3</v>
@@ -10677,7 +10677,7 @@
         <v>3.65</v>
       </c>
       <c r="BJ40" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK40" t="n">
         <v>5.8</v>
@@ -10686,7 +10686,7 @@
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN40" t="n">
         <v>9.6</v>
@@ -10698,13 +10698,13 @@
         <v>40</v>
       </c>
       <c r="BQ40" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR40" t="n">
         <v>40</v>
       </c>
       <c r="BS40" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT40" t="n">
         <v>4.7</v>
@@ -10722,17 +10722,17 @@
         <v>19.5</v>
       </c>
       <c r="BY40" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BZ40" t="n">
         <v>12</v>
       </c>
       <c r="CA40" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G41" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H41" t="n">
         <v>4.7</v>
@@ -10775,13 +10775,13 @@
         <v>5.2</v>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K41" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L41" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M41" t="n">
         <v>1.05</v>
@@ -10796,13 +10796,13 @@
         <v>2.18</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R41" t="n">
         <v>1.47</v>
       </c>
       <c r="S41" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T41" t="n">
         <v>1.74</v>
@@ -10814,7 +10814,7 @@
         <v>1.24</v>
       </c>
       <c r="W41" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X41" t="n">
         <v>22</v>
@@ -10832,7 +10832,7 @@
         <v>12</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD41" t="n">
         <v>21</v>
@@ -10844,7 +10844,7 @@
         <v>13.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH41" t="n">
         <v>22</v>
@@ -10853,7 +10853,7 @@
         <v>65</v>
       </c>
       <c r="AJ41" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK41" t="n">
         <v>21</v>
@@ -10865,22 +10865,22 @@
         <v>100</v>
       </c>
       <c r="AN41" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO41" t="n">
         <v>65</v>
       </c>
       <c r="AP41" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AQ41" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AR41" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS41" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT41" t="n">
         <v>9</v>
@@ -10889,40 +10889,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV41" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AW41" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX41" t="n">
         <v>9</v>
       </c>
       <c r="AY41" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AZ41" t="n">
         <v>14.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BC41" t="n">
         <v>13.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE41" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF41" t="n">
         <v>8.4</v>
       </c>
       <c r="BG41" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH41" t="n">
         <v>3.9</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
         <v>1.8</v>
       </c>
       <c r="G43" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H43" t="n">
         <v>4.6</v>
@@ -11286,10 +11286,10 @@
         <v>3.9</v>
       </c>
       <c r="K43" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L43" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M43" t="n">
         <v>1.05</v>
@@ -11319,10 +11319,10 @@
         <v>2.18</v>
       </c>
       <c r="V43" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X43" t="n">
         <v>22</v>
@@ -11340,13 +11340,13 @@
         <v>12</v>
       </c>
       <c r="AC43" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD43" t="n">
         <v>23</v>
       </c>
       <c r="AE43" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF43" t="n">
         <v>14.5</v>
@@ -11385,10 +11385,10 @@
         <v>16.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT43" t="n">
         <v>8.800000000000001</v>
@@ -11400,7 +11400,7 @@
         <v>14</v>
       </c>
       <c r="AW43" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX43" t="n">
         <v>10.5</v>
@@ -11412,7 +11412,7 @@
         <v>16</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB43" t="n">
         <v>17</v>
@@ -11421,16 +11421,16 @@
         <v>16</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF43" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG43" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH43" t="n">
         <v>3.75</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -11525,13 +11525,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G44" t="n">
         <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
@@ -11558,7 +11558,7 @@
         <v>1.06</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="R44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -11806,7 +11806,7 @@
         <v>2.9</v>
       </c>
       <c r="O45" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P45" t="n">
         <v>1.64</v>
@@ -11881,13 +11881,13 @@
         <v>160</v>
       </c>
       <c r="AN45" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO45" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP45" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ45" t="n">
         <v>4.3</v>
@@ -11905,25 +11905,25 @@
         <v>6.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AW45" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX45" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AY45" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AZ45" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BA45" t="n">
         <v>4</v>
       </c>
       <c r="BB45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BC45" t="n">
         <v>6.8</v>
@@ -11932,7 +11932,7 @@
         <v>4</v>
       </c>
       <c r="BE45" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BF45" t="n">
         <v>7</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
         <v>5</v>
       </c>
       <c r="H46" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="I46" t="n">
         <v>2.08</v>
@@ -12063,7 +12063,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q46" t="n">
         <v>2.16</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12302,7 @@
         <v>1.02</v>
       </c>
       <c r="K47" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -12311,13 +12311,13 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O47" t="n">
         <v>1.01</v>
       </c>
       <c r="P47" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q47" t="n">
         <v>1.05</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G48" t="n">
         <v>5.1</v>
@@ -12550,13 +12550,13 @@
         <v>1.85</v>
       </c>
       <c r="I48" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J48" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L48" t="n">
         <v>1.36</v>
@@ -12580,7 +12580,7 @@
         <v>1.33</v>
       </c>
       <c r="S48" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T48" t="n">
         <v>1.84</v>
@@ -12589,7 +12589,7 @@
         <v>2</v>
       </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W48" t="n">
         <v>1.25</v>
@@ -12658,7 +12658,7 @@
         <v>10</v>
       </c>
       <c r="AS48" t="n">
-        <v>5.1</v>
+        <v>18.5</v>
       </c>
       <c r="AT48" t="n">
         <v>13.5</v>
@@ -12700,16 +12700,16 @@
         <v>5.9</v>
       </c>
       <c r="BG48" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH48" t="n">
         <v>1000</v>
       </c>
       <c r="BI48" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BJ48" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK48" t="n">
         <v>1.61</v>
@@ -12718,13 +12718,13 @@
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BN48" t="n">
         <v>11</v>
       </c>
       <c r="BO48" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="BP48" t="n">
         <v>1000</v>
@@ -12736,35 +12736,35 @@
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BT48" t="n">
         <v>6.4</v>
       </c>
       <c r="BU48" t="n">
-        <v>3.45</v>
+        <v>1.41</v>
       </c>
       <c r="BV48" t="n">
         <v>20</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="BX48" t="n">
         <v>44</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BZ48" t="n">
         <v>38</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
         <v>1.02</v>
       </c>
       <c r="K49" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -12828,7 +12828,7 @@
         <v>1.09</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="R49" t="n">
         <v>1.07</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
         <v>3.9</v>
       </c>
       <c r="I50" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J50" t="n">
         <v>3.25</v>
@@ -13079,10 +13079,10 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
         <v>1.14</v>
       </c>
       <c r="O51" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P51" t="n">
         <v>1.14</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -13557,16 +13557,16 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G52" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H52" t="n">
         <v>3.4</v>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
         <v>2.82</v>
@@ -13578,19 +13578,19 @@
         <v>1.51</v>
       </c>
       <c r="M52" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N52" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="O52" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P52" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R52" t="n">
         <v>1.16</v>
@@ -13599,7 +13599,7 @@
         <v>5.7</v>
       </c>
       <c r="T52" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U52" t="n">
         <v>1.7</v>
@@ -13608,10 +13608,10 @@
         <v>1.33</v>
       </c>
       <c r="W52" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X52" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y52" t="n">
         <v>11.5</v>
@@ -13665,58 +13665,58 @@
         <v>120</v>
       </c>
       <c r="AP52" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ52" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR52" t="n">
         <v>17.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT52" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU52" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AV52" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AX52" t="n">
         <v>10.5</v>
       </c>
       <c r="AY52" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ52" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE52" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC52" t="n">
+      <c r="BF52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG52" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>4.5</v>
       </c>
       <c r="BH52" t="n">
         <v>2.68</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -857,52 +857,52 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
         <v>2.92</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q2" t="n">
         <v>2.26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V2" t="n">
         <v>1.27</v>
@@ -911,103 +911,103 @@
         <v>1.73</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
         <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
         <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
         <v>1.03</v>
@@ -1019,10 +1019,10 @@
         <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1037,7 +1037,7 @@
         <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -1165,16 +1165,16 @@
         <v>2.26</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Z3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA3" t="n">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="AB3" t="n">
         <v>8</v>
@@ -1183,10 +1183,10 @@
         <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AF3" t="n">
         <v>11</v>
@@ -1195,10 +1195,10 @@
         <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
         <v>21</v>
@@ -1207,31 +1207,31 @@
         <v>26</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AN3" t="n">
         <v>17.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
         <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
@@ -1240,19 +1240,19 @@
         <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
         <v>12.5</v>
@@ -1261,16 +1261,16 @@
         <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH3" t="n">
         <v>3.15</v>
@@ -1282,13 +1282,13 @@
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>4.2</v>
@@ -1300,41 +1300,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
         <v>10</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.46</v>
@@ -1395,7 +1395,7 @@
         <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
         <v>2.2</v>
@@ -1404,13 +1404,13 @@
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
         <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V4" t="n">
         <v>1.3</v>
@@ -1419,70 +1419,70 @@
         <v>1.87</v>
       </c>
       <c r="X4" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AA4" t="n">
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>170</v>
       </c>
       <c r="AN4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AO4" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AS4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
         <v>7.2</v>
@@ -1491,40 +1491,40 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="AX4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>8.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
         <v>17</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.15</v>
@@ -1536,13 +1536,13 @@
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
         <v>4.8</v>
@@ -1554,13 +1554,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
         <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT4" t="n">
         <v>7.8</v>
@@ -1572,23 +1572,23 @@
         <v>42</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -1625,10 +1625,10 @@
         <v>2.86</v>
       </c>
       <c r="H5" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -1637,7 +1637,7 @@
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
@@ -1649,7 +1649,7 @@
         <v>1.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -1661,10 +1661,10 @@
         <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
         <v>1.53</v>
@@ -1673,37 +1673,37 @@
         <v>1.54</v>
       </c>
       <c r="X5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="n">
         <v>19.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
         <v>34</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
         <v>55</v>
@@ -1721,13 +1721,13 @@
         <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>10</v>
@@ -1736,19 +1736,19 @@
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1760,25 +1760,25 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BC5" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF5" t="n">
         <v>19.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH5" t="n">
         <v>3.45</v>
@@ -1790,13 +1790,13 @@
         <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN5" t="n">
         <v>6</v>
@@ -1808,16 +1808,16 @@
         <v>23</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR5" t="n">
         <v>36</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU5" t="n">
         <v>4.4</v>
@@ -1826,23 +1826,23 @@
         <v>23</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX5" t="n">
         <v>36</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>29</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G6" t="n">
         <v>7.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I6" t="n">
         <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q6" t="n">
         <v>2.38</v>
@@ -1918,10 +1918,10 @@
         <v>2.34</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V6" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="W6" t="n">
         <v>1.15</v>
@@ -1933,7 +1933,7 @@
         <v>6.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AA6" t="n">
         <v>16</v>
@@ -1978,7 +1978,7 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
         <v>9.6</v>
@@ -2035,7 +2035,7 @@
         <v>12.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI6" t="n">
         <v>2.78</v>
@@ -2056,13 +2056,13 @@
         <v>10.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BQ6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
@@ -2071,16 +2071,16 @@
         <v>15.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BU6" t="n">
         <v>3.55</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
@@ -2089,14 +2089,14 @@
         <v>12</v>
       </c>
       <c r="BZ6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G7" t="n">
         <v>2.08</v>
@@ -2136,7 +2136,7 @@
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
         <v>3.45</v>
@@ -2145,7 +2145,7 @@
         <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -2157,10 +2157,10 @@
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R7" t="n">
         <v>1.31</v>
@@ -2169,10 +2169,10 @@
         <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
         <v>1.27</v>
@@ -2181,124 +2181,124 @@
         <v>1.92</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
         <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
         <v>22</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG7" t="n">
         <v>13</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM7" t="n">
         <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AO7" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>15</v>
-      </c>
       <c r="AW7" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AZ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC7" t="n">
         <v>16</v>
       </c>
-      <c r="BA7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD7" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BH7" t="n">
         <v>3.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,7 +2310,7 @@
         <v>4.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BP7" t="n">
         <v>15</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>9.4</v>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="H8" t="n">
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
         <v>4.8</v>
@@ -2411,10 +2411,10 @@
         <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
         <v>1.44</v>
@@ -2426,52 +2426,52 @@
         <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
         <v>8.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AB8" t="n">
         <v>38</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF8" t="n">
         <v>110</v>
       </c>
       <c r="AG8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AI8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AK8" t="n">
         <v>200</v>
@@ -2486,31 +2486,31 @@
         <v>280</v>
       </c>
       <c r="AO8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP8" t="n">
         <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR8" t="n">
         <v>7.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
         <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AX8" t="n">
         <v>1.01</v>
@@ -2579,13 +2579,13 @@
         <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BU8" t="n">
         <v>3</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BW8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
         <v>3.15</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
         <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2665,22 +2665,22 @@
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T9" t="n">
         <v>1.81</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V9" t="n">
         <v>1.39</v>
@@ -2689,7 +2689,7 @@
         <v>1.64</v>
       </c>
       <c r="X9" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y9" t="n">
         <v>14.5</v>
@@ -2698,22 +2698,22 @@
         <v>28</v>
       </c>
       <c r="AA9" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
         <v>17.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG9" t="n">
         <v>14</v>
@@ -2725,7 +2725,7 @@
         <v>65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AK9" t="n">
         <v>34</v>
@@ -2743,7 +2743,7 @@
         <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
         <v>8.800000000000001</v>
@@ -2758,16 +2758,16 @@
         <v>7.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV9" t="n">
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AX9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
         <v>8.6</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>1.92</v>
       </c>
       <c r="G10" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H10" t="n">
         <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
         <v>1.46</v>
@@ -2919,7 +2919,7 @@
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q10" t="n">
         <v>2.12</v>
@@ -2931,22 +2931,22 @@
         <v>3.95</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
         <v>1.95</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="X10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Z10" t="n">
         <v>46</v>
@@ -2958,13 +2958,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
         <v>26</v>
       </c>
       <c r="AE10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
         <v>12</v>
@@ -2988,103 +2988,103 @@
         <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR10" t="n">
         <v>23</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC10" t="n">
         <v>17</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF10" t="n">
         <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="n">
         <v>3.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BN10" t="n">
         <v>4.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
         <v>7.8</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -3146,19 +3146,19 @@
         <v>3.1</v>
       </c>
       <c r="G11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H11" t="n">
         <v>2.34</v>
       </c>
       <c r="I11" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J11" t="n">
         <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
         <v>1.35</v>
@@ -3167,25 +3167,25 @@
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q11" t="n">
         <v>1.81</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U11" t="n">
         <v>2.32</v>
@@ -3197,40 +3197,40 @@
         <v>1.44</v>
       </c>
       <c r="X11" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB11" t="n">
         <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ11" t="n">
         <v>55</v>
@@ -3242,13 +3242,13 @@
         <v>50</v>
       </c>
       <c r="AM11" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AO11" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP11" t="n">
         <v>14.5</v>
@@ -3260,43 +3260,43 @@
         <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT11" t="n">
         <v>12.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BD11" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
@@ -3314,31 +3314,31 @@
         <v>9.4</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11" t="n">
         <v>6.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP11" t="n">
         <v>24</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT11" t="n">
         <v>5.7</v>
@@ -3350,23 +3350,23 @@
         <v>18</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ11" t="n">
         <v>23</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -3397,58 +3397,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H12" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="I12" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R12" t="n">
         <v>1.8</v>
       </c>
       <c r="S12" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U12" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V12" t="n">
         <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="X12" t="n">
         <v>30</v>
@@ -3463,19 +3463,19 @@
         <v>200</v>
       </c>
       <c r="AB12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC12" t="n">
         <v>13.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE12" t="n">
         <v>80</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
@@ -3487,7 +3487,7 @@
         <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AK12" t="n">
         <v>14</v>
@@ -3499,16 +3499,16 @@
         <v>75</v>
       </c>
       <c r="AN12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO12" t="n">
         <v>65</v>
       </c>
       <c r="AP12" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR12" t="n">
         <v>32</v>
@@ -3553,16 +3553,16 @@
         <v>34</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH12" t="n">
         <v>5.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ12" t="n">
         <v>9.6</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN12" t="n">
         <v>4.6</v>
@@ -3586,13 +3586,13 @@
         <v>8.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT12" t="n">
         <v>11</v>
@@ -3601,16 +3601,16 @@
         <v>7</v>
       </c>
       <c r="BV12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="BY12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ12" t="n">
         <v>10</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.09</v>
+        <v>1.94</v>
       </c>
       <c r="O13" t="n">
         <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.09</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.3</v>
+        <v>1.92</v>
       </c>
       <c r="R13" t="n">
         <v>1.07</v>
       </c>
       <c r="S13" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -3911,16 +3911,16 @@
         <v>1.64</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J14" t="n">
         <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.27</v>
@@ -3944,16 +3944,16 @@
         <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="T14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W14" t="n">
         <v>2.56</v>
@@ -3968,7 +3968,7 @@
         <v>70</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB14" t="n">
         <v>11.5</v>
@@ -3992,31 +3992,31 @@
         <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ14" t="n">
         <v>18</v>
       </c>
       <c r="AK14" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
         <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO14" t="n">
         <v>120</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
@@ -4031,7 +4031,7 @@
         <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW14" t="n">
         <v>1.01</v>
@@ -4043,7 +4043,7 @@
         <v>7.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA14" t="n">
         <v>1.01</v>
@@ -4055,7 +4055,7 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4162,37 +4162,37 @@
         <v>2.18</v>
       </c>
       <c r="G15" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
         <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R15" t="n">
         <v>1.29</v>
@@ -4207,22 +4207,22 @@
         <v>2.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="n">
         <v>10.5</v>
@@ -4231,7 +4231,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
         <v>55</v>
@@ -4267,64 +4267,64 @@
         <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB15" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BC15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE15" t="n">
         <v>5</v>
       </c>
-      <c r="AT15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2.74</v>
-      </c>
       <c r="BF15" t="n">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
         <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
         <v>95</v>
@@ -4524,13 +4524,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.55</v>
+        <v>7.4</v>
       </c>
       <c r="AR16" t="n">
         <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT16" t="n">
         <v>9.199999999999999</v>
@@ -4539,7 +4539,7 @@
         <v>5.9</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.95</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW16" t="n">
         <v>20</v>
@@ -4557,19 +4557,19 @@
         <v>5.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BC16" t="n">
         <v>5.1</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG16" t="n">
         <v>18</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4670,19 +4670,19 @@
         <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.3</v>
@@ -4724,7 +4724,7 @@
         <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z17" t="n">
         <v>140</v>
@@ -4736,13 +4736,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD17" t="n">
         <v>55</v>
       </c>
       <c r="AE17" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AF17" t="n">
         <v>9</v>
@@ -4751,7 +4751,7 @@
         <v>13</v>
       </c>
       <c r="AH17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AI17" t="n">
         <v>230</v>
@@ -4766,13 +4766,13 @@
         <v>60</v>
       </c>
       <c r="AM17" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AN17" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP17" t="n">
         <v>12.5</v>
@@ -4787,7 +4787,7 @@
         <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU17" t="n">
         <v>9</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.16</v>
+        <v>1.98</v>
       </c>
       <c r="G18" t="n">
         <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
@@ -4945,7 +4945,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="O18" t="n">
         <v>1.02</v>
@@ -4969,7 +4969,7 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
         <v>1.02</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
@@ -5208,7 +5208,7 @@
         <v>1.07</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.61</v>
+        <v>1.05</v>
       </c>
       <c r="R19" t="n">
         <v>1.07</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.16</v>
+        <v>1.91</v>
       </c>
       <c r="G20" t="n">
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
@@ -5456,13 +5456,13 @@
         <v>1.08</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P20" t="n">
         <v>1.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.07</v>
@@ -5477,7 +5477,7 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="W20" t="n">
         <v>1.02</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
@@ -5710,7 +5710,7 @@
         <v>1.09</v>
       </c>
       <c r="O21" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="P21" t="n">
         <v>1.09</v>
@@ -5722,7 +5722,7 @@
         <v>1.07</v>
       </c>
       <c r="S21" t="n">
-        <v>1.43</v>
+        <v>1.05</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
         <v>4.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
@@ -6478,25 +6478,25 @@
         <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R24" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S24" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T24" t="n">
         <v>1.42</v>
       </c>
       <c r="U24" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="V24" t="n">
         <v>1.56</v>
       </c>
       <c r="W24" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X24" t="n">
         <v>90</v>
@@ -6511,7 +6511,7 @@
         <v>120</v>
       </c>
       <c r="AB24" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AC24" t="n">
         <v>11.5</v>
@@ -6523,13 +6523,13 @@
         <v>25</v>
       </c>
       <c r="AF24" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AG24" t="n">
         <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI24" t="n">
         <v>38</v>
@@ -6559,13 +6559,13 @@
         <v>18.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AS24" t="n">
         <v>25</v>
       </c>
       <c r="AT24" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -6586,16 +6586,16 @@
         <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BB24" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BC24" t="n">
         <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BE24" t="n">
         <v>34</v>
@@ -6607,13 +6607,13 @@
         <v>10.5</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.22</v>
+        <v>4.2</v>
       </c>
       <c r="BJ24" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BK24" t="n">
         <v>5.3</v>
@@ -6622,53 +6622,53 @@
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>2.16</v>
+        <v>8</v>
       </c>
       <c r="BN24" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP24" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BR24" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BS24" t="n">
-        <v>2.06</v>
+        <v>6.6</v>
       </c>
       <c r="BT24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV24" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BW24" t="n">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="BX24" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BY24" t="n">
-        <v>2.06</v>
+        <v>6.6</v>
       </c>
       <c r="BZ24" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.95</v>
+        <v>7.6</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6702,40 +6702,40 @@
         <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K25" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
         <v>1.29</v>
       </c>
       <c r="P25" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
         <v>3.15</v>
@@ -6744,13 +6744,13 @@
         <v>1.69</v>
       </c>
       <c r="U25" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W25" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X25" t="n">
         <v>18.5</v>
@@ -6774,7 +6774,7 @@
         <v>14.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AF25" t="n">
         <v>16</v>
@@ -6786,7 +6786,7 @@
         <v>17</v>
       </c>
       <c r="AI25" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AJ25" t="n">
         <v>32</v>
@@ -6801,22 +6801,22 @@
         <v>85</v>
       </c>
       <c r="AN25" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS25" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT25" t="n">
         <v>10</v>
@@ -6840,89 +6840,89 @@
         <v>6.6</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BB25" t="n">
         <v>8</v>
       </c>
       <c r="BC25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD25" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF25" t="n">
         <v>14.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH25" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.92</v>
+        <v>2.98</v>
       </c>
       <c r="BJ25" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.66</v>
+        <v>5.1</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.92</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>24</v>
+      </c>
+      <c r="CA25" t="n">
         <v>7.4</v>
       </c>
-      <c r="BO25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>34</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>1.82</v>
-      </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6956,16 +6956,16 @@
         <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H26" t="n">
         <v>2.38</v>
       </c>
       <c r="I26" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K26" t="n">
         <v>3.7</v>
@@ -6998,13 +6998,13 @@
         <v>1.68</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V26" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W26" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X26" t="n">
         <v>19</v>
@@ -7013,16 +7013,16 @@
         <v>14</v>
       </c>
       <c r="Z26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB26" t="n">
         <v>16</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD26" t="n">
         <v>12</v>
@@ -7031,7 +7031,7 @@
         <v>29</v>
       </c>
       <c r="AF26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG26" t="n">
         <v>16</v>
@@ -7046,7 +7046,7 @@
         <v>60</v>
       </c>
       <c r="AK26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL26" t="n">
         <v>48</v>
@@ -7055,7 +7055,7 @@
         <v>90</v>
       </c>
       <c r="AN26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO26" t="n">
         <v>21</v>
@@ -7067,10 +7067,10 @@
         <v>10.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT26" t="n">
         <v>12</v>
@@ -7082,10 +7082,10 @@
         <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.4</v>
+        <v>19</v>
       </c>
       <c r="AX26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
         <v>12</v>
@@ -7094,22 +7094,22 @@
         <v>14</v>
       </c>
       <c r="BA26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB26" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BC26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE26" t="n">
         <v>6</v>
       </c>
-      <c r="BC26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BF26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG26" t="n">
         <v>15.5</v>
@@ -7118,7 +7118,7 @@
         <v>3.65</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="BJ26" t="n">
         <v>9.199999999999999</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="G27" t="n">
         <v>2.5</v>
       </c>
       <c r="H27" t="n">
-        <v>2.54</v>
+        <v>1.09</v>
       </c>
       <c r="I27" t="n">
         <v>4.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7234,19 +7234,19 @@
         <v>1.13</v>
       </c>
       <c r="O27" t="n">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="P27" t="n">
         <v>1.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R27" t="n">
         <v>1.07</v>
       </c>
       <c r="S27" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T27" t="n">
         <v>1.04</v>
@@ -7264,28 +7264,28 @@
         <v>36</v>
       </c>
       <c r="Y27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z27" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AA27" t="n">
-        <v>610</v>
+        <v>940</v>
       </c>
       <c r="AB27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC27" t="n">
         <v>13</v>
       </c>
       <c r="AD27" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AE27" t="n">
-        <v>670</v>
+        <v>970</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>32</v>
@@ -7300,10 +7300,10 @@
         <v>95</v>
       </c>
       <c r="AK27" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AL27" t="n">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
@@ -7321,52 +7321,52 @@
         <v>6.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS27" t="n">
         <v>1.44</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AU27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ27" t="n">
         <v>11</v>
       </c>
       <c r="BA27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BD27" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BE27" t="n">
         <v>36</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -7461,25 +7461,25 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G28" t="n">
         <v>3.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I28" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
@@ -7488,31 +7488,31 @@
         <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R28" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U28" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="V28" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="W28" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X28" t="n">
         <v>21</v>
@@ -7521,16 +7521,16 @@
         <v>13</v>
       </c>
       <c r="Z28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA28" t="n">
         <v>29</v>
       </c>
       <c r="AB28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD28" t="n">
         <v>11.5</v>
@@ -7539,7 +7539,7 @@
         <v>22</v>
       </c>
       <c r="AF28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG28" t="n">
         <v>15</v>
@@ -7563,7 +7563,7 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO28" t="n">
         <v>13.5</v>
@@ -7575,25 +7575,25 @@
         <v>11.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS28" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AT28" t="n">
         <v>14</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW28" t="n">
         <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY28" t="n">
         <v>12.5</v>
@@ -7602,13 +7602,13 @@
         <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BB28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD28" t="n">
         <v>23</v>
@@ -7617,28 +7617,28 @@
         <v>32</v>
       </c>
       <c r="BF28" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG28" t="n">
         <v>11.5</v>
       </c>
       <c r="BH28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN28" t="n">
         <v>7.2</v>
@@ -7650,13 +7650,13 @@
         <v>26</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR28" t="n">
         <v>34</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT28" t="n">
         <v>5.5</v>
@@ -7665,16 +7665,16 @@
         <v>4.2</v>
       </c>
       <c r="BV28" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX28" t="n">
         <v>26</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7739,7 @@
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>1.24</v>
@@ -7748,7 +7748,7 @@
         <v>2.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R29" t="n">
         <v>1.51</v>
@@ -7757,7 +7757,7 @@
         <v>2.82</v>
       </c>
       <c r="T29" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U29" t="n">
         <v>1.86</v>
@@ -7901,7 +7901,7 @@
         <v>3.35</v>
       </c>
       <c r="BP29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ29" t="n">
         <v>5.3</v>
@@ -7913,7 +7913,7 @@
         <v>7.4</v>
       </c>
       <c r="BT29" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BU29" t="n">
         <v>6</v>
@@ -7934,11 +7934,11 @@
         <v>13.5</v>
       </c>
       <c r="CA29" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -8250,19 +8250,19 @@
         <v>1.11</v>
       </c>
       <c r="O31" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P31" t="n">
         <v>1.12</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R31" t="n">
         <v>1.07</v>
       </c>
       <c r="S31" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -8489,10 +8489,10 @@
         <v>4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K32" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L32" t="n">
         <v>1.35</v>
@@ -8510,7 +8510,7 @@
         <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R32" t="n">
         <v>1.43</v>
@@ -8519,10 +8519,10 @@
         <v>3.1</v>
       </c>
       <c r="T32" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U32" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V32" t="n">
         <v>1.33</v>
@@ -8531,7 +8531,7 @@
         <v>1.94</v>
       </c>
       <c r="X32" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y32" t="n">
         <v>16.5</v>
@@ -8546,7 +8546,7 @@
         <v>11</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD32" t="n">
         <v>16.5</v>
@@ -8567,13 +8567,13 @@
         <v>240</v>
       </c>
       <c r="AJ32" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK32" t="n">
         <v>22</v>
       </c>
       <c r="AL32" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
@@ -8597,7 +8597,7 @@
         <v>34</v>
       </c>
       <c r="AT32" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU32" t="n">
         <v>7.6</v>
@@ -8609,7 +8609,7 @@
         <v>25</v>
       </c>
       <c r="AX32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY32" t="n">
         <v>9.6</v>
@@ -8618,13 +8618,13 @@
         <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB32" t="n">
         <v>20</v>
       </c>
       <c r="BC32" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD32" t="n">
         <v>22</v>
@@ -8678,7 +8678,7 @@
         <v>7.6</v>
       </c>
       <c r="BU32" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV32" t="n">
         <v>32</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
         <v>2.8</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K33" t="n">
         <v>3.4</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -8985,82 +8985,82 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="G34" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="H34" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I34" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="J34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L34" t="n">
         <v>1.45</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O34" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P34" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R34" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
         <v>4.2</v>
       </c>
       <c r="T34" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="U34" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="V34" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W34" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="X34" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AA34" t="n">
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC34" t="n">
         <v>10.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF34" t="n">
         <v>12.5</v>
@@ -9069,10 +9069,10 @@
         <v>14.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ34" t="n">
         <v>25</v>
@@ -9081,16 +9081,16 @@
         <v>28</v>
       </c>
       <c r="AL34" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN34" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP34" t="n">
         <v>1.01</v>
@@ -9105,7 +9105,7 @@
         <v>1.03</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU34" t="n">
         <v>1.01</v>
@@ -9114,7 +9114,7 @@
         <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
         <v>1.01</v>
@@ -9126,7 +9126,7 @@
         <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
         <v>1.01</v>
@@ -9135,10 +9135,10 @@
         <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
         <v>1.01</v>
@@ -9150,10 +9150,10 @@
         <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="BJ34" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK34" t="n">
         <v>1.01</v>
@@ -9171,13 +9171,13 @@
         <v>3.35</v>
       </c>
       <c r="BP34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ34" t="n">
         <v>1.01</v>
       </c>
       <c r="BR34" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
         <v>1.96</v>
       </c>
       <c r="H35" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I35" t="n">
         <v>4.5</v>
@@ -9263,7 +9263,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
         <v>1.18</v>
@@ -9278,7 +9278,7 @@
         <v>1.6</v>
       </c>
       <c r="S35" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="T35" t="n">
         <v>1.56</v>
@@ -9287,16 +9287,16 @@
         <v>2.5</v>
       </c>
       <c r="V35" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W35" t="n">
         <v>2.04</v>
       </c>
       <c r="X35" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y35" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z35" t="n">
         <v>38</v>
@@ -9305,31 +9305,31 @@
         <v>90</v>
       </c>
       <c r="AB35" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD35" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE35" t="n">
         <v>50</v>
       </c>
       <c r="AF35" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH35" t="n">
         <v>16.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ35" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK35" t="n">
         <v>18</v>
@@ -9341,16 +9341,16 @@
         <v>70</v>
       </c>
       <c r="AN35" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO35" t="n">
         <v>36</v>
       </c>
       <c r="AP35" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AR35" t="n">
         <v>9.199999999999999</v>
@@ -9359,43 +9359,43 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AT35" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AU35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV35" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>5.7</v>
       </c>
       <c r="AW35" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AZ35" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="BA35" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BB35" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BE35" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BF35" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG35" t="n">
         <v>9.199999999999999</v>
@@ -9410,34 +9410,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK35" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN35" t="n">
         <v>5.3</v>
       </c>
       <c r="BO35" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP35" t="n">
         <v>13</v>
       </c>
       <c r="BQ35" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR35" t="n">
         <v>22</v>
       </c>
       <c r="BS35" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT35" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU35" t="n">
         <v>4.5</v>
@@ -9446,13 +9446,13 @@
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY35" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BX35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY35" t="n">
-        <v>7.8</v>
       </c>
       <c r="BZ35" t="n">
         <v>15.5</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G36" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H36" t="n">
         <v>9.199999999999999</v>
@@ -9505,7 +9505,7 @@
         <v>11</v>
       </c>
       <c r="J36" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K36" t="n">
         <v>6.2</v>
@@ -9532,22 +9532,22 @@
         <v>1.64</v>
       </c>
       <c r="S36" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T36" t="n">
         <v>1.91</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V36" t="n">
         <v>1.1</v>
       </c>
       <c r="W36" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X36" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y36" t="n">
         <v>38</v>
@@ -9583,7 +9583,7 @@
         <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK36" t="n">
         <v>14.5</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -9747,19 +9747,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="G37" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H37" t="n">
         <v>2.6</v>
       </c>
       <c r="I37" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J37" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K37" t="n">
         <v>3.7</v>
@@ -9777,16 +9777,16 @@
         <v>1.3</v>
       </c>
       <c r="P37" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q37" t="n">
         <v>1.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S37" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T37" t="n">
         <v>1.73</v>
@@ -9795,22 +9795,22 @@
         <v>2.22</v>
       </c>
       <c r="V37" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W37" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X37" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y37" t="n">
         <v>12</v>
       </c>
       <c r="Z37" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA37" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AB37" t="n">
         <v>12.5</v>
@@ -9825,13 +9825,13 @@
         <v>34</v>
       </c>
       <c r="AF37" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG37" t="n">
         <v>13.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI37" t="n">
         <v>46</v>
@@ -9840,19 +9840,19 @@
         <v>55</v>
       </c>
       <c r="AK37" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL37" t="n">
         <v>48</v>
       </c>
       <c r="AM37" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN37" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO37" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP37" t="n">
         <v>13.5</v>
@@ -9861,25 +9861,25 @@
         <v>10</v>
       </c>
       <c r="AR37" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT37" t="n">
         <v>10.5</v>
       </c>
       <c r="AU37" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV37" t="n">
         <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AX37" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY37" t="n">
         <v>11</v>
@@ -9888,25 +9888,25 @@
         <v>14.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB37" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC37" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BD37" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE37" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BF37" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG37" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH37" t="n">
         <v>3.6</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -10007,10 +10007,10 @@
         <v>3.4</v>
       </c>
       <c r="H38" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I38" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J38" t="n">
         <v>4</v>
@@ -10028,100 +10028,100 @@
         <v>5.7</v>
       </c>
       <c r="O38" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P38" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R38" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S38" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T38" t="n">
         <v>1.54</v>
       </c>
       <c r="U38" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V38" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W38" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X38" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Y38" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z38" t="n">
         <v>18</v>
       </c>
       <c r="AA38" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AB38" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AE38" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AF38" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AG38" t="n">
         <v>15</v>
       </c>
       <c r="AH38" t="n">
-        <v>830</v>
+        <v>15.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AJ38" t="n">
         <v>60</v>
       </c>
       <c r="AK38" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AL38" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM38" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AN38" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AO38" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP38" t="n">
-        <v>9.6</v>
+        <v>19</v>
       </c>
       <c r="AQ38" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AT38" t="n">
-        <v>16.5</v>
+        <v>6</v>
       </c>
       <c r="AU38" t="n">
         <v>9</v>
@@ -10130,10 +10130,10 @@
         <v>10</v>
       </c>
       <c r="AW38" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY38" t="n">
         <v>13</v>
@@ -10142,19 +10142,19 @@
         <v>13</v>
       </c>
       <c r="BA38" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BC38" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="BD38" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE38" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BF38" t="n">
         <v>17.5</v>
@@ -10193,7 +10193,7 @@
         <v>1.01</v>
       </c>
       <c r="BR38" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="G39" t="n">
         <v>1000</v>
@@ -10267,7 +10267,7 @@
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10279,22 +10279,22 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="O39" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P39" t="n">
         <v>1.13</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="R39" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S39" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -10512,13 +10512,13 @@
         <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H40" t="n">
         <v>1.57</v>
       </c>
       <c r="I40" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="J40" t="n">
         <v>4.8</v>
@@ -10539,7 +10539,7 @@
         <v>1.17</v>
       </c>
       <c r="P40" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q40" t="n">
         <v>1.52</v>
@@ -10560,7 +10560,7 @@
         <v>2.68</v>
       </c>
       <c r="W40" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
         <v>34</v>
@@ -10575,7 +10575,7 @@
         <v>18</v>
       </c>
       <c r="AB40" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AC40" t="n">
         <v>12</v>
@@ -10590,7 +10590,7 @@
         <v>65</v>
       </c>
       <c r="AG40" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH40" t="n">
         <v>18</v>
@@ -10605,7 +10605,7 @@
         <v>1000</v>
       </c>
       <c r="AL40" t="n">
-        <v>350</v>
+        <v>440</v>
       </c>
       <c r="AM40" t="n">
         <v>85</v>
@@ -10629,10 +10629,10 @@
         <v>14</v>
       </c>
       <c r="AT40" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AU40" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV40" t="n">
         <v>9.4</v>
@@ -10656,16 +10656,16 @@
         <v>44</v>
       </c>
       <c r="BC40" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD40" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE40" t="n">
         <v>32</v>
       </c>
       <c r="BF40" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BG40" t="n">
         <v>5.3</v>
@@ -10680,31 +10680,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK40" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN40" t="n">
         <v>9.6</v>
       </c>
       <c r="BO40" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BP40" t="n">
         <v>40</v>
       </c>
       <c r="BQ40" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BR40" t="n">
         <v>40</v>
       </c>
       <c r="BS40" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT40" t="n">
         <v>4.7</v>
@@ -10722,17 +10722,17 @@
         <v>19.5</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ40" t="n">
         <v>12</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -10766,19 +10766,19 @@
         <v>1.73</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H41" t="n">
         <v>4.7</v>
       </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J41" t="n">
         <v>4.1</v>
       </c>
       <c r="K41" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L41" t="n">
         <v>1.34</v>
@@ -10790,10 +10790,10 @@
         <v>4.4</v>
       </c>
       <c r="O41" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P41" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q41" t="n">
         <v>1.75</v>
@@ -10802,7 +10802,7 @@
         <v>1.47</v>
       </c>
       <c r="S41" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T41" t="n">
         <v>1.74</v>
@@ -10814,70 +10814,70 @@
         <v>1.24</v>
       </c>
       <c r="W41" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X41" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y41" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z41" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AA41" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD41" t="n">
         <v>21</v>
       </c>
       <c r="AE41" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF41" t="n">
         <v>13.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH41" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI41" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ41" t="n">
         <v>20</v>
       </c>
       <c r="AK41" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AL41" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR41" t="n">
         <v>32</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>6.8</v>
       </c>
       <c r="AS41" t="n">
         <v>7.6</v>
@@ -10886,10 +10886,10 @@
         <v>9</v>
       </c>
       <c r="AU41" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV41" t="n">
-        <v>5.9</v>
+        <v>17.5</v>
       </c>
       <c r="AW41" t="n">
         <v>7.2</v>
@@ -10898,19 +10898,19 @@
         <v>9</v>
       </c>
       <c r="AY41" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ41" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA41" t="n">
         <v>7.2</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.7</v>
+        <v>14</v>
       </c>
       <c r="BC41" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD41" t="n">
         <v>6.4</v>
@@ -10919,7 +10919,7 @@
         <v>7.6</v>
       </c>
       <c r="BF41" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG41" t="n">
         <v>7.2</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -11017,118 +11017,118 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="G42" t="n">
-        <v>1000</v>
+        <v>1.49</v>
       </c>
       <c r="H42" t="n">
-        <v>1.26</v>
+        <v>7</v>
       </c>
       <c r="I42" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J42" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N42" t="n">
-        <v>1.06</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="P42" t="n">
-        <v>1.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.21</v>
+        <v>1.74</v>
       </c>
       <c r="R42" t="n">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="S42" t="n">
-        <v>1.21</v>
+        <v>2.6</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR42" t="n">
         <v>1.03</v>
@@ -11137,37 +11137,37 @@
         <v>1.03</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW42" t="n">
         <v>1.03</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA42" t="n">
         <v>1.03</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE42" t="n">
         <v>1.03</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
         <v>3.9</v>
       </c>
       <c r="K43" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L43" t="n">
         <v>1.3</v>
@@ -11310,7 +11310,7 @@
         <v>1.45</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T43" t="n">
         <v>1.76</v>
@@ -11346,13 +11346,13 @@
         <v>23</v>
       </c>
       <c r="AE43" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF43" t="n">
         <v>14.5</v>
       </c>
       <c r="AG43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH43" t="n">
         <v>22</v>
@@ -11385,10 +11385,10 @@
         <v>16.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT43" t="n">
         <v>8.800000000000001</v>
@@ -11397,10 +11397,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV43" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX43" t="n">
         <v>10.5</v>
@@ -11412,7 +11412,7 @@
         <v>16</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB43" t="n">
         <v>17</v>
@@ -11421,16 +11421,16 @@
         <v>16</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF43" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG43" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH43" t="n">
         <v>3.75</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -11525,13 +11525,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G44" t="n">
         <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -11782,10 +11782,10 @@
         <v>2.94</v>
       </c>
       <c r="G45" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H45" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I45" t="n">
         <v>2.82</v>
@@ -11806,7 +11806,7 @@
         <v>2.9</v>
       </c>
       <c r="O45" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P45" t="n">
         <v>1.64</v>
@@ -11815,7 +11815,7 @@
         <v>2.24</v>
       </c>
       <c r="R45" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S45" t="n">
         <v>4.3</v>
@@ -11836,109 +11836,109 @@
         <v>13</v>
       </c>
       <c r="Y45" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="Z45" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB45" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE45" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF45" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AG45" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AH45" t="n">
         <v>21</v>
       </c>
       <c r="AI45" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK45" t="n">
         <v>55</v>
       </c>
-      <c r="AJ45" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>44</v>
-      </c>
       <c r="AL45" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM45" t="n">
         <v>160</v>
       </c>
       <c r="AN45" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO45" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP45" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AQ45" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AR45" t="n">
-        <v>5.5</v>
+        <v>14</v>
       </c>
       <c r="AS45" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AT45" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU45" t="n">
         <v>6.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AW45" t="n">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="AX45" t="n">
-        <v>5.8</v>
+        <v>15.5</v>
       </c>
       <c r="AY45" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AZ45" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="BB45" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="BC45" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="BD45" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="BE45" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BF45" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="BG45" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="BH45" t="n">
         <v>3.05</v>
@@ -11962,7 +11962,7 @@
         <v>6.4</v>
       </c>
       <c r="BO45" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP45" t="n">
         <v>1000</v>
@@ -11980,7 +11980,7 @@
         <v>5.6</v>
       </c>
       <c r="BU45" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -12039,10 +12039,10 @@
         <v>5</v>
       </c>
       <c r="H46" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="I46" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J46" t="n">
         <v>3.4</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
         <v>1.09</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="R47" t="n">
         <v>1.07</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -12544,10 +12544,10 @@
         <v>4.5</v>
       </c>
       <c r="G48" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="H48" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="I48" t="n">
         <v>1.98</v>
@@ -12562,7 +12562,7 @@
         <v>1.36</v>
       </c>
       <c r="M48" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N48" t="n">
         <v>3.5</v>
@@ -12574,16 +12574,16 @@
         <v>1.87</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R48" t="n">
         <v>1.33</v>
       </c>
       <c r="S48" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T48" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U48" t="n">
         <v>2</v>
@@ -12592,13 +12592,13 @@
         <v>2.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X48" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y48" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z48" t="n">
         <v>14</v>
@@ -12607,10 +12607,10 @@
         <v>26</v>
       </c>
       <c r="AB48" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AD48" t="n">
         <v>12.5</v>
@@ -12619,7 +12619,7 @@
         <v>26</v>
       </c>
       <c r="AF48" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG48" t="n">
         <v>23</v>
@@ -12628,22 +12628,22 @@
         <v>24</v>
       </c>
       <c r="AI48" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ48" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AK48" t="n">
         <v>65</v>
       </c>
       <c r="AL48" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AM48" t="n">
         <v>140</v>
       </c>
       <c r="AN48" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AO48" t="n">
         <v>17</v>
@@ -12652,16 +12652,16 @@
         <v>12</v>
       </c>
       <c r="AQ48" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR48" t="n">
         <v>10</v>
       </c>
       <c r="AS48" t="n">
-        <v>18.5</v>
+        <v>3.75</v>
       </c>
       <c r="AT48" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU48" t="n">
         <v>7.4</v>
@@ -12670,34 +12670,34 @@
         <v>9</v>
       </c>
       <c r="AW48" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="AX48" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AY48" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AZ48" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="BA48" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="BB48" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BC48" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="BE48" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BF48" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="BG48" t="n">
         <v>10</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -12828,7 +12828,7 @@
         <v>1.09</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="R49" t="n">
         <v>1.07</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -13049,10 +13049,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G50" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H50" t="n">
         <v>3.9</v>
@@ -13064,7 +13064,7 @@
         <v>3.25</v>
       </c>
       <c r="K50" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -13079,7 +13079,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q50" t="n">
         <v>2.2</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -13303,13 +13303,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="G51" t="n">
         <v>1000</v>
       </c>
       <c r="H51" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="I51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -13557,10 +13557,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G52" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H52" t="n">
         <v>3.4</v>
@@ -13569,7 +13569,7 @@
         <v>4.1</v>
       </c>
       <c r="J52" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K52" t="n">
         <v>3.3</v>
@@ -13587,10 +13587,10 @@
         <v>1.57</v>
       </c>
       <c r="P52" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R52" t="n">
         <v>1.16</v>
@@ -13602,16 +13602,16 @@
         <v>2.14</v>
       </c>
       <c r="U52" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V52" t="n">
         <v>1.33</v>
       </c>
       <c r="W52" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X52" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y52" t="n">
         <v>11.5</v>
@@ -13620,7 +13620,7 @@
         <v>29</v>
       </c>
       <c r="AA52" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB52" t="n">
         <v>8.800000000000001</v>
@@ -13650,7 +13650,7 @@
         <v>50</v>
       </c>
       <c r="AK52" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL52" t="n">
         <v>85</v>
@@ -13665,64 +13665,64 @@
         <v>120</v>
       </c>
       <c r="AP52" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AQ52" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AR52" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT52" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AU52" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AV52" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AX52" t="n">
         <v>10.5</v>
       </c>
       <c r="AY52" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ52" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC52" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB52" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>4</v>
-      </c>
       <c r="BD52" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF52" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF52" t="n">
-        <v>4</v>
-      </c>
       <c r="BG52" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH52" t="n">
         <v>2.68</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="BJ52" t="n">
         <v>12</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>2.92</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
         <v>3.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X2" t="n">
         <v>12.5</v>
@@ -947,64 +947,64 @@
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
         <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO2" t="n">
         <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AQ2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY2" t="n">
         <v>3.35</v>
       </c>
-      <c r="AR2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BA2" t="n">
         <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BD2" t="n">
         <v>4.1</v>
@@ -1013,49 +1013,49 @@
         <v>4.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="BN2" t="n">
         <v>5</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.27</v>
+        <v>2.98</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU2" t="n">
         <v>4.2</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.27</v>
+        <v>2.38</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.2</v>
+        <v>2.42</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.27</v>
+        <v>2.38</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -1219,31 +1219,31 @@
         <v>240</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS3" t="n">
         <v>4.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW3" t="n">
         <v>4.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
         <v>8.800000000000001</v>
@@ -1252,7 +1252,7 @@
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB3" t="n">
         <v>12.5</v>
@@ -1261,13 +1261,13 @@
         <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
         <v>4.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG3" t="n">
         <v>4.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -1377,13 +1377,13 @@
         <v>4.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1401,7 +1401,7 @@
         <v>2.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
         <v>4.3</v>
@@ -1410,7 +1410,7 @@
         <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V4" t="n">
         <v>1.3</v>
@@ -1431,7 +1431,7 @@
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
         <v>7.8</v>
@@ -1440,7 +1440,7 @@
         <v>18</v>
       </c>
       <c r="AE4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
         <v>13</v>
@@ -1452,10 +1452,10 @@
         <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AK4" t="n">
         <v>32</v>
@@ -1467,10 +1467,10 @@
         <v>170</v>
       </c>
       <c r="AN4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
@@ -1479,10 +1479,10 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT4" t="n">
         <v>7.2</v>
@@ -1494,7 +1494,7 @@
         <v>15</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AX4" t="n">
         <v>10.5</v>
@@ -1503,28 +1503,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BB4" t="n">
         <v>18.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
         <v>17</v>
       </c>
       <c r="BG4" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.15</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -1646,7 +1646,7 @@
         <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P5" t="n">
         <v>1.93</v>
@@ -1667,22 +1667,22 @@
         <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AB5" t="n">
         <v>11.5</v>
@@ -1697,43 +1697,43 @@
         <v>34</v>
       </c>
       <c r="AF5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="AJ5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP5" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS5" t="n">
         <v>34</v>
@@ -1745,40 +1745,40 @@
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>32</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>34</v>
       </c>
       <c r="BE5" t="n">
         <v>36</v>
       </c>
       <c r="BF5" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BG5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BH5" t="n">
         <v>3.45</v>
@@ -1787,7 +1787,7 @@
         <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK5" t="n">
         <v>5.1</v>
@@ -1796,53 +1796,53 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW5" t="n">
         <v>7.2</v>
       </c>
-      <c r="BR5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BX5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ5" t="n">
         <v>29</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>6.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="I6" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.5</v>
@@ -1906,7 +1906,7 @@
         <v>1.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
@@ -1915,13 +1915,13 @@
         <v>4.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.15</v>
@@ -1930,22 +1930,22 @@
         <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB6" t="n">
         <v>18</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE6" t="n">
         <v>22</v>
@@ -1954,13 +1954,13 @@
         <v>220</v>
       </c>
       <c r="AG6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
@@ -1972,7 +1972,7 @@
         <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN6" t="n">
         <v>1000</v>
@@ -1984,10 +1984,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
         <v>14</v>
@@ -2008,10 +2008,10 @@
         <v>27</v>
       </c>
       <c r="AY6" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BA6" t="n">
         <v>30</v>
@@ -2023,19 +2023,19 @@
         <v>42</v>
       </c>
       <c r="BD6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE6" t="n">
         <v>50</v>
       </c>
       <c r="BF6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BG6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI6" t="n">
         <v>2.78</v>
@@ -2050,53 +2050,53 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BO6" t="n">
         <v>6.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BQ6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BS6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BT6" t="n">
         <v>3.85</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R7" t="n">
         <v>1.31</v>
@@ -2211,7 +2211,7 @@
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>80</v>
@@ -2241,10 +2241,10 @@
         <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
         <v>7.4</v>
@@ -2256,7 +2256,7 @@
         <v>15</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX7" t="n">
         <v>8.800000000000001</v>
@@ -2268,7 +2268,7 @@
         <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB7" t="n">
         <v>17</v>
@@ -2277,22 +2277,22 @@
         <v>16</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF7" t="n">
         <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="n">
         <v>3.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>12.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="I8" t="n">
         <v>1.44</v>
@@ -2438,7 +2438,7 @@
         <v>24</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
         <v>8.6</v>
@@ -2447,13 +2447,13 @@
         <v>12</v>
       </c>
       <c r="AB8" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AC8" t="n">
         <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
@@ -2471,7 +2471,7 @@
         <v>46</v>
       </c>
       <c r="AJ8" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AK8" t="n">
         <v>200</v>
@@ -2513,7 +2513,7 @@
         <v>13.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY8" t="n">
         <v>26</v>
@@ -2522,22 +2522,22 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG8" t="n">
         <v>5.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -2650,10 +2650,10 @@
         <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2665,22 +2665,22 @@
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
         <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
         <v>1.4</v>
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="AA9" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB9" t="n">
         <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
         <v>17.5</v>
@@ -2752,7 +2752,7 @@
         <v>16.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT9" t="n">
         <v>7.2</v>
@@ -2764,7 +2764,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
@@ -2776,25 +2776,25 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BC9" t="n">
         <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
         <v>17</v>
       </c>
       <c r="BG9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BH9" t="n">
         <v>3.35</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G10" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H10" t="n">
         <v>4.4</v>
@@ -2940,7 +2940,7 @@
         <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X10" t="n">
         <v>14</v>
@@ -3027,7 +3027,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
         <v>6.8</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>2.44</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
         <v>3.8</v>
@@ -3173,13 +3173,13 @@
         <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
         <v>2.96</v>
@@ -3200,7 +3200,7 @@
         <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
         <v>21</v>
@@ -3224,10 +3224,10 @@
         <v>28</v>
       </c>
       <c r="AG11" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI11" t="n">
         <v>42</v>
@@ -3236,22 +3236,22 @@
         <v>55</v>
       </c>
       <c r="AK11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL11" t="n">
         <v>50</v>
       </c>
       <c r="AM11" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
         <v>17</v>
       </c>
       <c r="AP11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ11" t="n">
         <v>10.5</v>
@@ -3260,7 +3260,7 @@
         <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
         <v>12.5</v>
@@ -3284,22 +3284,22 @@
         <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BG11" t="n">
         <v>14.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.49</v>
       </c>
       <c r="G12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H12" t="n">
         <v>6.8</v>
@@ -3424,34 +3424,34 @@
         <v>6.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="Q12" t="n">
         <v>1.47</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T12" t="n">
         <v>1.66</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V12" t="n">
         <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y12" t="n">
         <v>42</v>
@@ -3493,16 +3493,16 @@
         <v>16.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM12" t="n">
         <v>80</v>
       </c>
       <c r="AN12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP12" t="n">
         <v>19.5</v>
@@ -3517,10 +3517,10 @@
         <v>46</v>
       </c>
       <c r="AT12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV12" t="n">
         <v>18</v>
@@ -3529,7 +3529,7 @@
         <v>34</v>
       </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
         <v>9.800000000000001</v>
@@ -3538,7 +3538,7 @@
         <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -3550,31 +3550,31 @@
         <v>18</v>
       </c>
       <c r="BE12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH12" t="n">
         <v>5.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BJ12" t="n">
         <v>9.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN12" t="n">
         <v>4.6</v>
@@ -3586,13 +3586,13 @@
         <v>8.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR12" t="n">
         <v>18</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT12" t="n">
         <v>11</v>
@@ -3604,10 +3604,10 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX12" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
         <v>11.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>1.66</v>
       </c>
       <c r="I13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="J13" t="n">
         <v>3.5</v>
@@ -3675,13 +3675,13 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
         <v>2</v>
@@ -3690,16 +3690,16 @@
         <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U13" t="n">
         <v>1.86</v>
       </c>
       <c r="V13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="W13" t="n">
         <v>1.18</v>
@@ -3840,7 +3840,7 @@
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3864,17 +3864,17 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BZ13" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
         <v>7.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -3914,10 +3914,10 @@
         <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
         <v>5.1</v>
@@ -3932,7 +3932,7 @@
         <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
         <v>2.18</v>
@@ -3941,7 +3941,7 @@
         <v>1.68</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
         <v>2.72</v>
@@ -3950,7 +3950,7 @@
         <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -4037,7 +4037,7 @@
         <v>4.1</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY14" t="n">
         <v>7.4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
         <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -4425,13 +4425,13 @@
         <v>2.34</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
         <v>3.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
         <v>1.09</v>
@@ -4446,7 +4446,7 @@
         <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
         <v>1.26</v>
@@ -4455,7 +4455,7 @@
         <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U16" t="n">
         <v>1.94</v>
@@ -4482,7 +4482,7 @@
         <v>14</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>13</v>
@@ -4506,7 +4506,7 @@
         <v>90</v>
       </c>
       <c r="AK16" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL16" t="n">
         <v>80</v>
@@ -4524,16 +4524,16 @@
         <v>8.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR16" t="n">
         <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU16" t="n">
         <v>5.9</v>
@@ -4554,22 +4554,22 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BG16" t="n">
         <v>18</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="G17" t="n">
         <v>1.4</v>
       </c>
       <c r="H17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
@@ -4715,7 +4715,7 @@
         <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W17" t="n">
         <v>3.5</v>
@@ -4724,7 +4724,7 @@
         <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z17" t="n">
         <v>140</v>
@@ -4742,7 +4742,7 @@
         <v>55</v>
       </c>
       <c r="AE17" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AF17" t="n">
         <v>9</v>
@@ -4772,13 +4772,13 @@
         <v>8</v>
       </c>
       <c r="AO17" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="AP17" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AR17" t="n">
         <v>4.2</v>
@@ -4787,43 +4787,43 @@
         <v>4.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AY17" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BG17" t="n">
         <v>4.3</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
         <v>1.11</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O18" t="n">
         <v>1.46</v>
@@ -4954,7 +4954,7 @@
         <v>1.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="R18" t="n">
         <v>1.21</v>
@@ -5086,7 +5086,7 @@
         <v>2.96</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="BJ18" t="n">
         <v>11.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>2.94</v>
       </c>
       <c r="G19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H19" t="n">
         <v>2.64</v>
@@ -5196,7 +5196,7 @@
         <v>1.56</v>
       </c>
       <c r="M19" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N19" t="n">
         <v>2.28</v>
@@ -5208,7 +5208,7 @@
         <v>1.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="R19" t="n">
         <v>1.17</v>
@@ -5226,7 +5226,7 @@
         <v>1.46</v>
       </c>
       <c r="W19" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X19" t="n">
         <v>8.4</v>
@@ -5241,7 +5241,7 @@
         <v>65</v>
       </c>
       <c r="AB19" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AC19" t="n">
         <v>8</v>
@@ -5283,64 +5283,64 @@
         <v>75</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT19" t="n">
         <v>3.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AV19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY19" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AZ19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA19" t="n">
         <v>5</v>
       </c>
-      <c r="AX19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA19" t="n">
+      <c r="BB19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE19" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BF19" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH19" t="n">
         <v>2.64</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="BJ19" t="n">
         <v>12.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -5456,13 +5456,13 @@
         <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P20" t="n">
         <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>1.3</v>
@@ -5492,10 +5492,10 @@
         <v>19.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AC20" t="n">
         <v>8.800000000000001</v>
@@ -5504,7 +5504,7 @@
         <v>14</v>
       </c>
       <c r="AE20" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF20" t="n">
         <v>24</v>
@@ -5513,19 +5513,19 @@
         <v>15.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AJ20" t="n">
         <v>60</v>
       </c>
       <c r="AK20" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM20" t="n">
         <v>120</v>
@@ -5534,61 +5534,61 @@
         <v>42</v>
       </c>
       <c r="AO20" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AP20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG20" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4.9</v>
       </c>
       <c r="BH20" t="n">
         <v>3.35</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -5692,13 +5692,13 @@
         <v>2.58</v>
       </c>
       <c r="I21" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="K21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L21" t="n">
         <v>1.51</v>
@@ -5707,13 +5707,13 @@
         <v>1.11</v>
       </c>
       <c r="N21" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="O21" t="n">
         <v>1.53</v>
       </c>
       <c r="P21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q21" t="n">
         <v>2.56</v>
@@ -5722,16 +5722,16 @@
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U21" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="W21" t="n">
         <v>1.4</v>
@@ -5755,10 +5755,10 @@
         <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF21" t="n">
         <v>24</v>
@@ -5767,88 +5767,88 @@
         <v>17</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="n">
         <v>75</v>
       </c>
       <c r="AK21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO21" t="n">
         <v>55</v>
       </c>
-      <c r="AL21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>50</v>
-      </c>
       <c r="AP21" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AR21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX21" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW21" t="n">
+      <c r="AY21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA21" t="n">
         <v>5</v>
       </c>
-      <c r="AX21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA21" t="n">
+      <c r="BB21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE21" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BF21" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BH21" t="n">
         <v>2.78</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="BJ21" t="n">
         <v>11.5</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G22" t="n">
         <v>8.4</v>
@@ -5946,13 +5946,13 @@
         <v>1.68</v>
       </c>
       <c r="I22" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="K22" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
         <v>1.54</v>
@@ -5982,22 +5982,22 @@
         <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V22" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y22" t="n">
         <v>5.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA22" t="n">
         <v>21</v>
@@ -6006,7 +6006,7 @@
         <v>16</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD22" t="n">
         <v>13.5</v>
@@ -6030,73 +6030,73 @@
         <v>340</v>
       </c>
       <c r="AK22" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AL22" t="n">
         <v>230</v>
       </c>
       <c r="AM22" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AN22" t="n">
         <v>450</v>
       </c>
       <c r="AO22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP22" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AQ22" t="n">
         <v>4.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AS22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG22" t="n">
         <v>5.3</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>5.5</v>
       </c>
       <c r="BH22" t="n">
         <v>2.7</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -6194,16 +6194,16 @@
         <v>2.64</v>
       </c>
       <c r="G23" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="H23" t="n">
         <v>2.38</v>
       </c>
       <c r="I23" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="J23" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="K23" t="n">
         <v>4.3</v>
@@ -6215,7 +6215,7 @@
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
@@ -6230,7 +6230,7 @@
         <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="T23" t="n">
         <v>1.58</v>
@@ -6239,10 +6239,10 @@
         <v>2.32</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="X23" t="n">
         <v>24</v>
@@ -6257,7 +6257,7 @@
         <v>44</v>
       </c>
       <c r="AB23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC23" t="n">
         <v>11</v>
@@ -6296,61 +6296,61 @@
         <v>25</v>
       </c>
       <c r="AO23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AP23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>3.55</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW23" t="n">
+      <c r="BA23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF23" t="n">
         <v>3.7</v>
       </c>
-      <c r="AX23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BG23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BH23" t="n">
         <v>4.2</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
         <v>3.75</v>
       </c>
       <c r="L24" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
@@ -6496,7 +6496,7 @@
         <v>1.43</v>
       </c>
       <c r="W24" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X24" t="n">
         <v>20</v>
@@ -6514,7 +6514,7 @@
         <v>11.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
         <v>14.5</v>
@@ -6532,7 +6532,7 @@
         <v>17</v>
       </c>
       <c r="AI24" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ24" t="n">
         <v>55</v>
@@ -6574,7 +6574,7 @@
         <v>12.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX24" t="n">
         <v>13.5</v>
@@ -6595,13 +6595,13 @@
         <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BE24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG24" t="n">
         <v>20</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -6705,16 +6705,16 @@
         <v>2.5</v>
       </c>
       <c r="H25" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I25" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J25" t="n">
         <v>4.1</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.2</v>
@@ -6732,10 +6732,10 @@
         <v>3.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R25" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S25" t="n">
         <v>2.04</v>
@@ -6774,10 +6774,10 @@
         <v>14</v>
       </c>
       <c r="AE25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG25" t="n">
         <v>13</v>
@@ -6801,7 +6801,7 @@
         <v>100</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AO25" t="n">
         <v>12.5</v>
@@ -6867,7 +6867,7 @@
         <v>4.2</v>
       </c>
       <c r="BJ25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK25" t="n">
         <v>6.4</v>
@@ -6876,10 +6876,10 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO25" t="n">
         <v>4.9</v>
@@ -6897,22 +6897,22 @@
         <v>6.6</v>
       </c>
       <c r="BT25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU25" t="n">
         <v>5.8</v>
       </c>
       <c r="BV25" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BW25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX25" t="n">
         <v>23</v>
       </c>
       <c r="BY25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ25" t="n">
         <v>12.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
         <v>2.4</v>
       </c>
       <c r="I26" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>3.6</v>
@@ -6986,7 +6986,7 @@
         <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R26" t="n">
         <v>1.43</v>
@@ -7001,7 +7001,7 @@
         <v>2.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W26" t="n">
         <v>1.44</v>
@@ -7022,7 +7022,7 @@
         <v>15</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD26" t="n">
         <v>12</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="G27" t="n">
         <v>2.58</v>
@@ -7216,7 +7216,7 @@
         <v>3.1</v>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J27" t="n">
         <v>3.25</v>
@@ -7234,34 +7234,34 @@
         <v>3.05</v>
       </c>
       <c r="O27" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P27" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R27" t="n">
         <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="T27" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U27" t="n">
         <v>1.96</v>
       </c>
       <c r="V27" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W27" t="n">
         <v>1.63</v>
       </c>
       <c r="X27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y27" t="n">
         <v>12.5</v>
@@ -7270,7 +7270,7 @@
         <v>24</v>
       </c>
       <c r="AA27" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB27" t="n">
         <v>10</v>
@@ -7282,7 +7282,7 @@
         <v>15.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF27" t="n">
         <v>16.5</v>
@@ -7315,13 +7315,13 @@
         <v>50</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ27" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR27" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="AS27" t="n">
         <v>42</v>
@@ -7336,7 +7336,7 @@
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX27" t="n">
         <v>12.5</v>
@@ -7348,28 +7348,28 @@
         <v>15.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="BC27" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF27" t="n">
         <v>15.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI27" t="n">
         <v>2.6</v>
@@ -7378,59 +7378,59 @@
         <v>10.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>2.36</v>
+        <v>8.6</v>
       </c>
       <c r="BN27" t="n">
         <v>5.6</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP27" t="n">
         <v>21</v>
       </c>
       <c r="BQ27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT27" t="n">
         <v>6.8</v>
       </c>
       <c r="BU27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV27" t="n">
         <v>30</v>
       </c>
       <c r="BW27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>2.28</v>
+        <v>7.6</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -7464,13 +7464,13 @@
         <v>1.38</v>
       </c>
       <c r="G28" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H28" t="n">
         <v>9.6</v>
       </c>
       <c r="I28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J28" t="n">
         <v>5.1</v>
@@ -7494,13 +7494,13 @@
         <v>2.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R28" t="n">
         <v>1.51</v>
       </c>
       <c r="S28" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
         <v>2.08</v>
@@ -7530,7 +7530,7 @@
         <v>9</v>
       </c>
       <c r="AC28" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD28" t="n">
         <v>75</v>
@@ -7545,7 +7545,7 @@
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
@@ -7554,16 +7554,16 @@
         <v>11.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL28" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
@@ -7572,7 +7572,7 @@
         <v>17</v>
       </c>
       <c r="AQ28" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR28" t="n">
         <v>36</v>
@@ -7617,7 +7617,7 @@
         <v>44</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG28" t="n">
         <v>48</v>
@@ -7650,7 +7650,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BR28" t="n">
         <v>25</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -7730,10 +7730,10 @@
         <v>3.9</v>
       </c>
       <c r="K29" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
@@ -7763,10 +7763,10 @@
         <v>2.42</v>
       </c>
       <c r="V29" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W29" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X29" t="n">
         <v>21</v>
@@ -7775,7 +7775,7 @@
         <v>12.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA29" t="n">
         <v>32</v>
@@ -7793,10 +7793,10 @@
         <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG29" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH29" t="n">
         <v>17</v>
@@ -7853,7 +7853,7 @@
         <v>13</v>
       </c>
       <c r="AZ29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA29" t="n">
         <v>21</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -7969,19 +7969,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G30" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H30" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I30" t="n">
         <v>4.2</v>
       </c>
       <c r="J30" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="K30" t="n">
         <v>3.7</v>
@@ -7993,148 +7993,148 @@
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O30" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P30" t="n">
         <v>1.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
         <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="T30" t="n">
         <v>1.78</v>
       </c>
       <c r="U30" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V30" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W30" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA30" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC30" t="n">
         <v>9.4</v>
       </c>
-      <c r="AC30" t="n">
-        <v>8</v>
-      </c>
       <c r="AD30" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
         <v>65</v>
       </c>
       <c r="AJ30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK30" t="n">
         <v>32</v>
       </c>
-      <c r="AK30" t="n">
-        <v>28</v>
-      </c>
       <c r="AL30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM30" t="n">
         <v>130</v>
       </c>
       <c r="AN30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.7</v>
+        <v>17.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="AT30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA30" t="n">
         <v>4</v>
       </c>
-      <c r="AU30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BB30" t="n">
-        <v>5.7</v>
+        <v>3.85</v>
       </c>
       <c r="BC30" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="BD30" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="BE30" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="BG30" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="BH30" t="n">
         <v>3.4</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ30" t="n">
         <v>10.5</v>
@@ -8149,13 +8149,13 @@
         <v>2.5</v>
       </c>
       <c r="BN30" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO30" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BP30" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ30" t="n">
         <v>6.4</v>
@@ -8164,19 +8164,19 @@
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BT30" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>2.36</v>
+        <v>7.6</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
@@ -8188,11 +8188,11 @@
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>7.4</v>
+        <v>2.34</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -8226,10 +8226,10 @@
         <v>2.32</v>
       </c>
       <c r="G31" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H31" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I31" t="n">
         <v>3.5</v>
@@ -8238,16 +8238,16 @@
         <v>2.94</v>
       </c>
       <c r="K31" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L31" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O31" t="n">
         <v>1.33</v>
@@ -8256,121 +8256,121 @@
         <v>1.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T31" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U31" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V31" t="n">
         <v>1.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X31" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y31" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA31" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB31" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AF31" t="n">
         <v>19</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI31" t="n">
         <v>55</v>
       </c>
       <c r="AJ31" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK31" t="n">
         <v>34</v>
       </c>
       <c r="AL31" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM31" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN31" t="n">
         <v>26</v>
       </c>
       <c r="AO31" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS31" t="n">
         <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW31" t="n">
         <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA31" t="n">
         <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD31" t="n">
         <v>1.01</v>
@@ -8379,74 +8379,74 @@
         <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG31" t="n">
         <v>1.01</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BJ31" t="n">
         <v>10</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN31" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP31" t="n">
         <v>19.5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR31" t="n">
         <v>34</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT31" t="n">
         <v>6.8</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
         <v>2.02</v>
       </c>
       <c r="G32" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H32" t="n">
         <v>3.9</v>
@@ -8489,13 +8489,13 @@
         <v>4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K32" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
@@ -8507,7 +8507,7 @@
         <v>1.28</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q32" t="n">
         <v>1.84</v>
@@ -8528,7 +8528,7 @@
         <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X32" t="n">
         <v>16.5</v>
@@ -8543,13 +8543,13 @@
         <v>80</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC32" t="n">
         <v>8.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE32" t="n">
         <v>46</v>
@@ -8564,7 +8564,7 @@
         <v>17.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AJ32" t="n">
         <v>25</v>
@@ -8579,7 +8579,7 @@
         <v>85</v>
       </c>
       <c r="AN32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO32" t="n">
         <v>44</v>
@@ -8648,7 +8648,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -8731,13 +8731,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G33" t="n">
         <v>3.15</v>
       </c>
       <c r="H33" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I33" t="n">
         <v>2.78</v>
@@ -8746,37 +8746,37 @@
         <v>3.2</v>
       </c>
       <c r="K33" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
         <v>1.38</v>
       </c>
       <c r="P33" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q33" t="n">
         <v>2.12</v>
       </c>
       <c r="R33" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
         <v>3.9</v>
       </c>
       <c r="T33" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="U33" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="V33" t="n">
         <v>1.56</v>
@@ -8788,7 +8788,7 @@
         <v>14</v>
       </c>
       <c r="Y33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
         <v>20</v>
@@ -8800,7 +8800,7 @@
         <v>12.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD33" t="n">
         <v>14.5</v>
@@ -8809,13 +8809,13 @@
         <v>38</v>
       </c>
       <c r="AF33" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI33" t="n">
         <v>55</v>
@@ -8854,13 +8854,13 @@
         <v>8.4</v>
       </c>
       <c r="AU33" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV33" t="n">
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX33" t="n">
         <v>15</v>
@@ -8875,16 +8875,16 @@
         <v>34</v>
       </c>
       <c r="BB33" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BC33" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BD33" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BE33" t="n">
-        <v>80</v>
+        <v>1.03</v>
       </c>
       <c r="BF33" t="n">
         <v>28</v>
@@ -8893,13 +8893,13 @@
         <v>22</v>
       </c>
       <c r="BH33" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="BJ33" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK33" t="n">
         <v>6.4</v>
@@ -8911,10 +8911,10 @@
         <v>21</v>
       </c>
       <c r="BN33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BO33" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP33" t="n">
         <v>34</v>
@@ -8923,16 +8923,16 @@
         <v>15.5</v>
       </c>
       <c r="BR33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS33" t="n">
         <v>21</v>
       </c>
       <c r="BT33" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="BU33" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV33" t="n">
         <v>30</v>
@@ -8947,14 +8947,14 @@
         <v>21</v>
       </c>
       <c r="BZ33" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA33" t="n">
         <v>20</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
         <v>5.4</v>
       </c>
       <c r="I34" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J34" t="n">
         <v>3.35</v>
@@ -9003,22 +9003,22 @@
         <v>3.75</v>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M34" t="n">
         <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="O34" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P34" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R34" t="n">
         <v>1.23</v>
@@ -9039,10 +9039,10 @@
         <v>2.08</v>
       </c>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z34" t="n">
         <v>60</v>
@@ -9078,7 +9078,7 @@
         <v>21</v>
       </c>
       <c r="AK34" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AL34" t="n">
         <v>65</v>
@@ -9087,7 +9087,7 @@
         <v>200</v>
       </c>
       <c r="AN34" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AO34" t="n">
         <v>190</v>
@@ -9096,58 +9096,58 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ34" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR34" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AS34" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT34" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AV34" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX34" t="n">
         <v>7</v>
       </c>
       <c r="AY34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AZ34" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA34" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC34" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC34" t="n">
-        <v>7</v>
-      </c>
       <c r="BD34" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE34" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BH34" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI34" t="n">
         <v>2.48</v>
@@ -9162,7 +9162,7 @@
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="BN34" t="n">
         <v>4.2</v>
@@ -9180,7 +9180,7 @@
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT34" t="n">
         <v>9</v>
@@ -9192,23 +9192,23 @@
         <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA34" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BZ34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA34" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -9239,19 +9239,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G35" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H35" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
         <v>4.4</v>
@@ -9278,55 +9278,55 @@
         <v>1.6</v>
       </c>
       <c r="S35" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T35" t="n">
         <v>1.56</v>
       </c>
       <c r="U35" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V35" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W35" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X35" t="n">
         <v>29</v>
       </c>
       <c r="Y35" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z35" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA35" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB35" t="n">
         <v>14.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD35" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AF35" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG35" t="n">
         <v>11.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ35" t="n">
         <v>25</v>
@@ -9335,76 +9335,76 @@
         <v>19</v>
       </c>
       <c r="AL35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM35" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN35" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AO35" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS35" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ35" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR35" t="n">
+      <c r="AT35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY35" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AS35" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AZ35" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BA35" t="n">
         <v>32</v>
       </c>
       <c r="BB35" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC35" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD35" t="n">
         <v>6.4</v>
       </c>
-      <c r="BD35" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE35" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF35" t="n">
         <v>8</v>
       </c>
       <c r="BG35" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="BH35" t="n">
         <v>4.6</v>
       </c>
       <c r="BI35" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="BJ35" t="n">
         <v>9</v>
@@ -9416,10 +9416,10 @@
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN35" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO35" t="n">
         <v>4.5</v>
@@ -9428,41 +9428,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ35" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR35" t="n">
         <v>23</v>
       </c>
       <c r="BS35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT35" t="n">
         <v>7.8</v>
       </c>
       <c r="BU35" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV35" t="n">
         <v>27</v>
       </c>
       <c r="BW35" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX35" t="n">
         <v>32</v>
       </c>
       <c r="BY35" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ35" t="n">
         <v>16</v>
       </c>
       <c r="CA35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -9493,25 +9493,25 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G36" t="n">
         <v>1.38</v>
       </c>
       <c r="H36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J36" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K36" t="n">
         <v>6.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M36" t="n">
         <v>1.03</v>
@@ -9538,7 +9538,7 @@
         <v>1.91</v>
       </c>
       <c r="U36" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>1.1</v>
@@ -9550,13 +9550,13 @@
         <v>28</v>
       </c>
       <c r="Y36" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z36" t="n">
         <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="AB36" t="n">
         <v>11</v>
@@ -9601,13 +9601,13 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR36" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS36" t="n">
         <v>55</v>
@@ -9619,22 +9619,22 @@
         <v>11.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW36" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX36" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ36" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA36" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB36" t="n">
         <v>10</v>
@@ -9658,22 +9658,22 @@
         <v>4.6</v>
       </c>
       <c r="BI36" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="BJ36" t="n">
         <v>12</v>
       </c>
       <c r="BK36" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN36" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO36" t="n">
         <v>3.25</v>
@@ -9688,25 +9688,25 @@
         <v>22</v>
       </c>
       <c r="BS36" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT36" t="n">
         <v>13.5</v>
       </c>
       <c r="BU36" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV36" t="n">
         <v>80</v>
       </c>
       <c r="BW36" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX36" t="n">
         <v>70</v>
       </c>
       <c r="BY36" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
         <v>2.96</v>
       </c>
       <c r="H37" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I37" t="n">
         <v>2.7</v>
@@ -9810,7 +9810,7 @@
         <v>19</v>
       </c>
       <c r="AA37" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AB37" t="n">
         <v>13</v>
@@ -9849,7 +9849,7 @@
         <v>100</v>
       </c>
       <c r="AN37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AO37" t="n">
         <v>27</v>
@@ -9858,13 +9858,13 @@
         <v>13</v>
       </c>
       <c r="AQ37" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR37" t="n">
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT37" t="n">
         <v>10.5</v>
@@ -9876,7 +9876,7 @@
         <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX37" t="n">
         <v>17</v>
@@ -9888,7 +9888,7 @@
         <v>14.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB37" t="n">
         <v>6.6</v>
@@ -9897,10 +9897,10 @@
         <v>6.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF37" t="n">
         <v>19.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G38" t="n">
         <v>1000</v>
@@ -10013,7 +10013,7 @@
         <v>2.24</v>
       </c>
       <c r="J38" t="n">
-        <v>1.83</v>
+        <v>5.7</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
@@ -10052,7 +10052,7 @@
         <v>1.8</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -10267,13 +10267,13 @@
         <v>2.22</v>
       </c>
       <c r="J39" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K39" t="n">
         <v>4.3</v>
       </c>
       <c r="L39" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="M39" t="n">
         <v>1.03</v>
@@ -10285,13 +10285,13 @@
         <v>1.18</v>
       </c>
       <c r="P39" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q39" t="n">
         <v>1.54</v>
       </c>
       <c r="R39" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S39" t="n">
         <v>2.34</v>
@@ -10339,7 +10339,7 @@
         <v>15</v>
       </c>
       <c r="AH39" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI39" t="n">
         <v>34</v>
@@ -10396,7 +10396,7 @@
         <v>13</v>
       </c>
       <c r="BA39" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB39" t="n">
         <v>40</v>
@@ -10405,19 +10405,19 @@
         <v>6.8</v>
       </c>
       <c r="BD39" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF39" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="BG39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH39" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI39" t="n">
         <v>3.5</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -10509,166 +10509,166 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="G40" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="H40" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="I40" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="J40" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K40" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="O40" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="P40" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="R40" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="S40" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="T40" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="U40" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="V40" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="W40" t="n">
         <v>1.1</v>
       </c>
       <c r="X40" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Y40" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AA40" t="n">
         <v>15</v>
       </c>
       <c r="AB40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC40" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD40" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE40" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AF40" t="n">
         <v>100</v>
       </c>
       <c r="AG40" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AH40" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AI40" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AJ40" t="n">
-        <v>480</v>
+        <v>390</v>
       </c>
       <c r="AK40" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="AL40" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM40" t="n">
         <v>200</v>
       </c>
-      <c r="AM40" t="n">
+      <c r="AN40" t="n">
         <v>270</v>
       </c>
-      <c r="AN40" t="n">
-        <v>410</v>
-      </c>
       <c r="AO40" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -10766,19 +10766,19 @@
         <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H41" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I41" t="n">
         <v>1.59</v>
       </c>
-      <c r="I41" t="n">
-        <v>1.61</v>
-      </c>
       <c r="J41" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K41" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L41" t="n">
         <v>1.27</v>
@@ -10808,82 +10808,82 @@
         <v>1.64</v>
       </c>
       <c r="U41" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V41" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="W41" t="n">
         <v>1.19</v>
       </c>
       <c r="X41" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Y41" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z41" t="n">
         <v>12.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AB41" t="n">
         <v>30</v>
       </c>
       <c r="AC41" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD41" t="n">
         <v>10.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF41" t="n">
         <v>55</v>
       </c>
       <c r="AG41" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH41" t="n">
         <v>17.5</v>
       </c>
       <c r="AI41" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ41" t="n">
         <v>1000</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL41" t="n">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="AM41" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN41" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO41" t="n">
         <v>5.8</v>
       </c>
       <c r="AP41" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ41" t="n">
         <v>12</v>
       </c>
       <c r="AR41" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS41" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT41" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="AU41" t="n">
         <v>10</v>
@@ -10895,34 +10895,34 @@
         <v>13</v>
       </c>
       <c r="AX41" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AY41" t="n">
         <v>21</v>
       </c>
       <c r="AZ41" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA41" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BB41" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BC41" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BD41" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BE41" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF41" t="n">
         <v>28</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH41" t="n">
         <v>4.7</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
         <v>5.3</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K42" t="n">
         <v>4.3</v>
@@ -11077,7 +11077,7 @@
         <v>24</v>
       </c>
       <c r="Z42" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA42" t="n">
         <v>130</v>
@@ -11116,7 +11116,7 @@
         <v>32</v>
       </c>
       <c r="AM42" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN42" t="n">
         <v>9.199999999999999</v>
@@ -11125,7 +11125,7 @@
         <v>70</v>
       </c>
       <c r="AP42" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AQ42" t="n">
         <v>17.5</v>
@@ -11143,10 +11143,10 @@
         <v>8.6</v>
       </c>
       <c r="AV42" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX42" t="n">
         <v>9</v>
@@ -11158,10 +11158,10 @@
         <v>14</v>
       </c>
       <c r="BA42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB42" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC42" t="n">
         <v>13</v>
@@ -11173,10 +11173,10 @@
         <v>6.4</v>
       </c>
       <c r="BF42" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH42" t="n">
         <v>3.9</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -11271,175 +11271,175 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="G43" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="H43" t="n">
         <v>7</v>
       </c>
       <c r="I43" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X43" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU43" t="n">
         <v>9.6</v>
       </c>
-      <c r="J43" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N43" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W43" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X43" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>350</v>
-      </c>
-      <c r="AB43" t="n">
+      <c r="AV43" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB43" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC43" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BC43" t="n">
-        <v>3.95</v>
+        <v>13.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.5</v>
+        <v>25</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG43" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BH43" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI43" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ43" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK43" t="n">
         <v>1.01</v>
@@ -11451,25 +11451,25 @@
         <v>1.01</v>
       </c>
       <c r="BN43" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO43" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP43" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ43" t="n">
         <v>1.01</v>
       </c>
       <c r="BR43" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS43" t="n">
         <v>1.01</v>
       </c>
       <c r="BT43" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G44" t="n">
         <v>1.84</v>
@@ -11540,13 +11540,13 @@
         <v>3.9</v>
       </c>
       <c r="K44" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L44" t="n">
         <v>1.3</v>
       </c>
       <c r="M44" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N44" t="n">
         <v>4.3</v>
@@ -11558,13 +11558,13 @@
         <v>2.14</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R44" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S44" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
         <v>1.78</v>
@@ -11573,7 +11573,7 @@
         <v>2.18</v>
       </c>
       <c r="V44" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W44" t="n">
         <v>2.18</v>
@@ -11591,7 +11591,7 @@
         <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC44" t="n">
         <v>9.199999999999999</v>
@@ -11603,13 +11603,13 @@
         <v>70</v>
       </c>
       <c r="AF44" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG44" t="n">
         <v>10</v>
       </c>
       <c r="AH44" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI44" t="n">
         <v>75</v>
@@ -11618,7 +11618,7 @@
         <v>23</v>
       </c>
       <c r="AK44" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL44" t="n">
         <v>38</v>
@@ -11627,7 +11627,7 @@
         <v>110</v>
       </c>
       <c r="AN44" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO44" t="n">
         <v>75</v>
@@ -11666,16 +11666,16 @@
         <v>16</v>
       </c>
       <c r="BA44" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BB44" t="n">
         <v>17</v>
       </c>
       <c r="BC44" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD44" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BE44" t="n">
         <v>38</v>
@@ -11684,13 +11684,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG44" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BH44" t="n">
         <v>3.75</v>
       </c>
       <c r="BI44" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ44" t="n">
         <v>9.6</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -11779,22 +11779,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.36</v>
+        <v>2.88</v>
       </c>
       <c r="G45" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="H45" t="n">
-        <v>1.37</v>
+        <v>2.42</v>
       </c>
       <c r="I45" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="K45" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
@@ -11803,22 +11803,22 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.53</v>
+        <v>2.34</v>
       </c>
       <c r="O45" t="n">
         <v>1.01</v>
       </c>
       <c r="P45" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.05</v>
+        <v>2.34</v>
       </c>
       <c r="R45" t="n">
         <v>1.14</v>
       </c>
       <c r="S45" t="n">
-        <v>1.42</v>
+        <v>2.96</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -11827,10 +11827,10 @@
         <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -12033,40 +12033,40 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G46" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H46" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I46" t="n">
         <v>2.82</v>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K46" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L46" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M46" t="n">
         <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O46" t="n">
         <v>1.43</v>
       </c>
       <c r="P46" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R46" t="n">
         <v>1.24</v>
@@ -12075,16 +12075,16 @@
         <v>4.3</v>
       </c>
       <c r="T46" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U46" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V46" t="n">
         <v>1.55</v>
       </c>
       <c r="W46" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X46" t="n">
         <v>13</v>
@@ -12099,7 +12099,7 @@
         <v>55</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC46" t="n">
         <v>8.6</v>
@@ -12111,13 +12111,13 @@
         <v>42</v>
       </c>
       <c r="AF46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG46" t="n">
         <v>17</v>
       </c>
       <c r="AH46" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI46" t="n">
         <v>65</v>
@@ -12141,28 +12141,28 @@
         <v>42</v>
       </c>
       <c r="AP46" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AQ46" t="n">
         <v>7.8</v>
       </c>
       <c r="AR46" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AS46" t="n">
-        <v>30</v>
+        <v>4.6</v>
       </c>
       <c r="AT46" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU46" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV46" t="n">
         <v>10.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX46" t="n">
         <v>17.5</v>
@@ -12174,46 +12174,46 @@
         <v>16.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>4.4</v>
+        <v>44</v>
       </c>
       <c r="BB46" t="n">
-        <v>4.4</v>
+        <v>40</v>
       </c>
       <c r="BC46" t="n">
-        <v>34</v>
+        <v>4.6</v>
       </c>
       <c r="BD46" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE46" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF46" t="n">
         <v>32</v>
       </c>
       <c r="BG46" t="n">
-        <v>25</v>
+        <v>4.5</v>
       </c>
       <c r="BH46" t="n">
         <v>3.05</v>
       </c>
       <c r="BI46" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BJ46" t="n">
         <v>10.5</v>
       </c>
       <c r="BK46" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN46" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO46" t="n">
         <v>4.6</v>
@@ -12222,13 +12222,13 @@
         <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT46" t="n">
         <v>5.6</v>
@@ -12240,23 +12240,23 @@
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ46" t="n">
         <v>1000</v>
       </c>
       <c r="CA46" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -12290,28 +12290,28 @@
         <v>4.3</v>
       </c>
       <c r="G47" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H47" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I47" t="n">
         <v>2.06</v>
       </c>
       <c r="J47" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K47" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L47" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M47" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
         <v>1.41</v>
@@ -12320,7 +12320,7 @@
         <v>1.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R47" t="n">
         <v>1.26</v>
@@ -12329,16 +12329,16 @@
         <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="U47" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="V47" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W47" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X47" t="n">
         <v>13.5</v>
@@ -12347,13 +12347,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z47" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA47" t="n">
         <v>27</v>
       </c>
       <c r="AB47" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC47" t="n">
         <v>9.199999999999999</v>
@@ -12362,13 +12362,13 @@
         <v>12.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF47" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AG47" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH47" t="n">
         <v>25</v>
@@ -12389,7 +12389,7 @@
         <v>170</v>
       </c>
       <c r="AN47" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AO47" t="n">
         <v>21</v>
@@ -12401,10 +12401,10 @@
         <v>6</v>
       </c>
       <c r="AR47" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS47" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT47" t="n">
         <v>10.5</v>
@@ -12416,46 +12416,46 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW47" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AX47" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AY47" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ47" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA47" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BB47" t="n">
-        <v>85</v>
+        <v>1.03</v>
       </c>
       <c r="BC47" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BD47" t="n">
-        <v>60</v>
+        <v>1.03</v>
       </c>
       <c r="BE47" t="n">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="BF47" t="n">
         <v>70</v>
       </c>
       <c r="BG47" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH47" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="BI47" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="BJ47" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BK47" t="n">
         <v>7</v>
@@ -12467,50 +12467,50 @@
         <v>21</v>
       </c>
       <c r="BN47" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BO47" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BP47" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ47" t="n">
         <v>21</v>
       </c>
       <c r="BR47" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BS47" t="n">
         <v>21</v>
       </c>
       <c r="BT47" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BU47" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BV47" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BW47" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BX47" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BY47" t="n">
         <v>20</v>
       </c>
       <c r="BZ47" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="CA47" t="n">
         <v>19</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -12541,31 +12541,31 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="I48" t="n">
-        <v>140</v>
+        <v>3.55</v>
       </c>
       <c r="J48" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="K48" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L48" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M48" t="n">
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O48" t="n">
         <v>1.13</v>
@@ -12589,7 +12589,7 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -13061,10 +13061,10 @@
         <v>1.97</v>
       </c>
       <c r="J50" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K50" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L50" t="n">
         <v>1.34</v>
@@ -13079,22 +13079,22 @@
         <v>1.34</v>
       </c>
       <c r="P50" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q50" t="n">
         <v>1.99</v>
       </c>
       <c r="R50" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S50" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T50" t="n">
         <v>1.86</v>
       </c>
       <c r="U50" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V50" t="n">
         <v>2.02</v>
@@ -13115,10 +13115,10 @@
         <v>26</v>
       </c>
       <c r="AB50" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC50" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD50" t="n">
         <v>12.5</v>
@@ -13166,7 +13166,7 @@
         <v>10</v>
       </c>
       <c r="AS50" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AT50" t="n">
         <v>11.5</v>
@@ -13178,10 +13178,10 @@
         <v>9</v>
       </c>
       <c r="AW50" t="n">
-        <v>18</v>
+        <v>3.6</v>
       </c>
       <c r="AX50" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AY50" t="n">
         <v>13.5</v>
@@ -13190,7 +13190,7 @@
         <v>14.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BB50" t="n">
         <v>4.1</v>
@@ -13205,7 +13205,7 @@
         <v>4.1</v>
       </c>
       <c r="BF50" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG50" t="n">
         <v>10.5</v>
@@ -13232,7 +13232,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO50" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BP50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -13306,43 +13306,43 @@
         <v>1.02</v>
       </c>
       <c r="G51" t="n">
-        <v>110</v>
+        <v>2.5</v>
       </c>
       <c r="H51" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O51" t="n">
         <v>1.02</v>
       </c>
-      <c r="I51" t="n">
-        <v>110</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K51" t="n">
-        <v>950</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P51" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R51" t="n">
         <v>1.18</v>
       </c>
       <c r="S51" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="T51" t="n">
         <v>1.01</v>
@@ -13354,7 +13354,7 @@
         <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -13560,13 +13560,13 @@
         <v>2.04</v>
       </c>
       <c r="G52" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H52" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I52" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J52" t="n">
         <v>3.25</v>
@@ -13593,22 +13593,22 @@
         <v>2.22</v>
       </c>
       <c r="R52" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S52" t="n">
         <v>2.22</v>
       </c>
       <c r="T52" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U52" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V52" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W52" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -13617,19 +13617,19 @@
         <v>1000</v>
       </c>
       <c r="Z52" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA52" t="n">
         <v>1000</v>
       </c>
       <c r="AB52" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC52" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD52" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE52" t="n">
         <v>1000</v>
@@ -13647,10 +13647,10 @@
         <v>1000</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK52" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL52" t="n">
         <v>1000</v>
@@ -13665,52 +13665,52 @@
         <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF52" t="n">
         <v>1.01</v>
@@ -13737,7 +13737,7 @@
         <v>21</v>
       </c>
       <c r="BN52" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO52" t="n">
         <v>3.3</v>
@@ -13749,13 +13749,13 @@
         <v>10.5</v>
       </c>
       <c r="BR52" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS52" t="n">
         <v>21</v>
       </c>
       <c r="BT52" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU52" t="n">
         <v>4.9</v>
@@ -13773,14 +13773,14 @@
         <v>21</v>
       </c>
       <c r="BZ52" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="CA52" t="n">
         <v>21</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -13817,13 +13817,13 @@
         <v>1000</v>
       </c>
       <c r="H53" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="I53" t="n">
         <v>2.84</v>
       </c>
       <c r="J53" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K53" t="n">
         <v>1000</v>
@@ -13862,7 +13862,7 @@
         <v>1.54</v>
       </c>
       <c r="W53" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -14089,22 +14089,22 @@
         <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O54" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P54" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R54" t="n">
         <v>1.18</v>
       </c>
       <c r="S54" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T54" t="n">
         <v>1.01</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G55" t="n">
         <v>2.82</v>
@@ -14328,7 +14328,7 @@
         <v>3.2</v>
       </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J55" t="n">
         <v>2.84</v>
@@ -14364,10 +14364,10 @@
         <v>2.12</v>
       </c>
       <c r="U55" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V55" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W55" t="n">
         <v>1.55</v>
@@ -14382,10 +14382,10 @@
         <v>27</v>
       </c>
       <c r="AA55" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB55" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC55" t="n">
         <v>8.6</v>
@@ -14397,7 +14397,7 @@
         <v>70</v>
       </c>
       <c r="AF55" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG55" t="n">
         <v>16</v>
@@ -14427,16 +14427,16 @@
         <v>100</v>
       </c>
       <c r="AP55" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ55" t="n">
         <v>7.8</v>
       </c>
       <c r="AR55" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT55" t="n">
         <v>6.4</v>
@@ -14448,7 +14448,7 @@
         <v>13</v>
       </c>
       <c r="AW55" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AX55" t="n">
         <v>11</v>
@@ -14460,25 +14460,25 @@
         <v>20</v>
       </c>
       <c r="BA55" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB55" t="n">
-        <v>4.4</v>
+        <v>34</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE55" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BF55" t="n">
-        <v>4.4</v>
+        <v>36</v>
       </c>
       <c r="BG55" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH55" t="n">
         <v>2.68</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -860,7 +860,7 @@
         <v>1.94</v>
       </c>
       <c r="G2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -875,13 +875,13 @@
         <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O2" t="n">
         <v>1.41</v>
@@ -896,7 +896,7 @@
         <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
         <v>1.93</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1.76</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
         <v>7.2</v>
@@ -1126,10 +1126,10 @@
         <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1138,7 +1138,7 @@
         <v>2.96</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
         <v>1.67</v>
@@ -1159,7 +1159,7 @@
         <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
         <v>2.3</v>
@@ -1222,10 +1222,10 @@
         <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS3" t="n">
         <v>6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H4" t="n">
         <v>4.1</v>
@@ -1386,19 +1386,19 @@
         <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
         <v>1.25</v>
@@ -1410,7 +1410,7 @@
         <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V4" t="n">
         <v>1.3</v>
@@ -1452,7 +1452,7 @@
         <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>170</v>
+        <v>370</v>
       </c>
       <c r="AJ4" t="n">
         <v>25</v>
@@ -1470,7 +1470,7 @@
         <v>21</v>
       </c>
       <c r="AO4" t="n">
-        <v>180</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
@@ -1497,7 +1497,7 @@
         <v>23</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.6</v>
@@ -1506,7 +1506,7 @@
         <v>19.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
@@ -1548,7 +1548,7 @@
         <v>4.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BP4" t="n">
         <v>16.5</v>
@@ -1566,7 +1566,7 @@
         <v>7.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV4" t="n">
         <v>42</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G5" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="H5" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I5" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J5" t="n">
         <v>3.5</v>
@@ -1649,7 +1649,7 @@
         <v>1.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -1667,10 +1667,10 @@
         <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
@@ -1688,7 +1688,7 @@
         <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
         <v>13</v>
@@ -1706,7 +1706,7 @@
         <v>17.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AJ5" t="n">
         <v>46</v>
@@ -1724,7 +1724,7 @@
         <v>26</v>
       </c>
       <c r="AO5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP5" t="n">
         <v>12.5</v>
@@ -1748,7 +1748,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX5" t="n">
         <v>15</v>
@@ -1760,16 +1760,16 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC5" t="n">
         <v>23</v>
       </c>
       <c r="BD5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE5" t="n">
         <v>36</v>
@@ -1778,7 +1778,7 @@
         <v>21</v>
       </c>
       <c r="BG5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BH5" t="n">
         <v>3.45</v>
@@ -1820,7 +1820,7 @@
         <v>6.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV5" t="n">
         <v>24</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
         <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q6" t="n">
         <v>2.38</v>
@@ -1918,7 +1918,7 @@
         <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V6" t="n">
         <v>2.5</v>
@@ -1936,7 +1936,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AB6" t="n">
         <v>18</v>
@@ -1972,7 +1972,7 @@
         <v>440</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
         <v>1000</v>
@@ -2005,7 +2005,7 @@
         <v>18.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AY6" t="n">
         <v>23</v>
@@ -2014,7 +2014,7 @@
         <v>24</v>
       </c>
       <c r="BA6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB6" t="n">
         <v>48</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>1.92</v>
       </c>
       <c r="G7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
         <v>3.5</v>
@@ -2151,13 +2151,13 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
         <v>1.99</v>
@@ -2175,10 +2175,10 @@
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X7" t="n">
         <v>14</v>
@@ -2193,7 +2193,7 @@
         <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7" t="n">
         <v>8.4</v>
@@ -2214,10 +2214,10 @@
         <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK7" t="n">
         <v>23</v>
@@ -2229,7 +2229,7 @@
         <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
         <v>75</v>
@@ -2238,13 +2238,13 @@
         <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT7" t="n">
         <v>7.4</v>
@@ -2265,10 +2265,10 @@
         <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB7" t="n">
         <v>19.5</v>
@@ -2286,25 +2286,25 @@
         <v>13</v>
       </c>
       <c r="BG7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN7" t="n">
         <v>4.8</v>
@@ -2316,41 +2316,41 @@
         <v>15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
         <v>32</v>
       </c>
       <c r="BS7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT7" t="n">
         <v>8</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV7" t="n">
         <v>40</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>28</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="G8" t="n">
         <v>11</v>
@@ -2426,7 +2426,7 @@
         <v>2.06</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
         <v>3.35</v>
@@ -2468,13 +2468,13 @@
         <v>34</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AK8" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AL8" t="n">
         <v>470</v>
@@ -2519,10 +2519,10 @@
         <v>26</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB8" t="n">
         <v>38</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2665,7 +2665,7 @@
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
         <v>2.02</v>
@@ -2692,10 +2692,10 @@
         <v>13.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA9" t="n">
         <v>65</v>
@@ -2707,19 +2707,19 @@
         <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
         <v>65</v>
@@ -2752,7 +2752,7 @@
         <v>20</v>
       </c>
       <c r="AS9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT9" t="n">
         <v>8.6</v>
@@ -2782,25 +2782,25 @@
         <v>26</v>
       </c>
       <c r="BC9" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="BF9" t="n">
         <v>20</v>
       </c>
       <c r="BG9" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BH9" t="n">
         <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2827,7 +2827,7 @@
         <v>6.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS9" t="n">
         <v>7.6</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -2889,25 +2889,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="G10" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
@@ -2919,10 +2919,10 @@
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
         <v>1.3</v>
@@ -2931,16 +2931,16 @@
         <v>3.95</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
         <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="X10" t="n">
         <v>14</v>
@@ -2955,7 +2955,7 @@
         <v>130</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC10" t="n">
         <v>9.4</v>
@@ -2967,7 +2967,7 @@
         <v>150</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
         <v>10.5</v>
@@ -3000,10 +3000,10 @@
         <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS10" t="n">
         <v>70</v>
@@ -3027,16 +3027,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD10" t="n">
         <v>28</v>
@@ -3045,34 +3045,34 @@
         <v>85</v>
       </c>
       <c r="BF10" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BG10" t="n">
         <v>46</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
@@ -3084,35 +3084,35 @@
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>12</v>
       </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G11" t="n">
         <v>3.25</v>
@@ -3170,7 +3170,7 @@
         <v>4.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P11" t="n">
         <v>2.14</v>
@@ -3182,7 +3182,7 @@
         <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
         <v>1.7</v>
@@ -3191,13 +3191,13 @@
         <v>2.36</v>
       </c>
       <c r="V11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W11" t="n">
         <v>1.44</v>
       </c>
       <c r="X11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="n">
         <v>19.5</v>
@@ -3212,7 +3212,7 @@
         <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
         <v>12.5</v>
@@ -3230,7 +3230,7 @@
         <v>16</v>
       </c>
       <c r="AI11" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AJ11" t="n">
         <v>440</v>
@@ -3242,7 +3242,7 @@
         <v>100</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
         <v>32</v>
@@ -3257,7 +3257,7 @@
         <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS11" t="n">
         <v>15</v>
@@ -3287,86 +3287,86 @@
         <v>16</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BC11" t="n">
         <v>16.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BG11" t="n">
         <v>14.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BP11" t="n">
         <v>24</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV11" t="n">
         <v>18</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -3415,13 +3415,13 @@
         <v>5.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.15</v>
@@ -3442,10 +3442,10 @@
         <v>1.63</v>
       </c>
       <c r="U12" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W12" t="n">
         <v>2.92</v>
@@ -3457,13 +3457,13 @@
         <v>42</v>
       </c>
       <c r="Z12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA12" t="n">
         <v>200</v>
       </c>
       <c r="AB12" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC12" t="n">
         <v>12.5</v>
@@ -3472,40 +3472,40 @@
         <v>32</v>
       </c>
       <c r="AE12" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH12" t="n">
         <v>18.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AJ12" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL12" t="n">
         <v>30</v>
       </c>
       <c r="AM12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN12" t="n">
         <v>4.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AP12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -3514,7 +3514,7 @@
         <v>48</v>
       </c>
       <c r="AS12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT12" t="n">
         <v>13.5</v>
@@ -3529,7 +3529,7 @@
         <v>42</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY12" t="n">
         <v>9.800000000000001</v>
@@ -3541,7 +3541,7 @@
         <v>44</v>
       </c>
       <c r="BB12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC12" t="n">
         <v>12.5</v>
@@ -3550,7 +3550,7 @@
         <v>22</v>
       </c>
       <c r="BE12" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BF12" t="n">
         <v>4.5</v>
@@ -3580,7 +3580,7 @@
         <v>4.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP12" t="n">
         <v>8.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G13" t="n">
         <v>6.6</v>
@@ -3660,7 +3660,7 @@
         <v>1.66</v>
       </c>
       <c r="I13" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>3.6</v>
@@ -3687,7 +3687,7 @@
         <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
         <v>3.6</v>
@@ -3699,7 +3699,7 @@
         <v>1.86</v>
       </c>
       <c r="V13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W13" t="n">
         <v>1.18</v>
@@ -3840,7 +3840,7 @@
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3864,17 +3864,17 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA13" t="n">
         <v>7.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -3938,10 +3938,10 @@
         <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
         <v>2.72</v>
@@ -3983,10 +3983,10 @@
         <v>400</v>
       </c>
       <c r="AF14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH14" t="n">
         <v>23</v>
@@ -4004,52 +4004,52 @@
         <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AO14" t="n">
         <v>440</v>
       </c>
       <c r="AP14" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AQ14" t="n">
         <v>17.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AV14" t="n">
         <v>18</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC14" t="n">
         <v>11.5</v>
@@ -4058,13 +4058,13 @@
         <v>16</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF14" t="n">
         <v>6.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH14" t="n">
         <v>4.1</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
         <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
@@ -4210,7 +4210,7 @@
         <v>1.34</v>
       </c>
       <c r="W15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X15" t="n">
         <v>14.5</v>
@@ -4222,7 +4222,7 @@
         <v>30</v>
       </c>
       <c r="AA15" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AB15" t="n">
         <v>9.199999999999999</v>
@@ -4234,7 +4234,7 @@
         <v>18</v>
       </c>
       <c r="AE15" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AF15" t="n">
         <v>14.5</v>
@@ -4243,28 +4243,28 @@
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AK15" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AL15" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM15" t="n">
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AO15" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AP15" t="n">
         <v>10.5</v>
@@ -4273,10 +4273,10 @@
         <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.8</v>
+        <v>46</v>
       </c>
       <c r="AT15" t="n">
         <v>8</v>
@@ -4288,7 +4288,7 @@
         <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="AX15" t="n">
         <v>12</v>
@@ -4300,25 +4300,25 @@
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BB15" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.4</v>
+        <v>26</v>
       </c>
       <c r="BE15" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BF15" t="n">
         <v>18.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.4</v>
+        <v>27</v>
       </c>
       <c r="BH15" t="n">
         <v>3.2</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>4.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="I16" t="n">
         <v>2.3</v>
@@ -4431,7 +4431,7 @@
         <v>3.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M16" t="n">
         <v>1.1</v>
@@ -4509,7 +4509,7 @@
         <v>60</v>
       </c>
       <c r="AL16" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
@@ -4521,64 +4521,64 @@
         <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU16" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6</v>
       </c>
       <c r="AV16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG16" t="n">
         <v>20</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>18</v>
       </c>
       <c r="BH16" t="n">
         <v>3.05</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.34</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H17" t="n">
         <v>11</v>
@@ -4682,7 +4682,7 @@
         <v>5.1</v>
       </c>
       <c r="K17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L17" t="n">
         <v>1.3</v>
@@ -4721,7 +4721,7 @@
         <v>3.5</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
         <v>38</v>
@@ -4736,7 +4736,7 @@
         <v>9</v>
       </c>
       <c r="AC17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
         <v>55</v>
@@ -4760,7 +4760,7 @@
         <v>13</v>
       </c>
       <c r="AK17" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AL17" t="n">
         <v>60</v>
@@ -4778,13 +4778,13 @@
         <v>15</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT17" t="n">
         <v>6.6</v>
@@ -4793,10 +4793,10 @@
         <v>10.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AX17" t="n">
         <v>6.6</v>
@@ -4805,10 +4805,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BB17" t="n">
         <v>9.199999999999999</v>
@@ -4817,16 +4817,16 @@
         <v>14</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
         <v>5.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH17" t="n">
         <v>3.75</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G18" t="n">
         <v>2.34</v>
       </c>
       <c r="H18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L18" t="n">
         <v>1.46</v>
@@ -4960,7 +4960,7 @@
         <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>1.08</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
@@ -4969,10 +4969,10 @@
         <v>1.82</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X18" t="n">
         <v>10.5</v>
@@ -5002,10 +5002,10 @@
         <v>13.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
         <v>500</v>
@@ -5017,76 +5017,76 @@
         <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AM18" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
         <v>32</v>
       </c>
       <c r="AO18" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD18" t="n">
         <v>5.9</v>
       </c>
-      <c r="AT18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD18" t="n">
+      <c r="BE18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF18" t="n">
         <v>5.5</v>
       </c>
-      <c r="BE18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG18" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH18" t="n">
         <v>2.96</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="BJ18" t="n">
         <v>11.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
         <v>7.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE19" t="n">
         <v>55</v>
@@ -5277,70 +5277,70 @@
         <v>500</v>
       </c>
       <c r="AN19" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO19" t="n">
         <v>75</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AR19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AV19" t="n">
         <v>4.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BA19" t="n">
         <v>6.4</v>
       </c>
       <c r="BB19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC19" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC19" t="n">
-        <v>6</v>
-      </c>
       <c r="BD19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF19" t="n">
         <v>6.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH19" t="n">
         <v>2.64</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="BJ19" t="n">
         <v>12.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O20" t="n">
         <v>1.35</v>
@@ -5468,7 +5468,7 @@
         <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
         <v>1.78</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -5692,13 +5692,13 @@
         <v>2.18</v>
       </c>
       <c r="I21" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J21" t="n">
         <v>2.92</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L21" t="n">
         <v>1.5</v>
@@ -5707,7 +5707,7 @@
         <v>1.11</v>
       </c>
       <c r="N21" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="O21" t="n">
         <v>1.52</v>
@@ -5716,22 +5716,22 @@
         <v>1.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="R21" t="n">
         <v>1.19</v>
       </c>
       <c r="S21" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V21" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W21" t="n">
         <v>1.29</v>
@@ -5764,7 +5764,7 @@
         <v>29</v>
       </c>
       <c r="AG21" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AH21" t="n">
         <v>25</v>
@@ -5797,10 +5797,10 @@
         <v>4.9</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT21" t="n">
         <v>5.6</v>
@@ -5809,40 +5809,40 @@
         <v>4.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AW21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX21" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9</v>
       </c>
       <c r="AY21" t="n">
         <v>5.9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC21" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH21" t="n">
         <v>2.8</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>5.7</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H22" t="n">
         <v>1.68</v>
@@ -5967,7 +5967,7 @@
         <v>1.58</v>
       </c>
       <c r="P22" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q22" t="n">
         <v>2.6</v>
@@ -5988,7 +5988,7 @@
         <v>2.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
         <v>8.4</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G23" t="n">
         <v>3.1</v>
       </c>
       <c r="H23" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I23" t="n">
         <v>2.78</v>
@@ -6209,28 +6209,28 @@
         <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M23" t="n">
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="T23" t="n">
         <v>1.58</v>
@@ -6314,7 +6314,7 @@
         <v>5.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AV23" t="n">
         <v>4.9</v>
@@ -6329,7 +6329,7 @@
         <v>5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BA23" t="n">
         <v>6.4</v>
@@ -6392,7 +6392,7 @@
         <v>6.2</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="BV23" t="n">
         <v>19</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
         <v>3.75</v>
       </c>
       <c r="L24" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
@@ -6478,7 +6478,7 @@
         <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R24" t="n">
         <v>1.45</v>
@@ -6505,13 +6505,13 @@
         <v>15.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AA24" t="n">
         <v>110</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC24" t="n">
         <v>8.4</v>
@@ -6544,10 +6544,10 @@
         <v>70</v>
       </c>
       <c r="AM24" t="n">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AN24" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AO24" t="n">
         <v>50</v>
@@ -6562,7 +6562,7 @@
         <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AT24" t="n">
         <v>11</v>
@@ -6574,7 +6574,7 @@
         <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AX24" t="n">
         <v>15</v>
@@ -6586,89 +6586,89 @@
         <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BB24" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BC24" t="n">
         <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BE24" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BF24" t="n">
         <v>13</v>
       </c>
       <c r="BG24" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ24" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BN24" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP24" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR24" t="n">
         <v>29</v>
       </c>
       <c r="BS24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BV24" t="n">
         <v>26</v>
       </c>
       <c r="BW24" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX24" t="n">
         <v>36</v>
       </c>
       <c r="BY24" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BZ24" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -6699,25 +6699,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G25" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H25" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="I25" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J25" t="n">
         <v>4.1</v>
       </c>
       <c r="K25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M25" t="n">
         <v>1.02</v>
@@ -6732,7 +6732,7 @@
         <v>3.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R25" t="n">
         <v>1.88</v>
@@ -6750,10 +6750,10 @@
         <v>1.53</v>
       </c>
       <c r="W25" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X25" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="Y25" t="n">
         <v>25</v>
@@ -6762,19 +6762,19 @@
         <v>42</v>
       </c>
       <c r="AA25" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AB25" t="n">
         <v>22</v>
       </c>
       <c r="AC25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD25" t="n">
         <v>14</v>
       </c>
       <c r="AE25" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AF25" t="n">
         <v>25</v>
@@ -6789,13 +6789,13 @@
         <v>28</v>
       </c>
       <c r="AJ25" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AK25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL25" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AM25" t="n">
         <v>85</v>
@@ -6807,19 +6807,19 @@
         <v>12.5</v>
       </c>
       <c r="AP25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR25" t="n">
         <v>22</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>20</v>
-      </c>
       <c r="AS25" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AU25" t="n">
         <v>10</v>
@@ -6840,10 +6840,10 @@
         <v>12</v>
       </c>
       <c r="BA25" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BB25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC25" t="n">
         <v>18.5</v>
@@ -6852,19 +6852,19 @@
         <v>21</v>
       </c>
       <c r="BE25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG25" t="n">
         <v>11</v>
       </c>
       <c r="BH25" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BI25" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BJ25" t="n">
         <v>8.4</v>
@@ -6876,25 +6876,25 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN25" t="n">
         <v>6.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BP25" t="n">
         <v>16</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR25" t="n">
         <v>21</v>
       </c>
       <c r="BS25" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT25" t="n">
         <v>7</v>
@@ -6906,13 +6906,13 @@
         <v>18</v>
       </c>
       <c r="BW25" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY25" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ25" t="n">
         <v>12.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -6953,16 +6953,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="G26" t="n">
         <v>2.62</v>
       </c>
       <c r="H26" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I26" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J26" t="n">
         <v>3.2</v>
@@ -6971,7 +6971,7 @@
         <v>3.35</v>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M26" t="n">
         <v>1.08</v>
@@ -6980,13 +6980,13 @@
         <v>3.05</v>
       </c>
       <c r="O26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P26" t="n">
         <v>1.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R26" t="n">
         <v>1.27</v>
@@ -6995,16 +6995,16 @@
         <v>3.85</v>
       </c>
       <c r="T26" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U26" t="n">
         <v>1.95</v>
       </c>
       <c r="V26" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X26" t="n">
         <v>12.5</v>
@@ -7028,7 +7028,7 @@
         <v>15</v>
       </c>
       <c r="AE26" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF26" t="n">
         <v>17.5</v>
@@ -7046,19 +7046,19 @@
         <v>40</v>
       </c>
       <c r="AK26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL26" t="n">
         <v>50</v>
       </c>
       <c r="AM26" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN26" t="n">
         <v>32</v>
       </c>
       <c r="AO26" t="n">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AP26" t="n">
         <v>9.800000000000001</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="BB26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC26" t="n">
         <v>7</v>
@@ -7112,7 +7112,7 @@
         <v>22</v>
       </c>
       <c r="BG26" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BH26" t="n">
         <v>3.3</v>
@@ -7145,7 +7145,7 @@
         <v>6.2</v>
       </c>
       <c r="BR26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS26" t="n">
         <v>7</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
         <v>3.25</v>
       </c>
       <c r="H27" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I27" t="n">
         <v>2.52</v>
@@ -7222,7 +7222,7 @@
         <v>3.6</v>
       </c>
       <c r="K27" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L27" t="n">
         <v>1.37</v>
@@ -7237,16 +7237,16 @@
         <v>1.27</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R27" t="n">
         <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
         <v>1.65</v>
@@ -7267,13 +7267,13 @@
         <v>13.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA27" t="n">
         <v>34</v>
       </c>
       <c r="AB27" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AC27" t="n">
         <v>8.199999999999999</v>
@@ -7306,7 +7306,7 @@
         <v>46</v>
       </c>
       <c r="AM27" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN27" t="n">
         <v>27</v>
@@ -7339,28 +7339,28 @@
         <v>19</v>
       </c>
       <c r="AX27" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AY27" t="n">
         <v>12</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB27" t="n">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BC27" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BD27" t="n">
         <v>34</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BF27" t="n">
         <v>20</v>
@@ -7372,19 +7372,19 @@
         <v>3.7</v>
       </c>
       <c r="BI27" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN27" t="n">
         <v>6.4</v>
@@ -7396,41 +7396,41 @@
         <v>23</v>
       </c>
       <c r="BQ27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT27" t="n">
         <v>5.5</v>
       </c>
       <c r="BU27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV27" t="n">
         <v>17.5</v>
       </c>
       <c r="BW27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX27" t="n">
         <v>28</v>
       </c>
       <c r="BY27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ27" t="n">
         <v>23</v>
       </c>
       <c r="CA27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -7467,37 +7467,37 @@
         <v>1.39</v>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I28" t="n">
         <v>12</v>
       </c>
       <c r="J28" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K28" t="n">
         <v>5.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S28" t="n">
         <v>2.74</v>
@@ -7515,10 +7515,10 @@
         <v>3.55</v>
       </c>
       <c r="X28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="Z28" t="n">
         <v>530</v>
@@ -7527,7 +7527,7 @@
         <v>430</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC28" t="n">
         <v>12.5</v>
@@ -7545,13 +7545,13 @@
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AI28" t="n">
         <v>460</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AK28" t="n">
         <v>14.5</v>
@@ -7569,13 +7569,13 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ28" t="n">
         <v>23</v>
       </c>
       <c r="AR28" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AS28" t="n">
         <v>65</v>
@@ -7599,13 +7599,13 @@
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA28" t="n">
         <v>42</v>
       </c>
       <c r="BB28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC28" t="n">
         <v>13</v>
@@ -7623,10 +7623,10 @@
         <v>48</v>
       </c>
       <c r="BH28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BJ28" t="n">
         <v>12.5</v>
@@ -7638,53 +7638,53 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BN28" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BP28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BR28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS28" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT28" t="n">
         <v>14</v>
       </c>
       <c r="BU28" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BZ28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G29" t="n">
         <v>3.35</v>
       </c>
       <c r="H29" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I29" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J29" t="n">
         <v>3.9</v>
@@ -7733,13 +7733,13 @@
         <v>4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
         <v>1.22</v>
@@ -7748,10 +7748,10 @@
         <v>2.38</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S29" t="n">
         <v>2.74</v>
@@ -7763,7 +7763,7 @@
         <v>2.52</v>
       </c>
       <c r="V29" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="W29" t="n">
         <v>1.42</v>
@@ -7775,7 +7775,7 @@
         <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA29" t="n">
         <v>30</v>
@@ -7784,7 +7784,7 @@
         <v>17</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD29" t="n">
         <v>11.5</v>
@@ -7796,7 +7796,7 @@
         <v>26</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH29" t="n">
         <v>15.5</v>
@@ -7820,7 +7820,7 @@
         <v>25</v>
       </c>
       <c r="AO29" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP29" t="n">
         <v>17.5</v>
@@ -7853,7 +7853,7 @@
         <v>13</v>
       </c>
       <c r="AZ29" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA29" t="n">
         <v>27</v>
@@ -7895,10 +7895,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO29" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BP29" t="n">
         <v>25</v>
@@ -7919,16 +7919,16 @@
         <v>4.3</v>
       </c>
       <c r="BV29" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW29" t="n">
         <v>6.2</v>
       </c>
       <c r="BX29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
         <v>3.7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
@@ -8008,7 +8008,7 @@
         <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T30" t="n">
         <v>1.78</v>
@@ -8032,7 +8032,7 @@
         <v>26</v>
       </c>
       <c r="AA30" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB30" t="n">
         <v>10</v>
@@ -8074,7 +8074,7 @@
         <v>26</v>
       </c>
       <c r="AO30" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP30" t="n">
         <v>9.6</v>
@@ -8098,7 +8098,7 @@
         <v>11</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.7</v>
+        <v>30</v>
       </c>
       <c r="AX30" t="n">
         <v>10.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -8223,13 +8223,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G31" t="n">
         <v>2.7</v>
       </c>
       <c r="H31" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I31" t="n">
         <v>3.5</v>
@@ -8238,7 +8238,7 @@
         <v>3.15</v>
       </c>
       <c r="K31" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L31" t="n">
         <v>1.4</v>
@@ -8247,7 +8247,7 @@
         <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O31" t="n">
         <v>1.33</v>
@@ -8256,7 +8256,7 @@
         <v>1.81</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R31" t="n">
         <v>1.32</v>
@@ -8277,19 +8277,19 @@
         <v>1.58</v>
       </c>
       <c r="X31" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA31" t="n">
         <v>900</v>
       </c>
       <c r="AB31" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC31" t="n">
         <v>8.4</v>
@@ -8310,40 +8310,40 @@
         <v>19</v>
       </c>
       <c r="AI31" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ31" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
       </c>
       <c r="AL31" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM31" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO31" t="n">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="AP31" t="n">
         <v>10</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AR31" t="n">
-        <v>15.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AU31" t="n">
         <v>5.9</v>
@@ -8352,101 +8352,101 @@
         <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AY31" t="n">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="AZ31" t="n">
         <v>12.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB31" t="n">
         <v>22</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.1</v>
+        <v>22</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF31" t="n">
         <v>16</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ31" t="n">
         <v>10.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN31" t="n">
         <v>5.7</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR31" t="n">
         <v>36</v>
       </c>
       <c r="BS31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT31" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV31" t="n">
         <v>27</v>
       </c>
       <c r="BW31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ31" t="n">
         <v>32</v>
       </c>
       <c r="CA31" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
         <v>2.02</v>
       </c>
       <c r="G32" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H32" t="n">
         <v>3.85</v>
@@ -8495,7 +8495,7 @@
         <v>4.1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
@@ -8510,7 +8510,7 @@
         <v>2.16</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R32" t="n">
         <v>1.43</v>
@@ -8528,7 +8528,7 @@
         <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X32" t="n">
         <v>17.5</v>
@@ -8543,16 +8543,16 @@
         <v>80</v>
       </c>
       <c r="AB32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32" t="n">
         <v>16</v>
       </c>
       <c r="AE32" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AF32" t="n">
         <v>13.5</v>
@@ -8564,16 +8564,16 @@
         <v>17.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AJ32" t="n">
         <v>24</v>
       </c>
       <c r="AK32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM32" t="n">
         <v>85</v>
@@ -8582,25 +8582,25 @@
         <v>13</v>
       </c>
       <c r="AO32" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP32" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR32" t="n">
         <v>26</v>
       </c>
       <c r="AS32" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AT32" t="n">
         <v>10</v>
       </c>
       <c r="AU32" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV32" t="n">
         <v>14.5</v>
@@ -8621,7 +8621,7 @@
         <v>42</v>
       </c>
       <c r="BB32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC32" t="n">
         <v>18</v>
@@ -8630,19 +8630,19 @@
         <v>29</v>
       </c>
       <c r="BE32" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BF32" t="n">
         <v>11.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BH32" t="n">
         <v>3.8</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ32" t="n">
         <v>9.800000000000001</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
         <v>3.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
@@ -8839,10 +8839,10 @@
         <v>36</v>
       </c>
       <c r="AP33" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AR33" t="n">
         <v>13</v>
@@ -8851,16 +8851,16 @@
         <v>30</v>
       </c>
       <c r="AT33" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU33" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV33" t="n">
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.2</v>
+        <v>25</v>
       </c>
       <c r="AX33" t="n">
         <v>15</v>
@@ -8869,7 +8869,7 @@
         <v>10</v>
       </c>
       <c r="AZ33" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BA33" t="n">
         <v>34</v>
@@ -8878,7 +8878,7 @@
         <v>5.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>5.3</v>
+        <v>28</v>
       </c>
       <c r="BD33" t="n">
         <v>5.4</v>
@@ -8887,7 +8887,7 @@
         <v>5.7</v>
       </c>
       <c r="BF33" t="n">
-        <v>5.3</v>
+        <v>28</v>
       </c>
       <c r="BG33" t="n">
         <v>5.2</v>
@@ -8908,7 +8908,7 @@
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BN33" t="n">
         <v>6</v>
@@ -8920,13 +8920,13 @@
         <v>34</v>
       </c>
       <c r="BQ33" t="n">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR33" t="n">
         <v>55</v>
       </c>
       <c r="BS33" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BT33" t="n">
         <v>5.6</v>
@@ -8938,23 +8938,23 @@
         <v>30</v>
       </c>
       <c r="BW33" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BX33" t="n">
         <v>50</v>
       </c>
       <c r="BY33" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BZ33" t="n">
         <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G34" t="n">
         <v>1.89</v>
@@ -9081,10 +9081,10 @@
         <v>38</v>
       </c>
       <c r="AL34" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AM34" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN34" t="n">
         <v>22</v>
@@ -9114,25 +9114,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX34" t="n">
         <v>7</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AZ34" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BA34" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB34" t="n">
         <v>15.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BD34" t="n">
         <v>7.2</v>
@@ -9180,13 +9180,13 @@
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>3</v>
+        <v>10.5</v>
       </c>
       <c r="BT34" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU34" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
@@ -9204,11 +9204,11 @@
         <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>3</v>
+        <v>10.5</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -9242,10 +9242,10 @@
         <v>1.93</v>
       </c>
       <c r="G35" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H35" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I35" t="n">
         <v>4.2</v>
@@ -9257,7 +9257,7 @@
         <v>4.4</v>
       </c>
       <c r="L35" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M35" t="n">
         <v>1.03</v>
@@ -9266,7 +9266,7 @@
         <v>5.4</v>
       </c>
       <c r="O35" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P35" t="n">
         <v>2.48</v>
@@ -9290,16 +9290,16 @@
         <v>1.31</v>
       </c>
       <c r="W35" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X35" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y35" t="n">
         <v>22</v>
       </c>
       <c r="Z35" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AA35" t="n">
         <v>900</v>
@@ -9314,7 +9314,7 @@
         <v>17.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AF35" t="n">
         <v>15.5</v>
@@ -9326,7 +9326,7 @@
         <v>16.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AJ35" t="n">
         <v>25</v>
@@ -9338,7 +9338,7 @@
         <v>28</v>
       </c>
       <c r="AM35" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AN35" t="n">
         <v>9.4</v>
@@ -9347,19 +9347,19 @@
         <v>29</v>
       </c>
       <c r="AP35" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AQ35" t="n">
         <v>17.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AS35" t="n">
         <v>9</v>
       </c>
       <c r="AT35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU35" t="n">
         <v>8.4</v>
@@ -9368,19 +9368,19 @@
         <v>14</v>
       </c>
       <c r="AW35" t="n">
-        <v>32</v>
+        <v>9.6</v>
       </c>
       <c r="AX35" t="n">
         <v>12.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA35" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BB35" t="n">
         <v>19.5</v>
@@ -9389,22 +9389,22 @@
         <v>15.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BE35" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="BF35" t="n">
         <v>7.8</v>
       </c>
       <c r="BG35" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BH35" t="n">
         <v>4.6</v>
       </c>
       <c r="BI35" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="BJ35" t="n">
         <v>9</v>
@@ -9422,7 +9422,7 @@
         <v>5.4</v>
       </c>
       <c r="BO35" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP35" t="n">
         <v>13.5</v>
@@ -9440,7 +9440,7 @@
         <v>7.8</v>
       </c>
       <c r="BU35" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV35" t="n">
         <v>27</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
         <v>1.38</v>
       </c>
       <c r="H36" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I36" t="n">
         <v>11</v>
@@ -9511,7 +9511,7 @@
         <v>6.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M36" t="n">
         <v>1.03</v>
@@ -9526,13 +9526,13 @@
         <v>2.62</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R36" t="n">
         <v>1.64</v>
       </c>
       <c r="S36" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T36" t="n">
         <v>1.91</v>
@@ -9544,7 +9544,7 @@
         <v>1.1</v>
       </c>
       <c r="W36" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="X36" t="n">
         <v>28</v>
@@ -9553,7 +9553,7 @@
         <v>75</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AA36" t="n">
         <v>370</v>
@@ -9562,7 +9562,7 @@
         <v>11</v>
       </c>
       <c r="AC36" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD36" t="n">
         <v>38</v>
@@ -9577,10 +9577,10 @@
         <v>12</v>
       </c>
       <c r="AH36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ36" t="n">
         <v>11.5</v>
@@ -9592,10 +9592,10 @@
         <v>34</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AN36" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
@@ -9604,13 +9604,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AR36" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AS36" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AT36" t="n">
         <v>9.6</v>
@@ -9619,7 +9619,7 @@
         <v>11.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AW36" t="n">
         <v>42</v>
@@ -9628,13 +9628,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ36" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BB36" t="n">
         <v>10</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -9747,19 +9747,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="G37" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H37" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I37" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J37" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K37" t="n">
         <v>3.65</v>
@@ -9774,22 +9774,22 @@
         <v>4.1</v>
       </c>
       <c r="O37" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P37" t="n">
         <v>2.02</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R37" t="n">
         <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U37" t="n">
         <v>2.28</v>
@@ -9798,7 +9798,7 @@
         <v>1.57</v>
       </c>
       <c r="W37" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X37" t="n">
         <v>15.5</v>
@@ -9807,13 +9807,13 @@
         <v>12.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA37" t="n">
         <v>40</v>
       </c>
       <c r="AB37" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC37" t="n">
         <v>8</v>
@@ -9825,10 +9825,10 @@
         <v>30</v>
       </c>
       <c r="AF37" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH37" t="n">
         <v>16.5</v>
@@ -9846,7 +9846,7 @@
         <v>42</v>
       </c>
       <c r="AM37" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN37" t="n">
         <v>27</v>
@@ -9855,7 +9855,7 @@
         <v>23</v>
       </c>
       <c r="AP37" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ37" t="n">
         <v>11</v>
@@ -9864,7 +9864,7 @@
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AT37" t="n">
         <v>11</v>
@@ -9876,28 +9876,28 @@
         <v>11</v>
       </c>
       <c r="AW37" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AX37" t="n">
         <v>17</v>
       </c>
       <c r="AY37" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ37" t="n">
         <v>14.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BB37" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BC37" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BD37" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BE37" t="n">
         <v>36</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -10025,28 +10025,28 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2.04</v>
+        <v>3.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="R38" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S38" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="V38" t="n">
         <v>3.15</v>
@@ -10055,112 +10055,112 @@
         <v>1.13</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y38" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="Z38" t="n">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>900</v>
+        <v>15.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AD38" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AE38" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AG38" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AH38" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AL38" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM38" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO38" t="n">
-        <v>500</v>
+        <v>3.75</v>
       </c>
       <c r="AP38" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BB38" t="n">
         <v>1.03</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE38" t="n">
         <v>1.03</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BH38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -10258,13 +10258,13 @@
         <v>3.2</v>
       </c>
       <c r="G39" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H39" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I39" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J39" t="n">
         <v>4.2</v>
@@ -10288,82 +10288,82 @@
         <v>2.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R39" t="n">
         <v>1.68</v>
       </c>
       <c r="S39" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T39" t="n">
         <v>1.53</v>
       </c>
       <c r="U39" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V39" t="n">
         <v>1.81</v>
       </c>
       <c r="W39" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X39" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y39" t="n">
         <v>16.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB39" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC39" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD39" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF39" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AG39" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH39" t="n">
         <v>15</v>
       </c>
       <c r="AI39" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ39" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AK39" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AL39" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AM39" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="AN39" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO39" t="n">
         <v>10.5</v>
       </c>
       <c r="AP39" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AQ39" t="n">
         <v>13.5</v>
@@ -10372,7 +10372,7 @@
         <v>15.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT39" t="n">
         <v>17</v>
@@ -10387,7 +10387,7 @@
         <v>17.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AY39" t="n">
         <v>13</v>
@@ -10396,25 +10396,25 @@
         <v>13</v>
       </c>
       <c r="BA39" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB39" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BC39" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BD39" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BE39" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BF39" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH39" t="n">
         <v>4.5</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -10512,13 +10512,13 @@
         <v>8</v>
       </c>
       <c r="G40" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H40" t="n">
         <v>1.43</v>
       </c>
       <c r="I40" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J40" t="n">
         <v>4.4</v>
@@ -10536,7 +10536,7 @@
         <v>3.95</v>
       </c>
       <c r="O40" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P40" t="n">
         <v>2</v>
@@ -10560,7 +10560,7 @@
         <v>2.88</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X40" t="n">
         <v>21</v>
@@ -10599,7 +10599,7 @@
         <v>48</v>
       </c>
       <c r="AJ40" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AK40" t="n">
         <v>180</v>
@@ -10614,58 +10614,58 @@
         <v>270</v>
       </c>
       <c r="AO40" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP40" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ40" t="n">
         <v>5.9</v>
       </c>
       <c r="AR40" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS40" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AT40" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AV40" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX40" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA40" t="n">
         <v>5.1</v>
       </c>
-      <c r="AY40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BB40" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BC40" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG40" t="n">
         <v>6</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
         <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H41" t="n">
         <v>1.58</v>
@@ -10790,22 +10790,22 @@
         <v>6.4</v>
       </c>
       <c r="O41" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P41" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R41" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S41" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T41" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U41" t="n">
         <v>2.5</v>
@@ -10829,7 +10829,7 @@
         <v>15.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC41" t="n">
         <v>11.5</v>
@@ -10838,10 +10838,10 @@
         <v>10.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AF41" t="n">
-        <v>310</v>
+        <v>55</v>
       </c>
       <c r="AG41" t="n">
         <v>23</v>
@@ -10850,7 +10850,7 @@
         <v>18</v>
       </c>
       <c r="AI41" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AJ41" t="n">
         <v>690</v>
@@ -10862,7 +10862,7 @@
         <v>60</v>
       </c>
       <c r="AM41" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AN41" t="n">
         <v>50</v>
@@ -10874,7 +10874,7 @@
         <v>25</v>
       </c>
       <c r="AQ41" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR41" t="n">
         <v>11</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -11017,16 +11017,16 @@
         </is>
       </c>
       <c r="F42" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G42" t="n">
         <v>1.81</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1.82</v>
       </c>
       <c r="H42" t="n">
         <v>4.9</v>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>3.95</v>
@@ -11041,16 +11041,16 @@
         <v>1.05</v>
       </c>
       <c r="N42" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
         <v>1.27</v>
       </c>
       <c r="P42" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R42" t="n">
         <v>1.45</v>
@@ -11068,13 +11068,13 @@
         <v>1.24</v>
       </c>
       <c r="W42" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X42" t="n">
         <v>18.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z42" t="n">
         <v>40</v>
@@ -11086,7 +11086,7 @@
         <v>10</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD42" t="n">
         <v>19.5</v>
@@ -11107,7 +11107,7 @@
         <v>70</v>
       </c>
       <c r="AJ42" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AK42" t="n">
         <v>18</v>
@@ -11119,7 +11119,7 @@
         <v>100</v>
       </c>
       <c r="AN42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO42" t="n">
         <v>60</v>
@@ -11137,7 +11137,7 @@
         <v>40</v>
       </c>
       <c r="AT42" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU42" t="n">
         <v>8.4</v>
@@ -11176,7 +11176,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG42" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="BH42" t="n">
         <v>3.75</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -11283,10 +11283,10 @@
         <v>5.2</v>
       </c>
       <c r="J43" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L43" t="n">
         <v>1.3</v>
@@ -11295,28 +11295,28 @@
         <v>1.05</v>
       </c>
       <c r="N43" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O43" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R43" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S43" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="T43" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U43" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V43" t="n">
         <v>1.23</v>
@@ -11325,13 +11325,13 @@
         <v>2.24</v>
       </c>
       <c r="X43" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y43" t="n">
         <v>23</v>
       </c>
       <c r="Z43" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA43" t="n">
         <v>900</v>
@@ -11340,13 +11340,13 @@
         <v>11.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD43" t="n">
         <v>23</v>
       </c>
       <c r="AE43" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF43" t="n">
         <v>13.5</v>
@@ -11358,7 +11358,7 @@
         <v>21</v>
       </c>
       <c r="AI43" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ43" t="n">
         <v>22</v>
@@ -11373,13 +11373,13 @@
         <v>100</v>
       </c>
       <c r="AN43" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AO43" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AP43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ43" t="n">
         <v>17.5</v>
@@ -11388,19 +11388,19 @@
         <v>32</v>
       </c>
       <c r="AS43" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT43" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU43" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV43" t="n">
         <v>17</v>
       </c>
       <c r="AW43" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX43" t="n">
         <v>9</v>
@@ -11412,7 +11412,7 @@
         <v>14</v>
       </c>
       <c r="BA43" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB43" t="n">
         <v>16</v>
@@ -11421,19 +11421,19 @@
         <v>13</v>
       </c>
       <c r="BD43" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BE43" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF43" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG43" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH43" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI43" t="n">
         <v>3.15</v>
@@ -11448,7 +11448,7 @@
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN43" t="n">
         <v>4.5</v>
@@ -11478,13 +11478,13 @@
         <v>40</v>
       </c>
       <c r="BW43" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ43" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -11525,10 +11525,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G44" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H44" t="n">
         <v>8.800000000000001</v>
@@ -11537,7 +11537,7 @@
         <v>9.6</v>
       </c>
       <c r="J44" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K44" t="n">
         <v>5.4</v>
@@ -11564,7 +11564,7 @@
         <v>1.53</v>
       </c>
       <c r="S44" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T44" t="n">
         <v>1.92</v>
@@ -11576,7 +11576,7 @@
         <v>1.12</v>
       </c>
       <c r="W44" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X44" t="n">
         <v>23</v>
@@ -11588,7 +11588,7 @@
         <v>85</v>
       </c>
       <c r="AA44" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AB44" t="n">
         <v>10</v>
@@ -11684,7 +11684,7 @@
         <v>5.2</v>
       </c>
       <c r="BG44" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BH44" t="n">
         <v>4.2</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -11779,28 +11779,28 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="G45" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H45" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I45" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="J45" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K45" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N45" t="n">
         <v>2.5</v>
@@ -11809,136 +11809,136 @@
         <v>1.52</v>
       </c>
       <c r="P45" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R45" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S45" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V45" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W45" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X45" t="n">
-        <v>500</v>
+        <v>9</v>
       </c>
       <c r="Y45" t="n">
-        <v>500</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z45" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AA45" t="n">
-        <v>900</v>
+        <v>42</v>
       </c>
       <c r="AB45" t="n">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>500</v>
+        <v>7.4</v>
       </c>
       <c r="AD45" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AF45" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AG45" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AI45" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ45" t="n">
         <v>500</v>
       </c>
       <c r="AK45" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL45" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AM45" t="n">
         <v>500</v>
       </c>
       <c r="AN45" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AO45" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -12036,10 +12036,10 @@
         <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H46" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I46" t="n">
         <v>2.8</v>
@@ -12048,10 +12048,10 @@
         <v>3.05</v>
       </c>
       <c r="K46" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L46" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M46" t="n">
         <v>1.1</v>
@@ -12063,7 +12063,7 @@
         <v>1.43</v>
       </c>
       <c r="P46" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q46" t="n">
         <v>2.3</v>
@@ -12081,7 +12081,7 @@
         <v>1.93</v>
       </c>
       <c r="V46" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W46" t="n">
         <v>1.42</v>
@@ -12102,7 +12102,7 @@
         <v>10.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD46" t="n">
         <v>15</v>
@@ -12150,7 +12150,7 @@
         <v>14</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AT46" t="n">
         <v>8.800000000000001</v>
@@ -12162,7 +12162,7 @@
         <v>10.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX46" t="n">
         <v>17.5</v>
@@ -12174,25 +12174,25 @@
         <v>16.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB46" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BC46" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BD46" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF46" t="n">
         <v>32</v>
       </c>
       <c r="BG46" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH46" t="n">
         <v>3.05</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
         <v>1.91</v>
       </c>
       <c r="I47" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J47" t="n">
         <v>3.5</v>
@@ -12335,7 +12335,7 @@
         <v>1.9</v>
       </c>
       <c r="V47" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W47" t="n">
         <v>1.25</v>
@@ -12419,7 +12419,7 @@
         <v>19.5</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AY47" t="n">
         <v>14.5</v>
@@ -12431,19 +12431,19 @@
         <v>34</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF47" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="BG47" t="n">
         <v>13.5</v>
@@ -12464,7 +12464,7 @@
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BN47" t="n">
         <v>8.4</v>
@@ -12476,13 +12476,13 @@
         <v>48</v>
       </c>
       <c r="BQ47" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="BR47" t="n">
         <v>85</v>
       </c>
       <c r="BS47" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BT47" t="n">
         <v>4.6</v>
@@ -12500,17 +12500,17 @@
         <v>34</v>
       </c>
       <c r="BY47" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BZ47" t="n">
         <v>32</v>
       </c>
       <c r="CA47" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -12547,13 +12547,13 @@
         <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="I48" t="n">
         <v>3.55</v>
       </c>
       <c r="J48" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="K48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12807,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K49" t="n">
         <v>4</v>
@@ -12855,10 +12855,10 @@
         <v>18.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AA49" t="n">
-        <v>420</v>
+        <v>700</v>
       </c>
       <c r="AB49" t="n">
         <v>6.4</v>
@@ -12870,7 +12870,7 @@
         <v>36</v>
       </c>
       <c r="AE49" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AF49" t="n">
         <v>8.6</v>
@@ -12882,7 +12882,7 @@
         <v>40</v>
       </c>
       <c r="AI49" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AJ49" t="n">
         <v>18</v>
@@ -12894,13 +12894,13 @@
         <v>500</v>
       </c>
       <c r="AM49" t="n">
-        <v>410</v>
+        <v>700</v>
       </c>
       <c r="AN49" t="n">
         <v>22</v>
       </c>
       <c r="AO49" t="n">
-        <v>520</v>
+        <v>700</v>
       </c>
       <c r="AP49" t="n">
         <v>3.95</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
         <v>4.9</v>
       </c>
       <c r="H50" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I50" t="n">
         <v>1.99</v>
@@ -13106,25 +13106,25 @@
         <v>16.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB50" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AC50" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD50" t="n">
         <v>12.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF50" t="n">
         <v>40</v>
@@ -13166,7 +13166,7 @@
         <v>10</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT50" t="n">
         <v>11.5</v>
@@ -13178,10 +13178,10 @@
         <v>9</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX50" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AY50" t="n">
         <v>13.5</v>
@@ -13190,22 +13190,22 @@
         <v>14.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB50" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BC50" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BD50" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE50" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF50" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BG50" t="n">
         <v>11.5</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -13303,13 +13303,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="G51" t="n">
         <v>2.28</v>
       </c>
       <c r="H51" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I51" t="n">
         <v>5.5</v>
@@ -13318,7 +13318,7 @@
         <v>3.45</v>
       </c>
       <c r="K51" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -13327,10 +13327,10 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>1.8</v>
+        <v>2.92</v>
       </c>
       <c r="O51" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P51" t="n">
         <v>1.8</v>
@@ -13339,10 +13339,10 @@
         <v>1.7</v>
       </c>
       <c r="R51" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="S51" t="n">
-        <v>1.7</v>
+        <v>2.46</v>
       </c>
       <c r="T51" t="n">
         <v>1.01</v>
@@ -13357,109 +13357,109 @@
         <v>1.78</v>
       </c>
       <c r="X51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BG51" t="n">
         <v>1.01</v>
@@ -13474,49 +13474,49 @@
         <v>1000</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BN51" t="n">
         <v>1000</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BP51" t="n">
         <v>1000</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BR51" t="n">
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BT51" t="n">
         <v>1000</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BV51" t="n">
         <v>1000</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BZ51" t="n">
         <v>0</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -13596,13 +13596,13 @@
         <v>1.25</v>
       </c>
       <c r="S52" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="T52" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U52" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V52" t="n">
         <v>1.53</v>
@@ -13647,16 +13647,16 @@
         <v>60</v>
       </c>
       <c r="AJ52" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AK52" t="n">
         <v>48</v>
       </c>
       <c r="AL52" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM52" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN52" t="n">
         <v>55</v>
@@ -13665,58 +13665,58 @@
         <v>40</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG52" t="n">
-        <v>25</v>
+        <v>4.5</v>
       </c>
       <c r="BH52" t="n">
         <v>3.5</v>
@@ -13728,49 +13728,49 @@
         <v>1000</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BN52" t="n">
         <v>1000</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BP52" t="n">
         <v>1000</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BR52" t="n">
         <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BT52" t="n">
         <v>1000</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BV52" t="n">
         <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BX52" t="n">
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BZ52" t="n">
         <v>0</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -13811,19 +13811,19 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="G53" t="n">
         <v>2.54</v>
       </c>
       <c r="H53" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="I53" t="n">
         <v>1000</v>
       </c>
       <c r="J53" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="K53" t="n">
         <v>1000</v>
@@ -13835,7 +13835,7 @@
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O53" t="n">
         <v>1.02</v>
@@ -13853,7 +13853,7 @@
         <v>1.54</v>
       </c>
       <c r="T53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U53" t="n">
         <v>1.01</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -14068,34 +14068,34 @@
         <v>2.92</v>
       </c>
       <c r="G54" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H54" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I54" t="n">
         <v>2.84</v>
       </c>
       <c r="J54" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K54" t="n">
         <v>3.25</v>
       </c>
       <c r="L54" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M54" t="n">
         <v>1.12</v>
       </c>
       <c r="N54" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O54" t="n">
         <v>1.52</v>
       </c>
       <c r="P54" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q54" t="n">
         <v>2.54</v>
@@ -14116,7 +14116,7 @@
         <v>1.54</v>
       </c>
       <c r="W54" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X54" t="n">
         <v>10</v>
@@ -14128,7 +14128,7 @@
         <v>21</v>
       </c>
       <c r="AA54" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AB54" t="n">
         <v>10.5</v>
@@ -14152,22 +14152,22 @@
         <v>26</v>
       </c>
       <c r="AI54" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ54" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AK54" t="n">
         <v>55</v>
       </c>
       <c r="AL54" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM54" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN54" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO54" t="n">
         <v>60</v>
@@ -14194,7 +14194,7 @@
         <v>10.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX54" t="n">
         <v>14.5</v>
@@ -14206,34 +14206,34 @@
         <v>16.5</v>
       </c>
       <c r="BA54" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB54" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>4.8</v>
       </c>
       <c r="BC54" t="n">
         <v>4.8</v>
       </c>
       <c r="BD54" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF54" t="n">
         <v>4.9</v>
       </c>
-      <c r="BE54" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF54" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG54" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH54" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BJ54" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK54" t="n">
         <v>1.01</v>
@@ -14245,10 +14245,10 @@
         <v>1.01</v>
       </c>
       <c r="BN54" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO54" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP54" t="n">
         <v>1000</v>
@@ -14263,10 +14263,10 @@
         <v>1.01</v>
       </c>
       <c r="BT54" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU54" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -14319,19 +14319,19 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="G55" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H55" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I55" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J55" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K55" t="n">
         <v>3.7</v>
@@ -14346,7 +14346,7 @@
         <v>2.68</v>
       </c>
       <c r="O55" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P55" t="n">
         <v>1.59</v>
@@ -14358,19 +14358,19 @@
         <v>1.21</v>
       </c>
       <c r="S55" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T55" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U55" t="n">
         <v>1.74</v>
       </c>
       <c r="V55" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W55" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X55" t="n">
         <v>12</v>
@@ -14379,7 +14379,7 @@
         <v>14.5</v>
       </c>
       <c r="Z55" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AA55" t="n">
         <v>900</v>
@@ -14391,10 +14391,10 @@
         <v>9.4</v>
       </c>
       <c r="AD55" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE55" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF55" t="n">
         <v>11</v>
@@ -14412,7 +14412,7 @@
         <v>24</v>
       </c>
       <c r="AK55" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL55" t="n">
         <v>65</v>
@@ -14427,58 +14427,58 @@
         <v>700</v>
       </c>
       <c r="AP55" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ55" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR55" t="n">
         <v>5.7</v>
       </c>
       <c r="AS55" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW55" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT55" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW55" t="n">
+      <c r="AX55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD55" t="n">
         <v>6</v>
       </c>
-      <c r="AX55" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ55" t="n">
+      <c r="BE55" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF55" t="n">
         <v>5.2</v>
       </c>
-      <c r="BA55" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>5</v>
-      </c>
       <c r="BG55" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH55" t="n">
         <v>2.94</v>
@@ -14490,7 +14490,7 @@
         <v>12</v>
       </c>
       <c r="BK55" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
@@ -14505,7 +14505,7 @@
         <v>3.2</v>
       </c>
       <c r="BP55" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ55" t="n">
         <v>6.4</v>
@@ -14520,13 +14520,13 @@
         <v>8.6</v>
       </c>
       <c r="BU55" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV55" t="n">
         <v>55</v>
       </c>
       <c r="BW55" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -14576,10 +14576,10 @@
         <v>2.06</v>
       </c>
       <c r="G56" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H56" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I56" t="n">
         <v>4.5</v>
@@ -14591,7 +14591,7 @@
         <v>3.6</v>
       </c>
       <c r="L56" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M56" t="n">
         <v>1.09</v>
@@ -14606,7 +14606,7 @@
         <v>1.66</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R56" t="n">
         <v>1.24</v>
@@ -14624,7 +14624,7 @@
         <v>1.28</v>
       </c>
       <c r="W56" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X56" t="n">
         <v>12.5</v>
@@ -14651,7 +14651,7 @@
         <v>500</v>
       </c>
       <c r="AF56" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG56" t="n">
         <v>11.5</v>
@@ -14675,7 +14675,7 @@
         <v>500</v>
       </c>
       <c r="AN56" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO56" t="n">
         <v>500</v>
@@ -14690,19 +14690,19 @@
         <v>21</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT56" t="n">
         <v>6.8</v>
       </c>
       <c r="AU56" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV56" t="n">
         <v>13</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AX56" t="n">
         <v>10.5</v>
@@ -14714,7 +14714,7 @@
         <v>15.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB56" t="n">
         <v>20</v>
@@ -14726,22 +14726,22 @@
         <v>34</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF56" t="n">
         <v>18.5</v>
       </c>
       <c r="BG56" t="n">
-        <v>2.42</v>
+        <v>7.4</v>
       </c>
       <c r="BH56" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="BJ56" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK56" t="n">
         <v>6.8</v>
@@ -14750,28 +14750,28 @@
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BN56" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BO56" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP56" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="BQ56" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR56" t="n">
         <v>50</v>
       </c>
       <c r="BS56" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BT56" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BU56" t="n">
         <v>4.9</v>
@@ -14780,23 +14780,23 @@
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BX56" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY56" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BZ56" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14830,7 @@
         <v>2.56</v>
       </c>
       <c r="G57" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H57" t="n">
         <v>3.2</v>
@@ -14839,7 +14839,7 @@
         <v>3.55</v>
       </c>
       <c r="J57" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K57" t="n">
         <v>3.2</v>
@@ -14851,7 +14851,7 @@
         <v>1.13</v>
       </c>
       <c r="N57" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="O57" t="n">
         <v>1.57</v>
@@ -14878,7 +14878,7 @@
         <v>1.4</v>
       </c>
       <c r="W57" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X57" t="n">
         <v>8.4</v>
@@ -14899,7 +14899,7 @@
         <v>7.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE57" t="n">
         <v>70</v>
@@ -14944,7 +14944,7 @@
         <v>17.5</v>
       </c>
       <c r="AS57" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT57" t="n">
         <v>6.4</v>
@@ -14956,7 +14956,7 @@
         <v>13</v>
       </c>
       <c r="AW57" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX57" t="n">
         <v>11</v>
@@ -14968,25 +14968,25 @@
         <v>20</v>
       </c>
       <c r="BA57" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB57" t="n">
         <v>34</v>
       </c>
       <c r="BC57" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD57" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE57" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF57" t="n">
         <v>36</v>
       </c>
       <c r="BG57" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH57" t="n">
         <v>2.68</v>
@@ -14998,7 +14998,7 @@
         <v>12</v>
       </c>
       <c r="BK57" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL57" t="n">
         <v>1000</v>
@@ -15013,7 +15013,7 @@
         <v>4</v>
       </c>
       <c r="BP57" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ57" t="n">
         <v>7.8</v>
@@ -15022,7 +15022,7 @@
         <v>1000</v>
       </c>
       <c r="BS57" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT57" t="n">
         <v>6.6</v>
@@ -15034,13 +15034,13 @@
         <v>1000</v>
       </c>
       <c r="BW57" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX57" t="n">
         <v>1000</v>
       </c>
       <c r="BY57" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ57" t="n">
         <v>1000</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,260 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Guayaquil City</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Delfin</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>210</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>540</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>120</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>140</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>410</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>200</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>75</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-07-11 21:00:43</t>
         </is>
       </c>
     </row>
